--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-14.xlsx
@@ -946,7 +946,7 @@
     <t>Deportes Limache</t>
   </si>
   <si>
-    <t>2026-09-13 09:38:58</t>
+    <t>2026-09-13 11:58:09</t>
   </si>
 </sst>
 </file>
@@ -1540,22 +1540,22 @@
         <v>235</v>
       </c>
       <c r="F2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="G2">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H2">
         <v>1.57</v>
       </c>
       <c r="I2">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="J2">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K2">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L2">
         <v>1.25</v>
@@ -1564,142 +1564,142 @@
         <v>1.02</v>
       </c>
       <c r="N2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O2">
         <v>1.16</v>
       </c>
       <c r="P2">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q2">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R2">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="S2">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T2">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="U2">
-        <v>1.02</v>
+        <v>2.42</v>
       </c>
       <c r="V2">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="W2">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1782,16 +1782,16 @@
         <v>236</v>
       </c>
       <c r="F3">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G3">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H3">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I3">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J3">
         <v>3.25</v>
@@ -1803,7 +1803,7 @@
         <v>1.44</v>
       </c>
       <c r="M3">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N3">
         <v>3.6</v>
@@ -1812,7 +1812,7 @@
         <v>1.36</v>
       </c>
       <c r="P3">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q3">
         <v>2.1</v>
@@ -1830,10 +1830,10 @@
         <v>2.08</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W3">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X3">
         <v>13</v>
@@ -1842,13 +1842,13 @@
         <v>16</v>
       </c>
       <c r="Z3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AA3">
         <v>70</v>
       </c>
       <c r="AB3">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AC3">
         <v>7.8</v>
@@ -1866,7 +1866,7 @@
         <v>11.5</v>
       </c>
       <c r="AH3">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AI3">
         <v>70</v>
@@ -1911,7 +1911,7 @@
         <v>13</v>
       </c>
       <c r="AW3">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
         <v>12.5</v>
@@ -1926,10 +1926,10 @@
         <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
         <v>1.01</v>
@@ -2027,10 +2027,10 @@
         <v>2.74</v>
       </c>
       <c r="G4">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I4">
         <v>3.35</v>
@@ -2039,10 +2039,10 @@
         <v>2.92</v>
       </c>
       <c r="K4">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="M4">
         <v>1.16</v>
@@ -2057,10 +2057,10 @@
         <v>1.46</v>
       </c>
       <c r="Q4">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R4">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S4">
         <v>6.8</v>
@@ -2075,7 +2075,7 @@
         <v>1.42</v>
       </c>
       <c r="W4">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X4">
         <v>7.2</v>
@@ -2111,7 +2111,7 @@
         <v>27</v>
       </c>
       <c r="AI4">
-        <v>580</v>
+        <v>480</v>
       </c>
       <c r="AJ4">
         <v>120</v>
@@ -2120,19 +2120,19 @@
         <v>130</v>
       </c>
       <c r="AL4">
-        <v>580</v>
+        <v>480</v>
       </c>
       <c r="AM4">
         <v>300</v>
       </c>
       <c r="AN4">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AO4">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ4">
         <v>7.6</v>
@@ -2141,7 +2141,7 @@
         <v>17.5</v>
       </c>
       <c r="AS4">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AT4">
         <v>7</v>
@@ -2174,31 +2174,31 @@
         <v>40</v>
       </c>
       <c r="BD4">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="BE4">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="BF4">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BG4">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="BH4">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="BI4">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="BJ4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BK4">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL4">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="BM4">
         <v>1.01</v>
@@ -2207,43 +2207,43 @@
         <v>6.2</v>
       </c>
       <c r="BO4">
+        <v>4.3</v>
+      </c>
+      <c r="BP4">
+        <v>28</v>
+      </c>
+      <c r="BQ4">
+        <v>1.01</v>
+      </c>
+      <c r="BR4">
+        <v>60</v>
+      </c>
+      <c r="BS4">
+        <v>1.01</v>
+      </c>
+      <c r="BT4">
+        <v>6.8</v>
+      </c>
+      <c r="BU4">
         <v>4.7</v>
       </c>
-      <c r="BP4">
-        <v>32</v>
-      </c>
-      <c r="BQ4">
-        <v>20</v>
-      </c>
-      <c r="BR4">
+      <c r="BV4">
+        <v>34</v>
+      </c>
+      <c r="BW4">
+        <v>1.01</v>
+      </c>
+      <c r="BX4">
         <v>65</v>
       </c>
-      <c r="BS4">
-        <v>40</v>
-      </c>
-      <c r="BT4">
-        <v>7</v>
-      </c>
-      <c r="BU4">
-        <v>5.2</v>
-      </c>
-      <c r="BV4">
-        <v>40</v>
-      </c>
-      <c r="BW4">
-        <v>25</v>
-      </c>
-      <c r="BX4">
+      <c r="BY4">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4">
         <v>70</v>
       </c>
-      <c r="BY4">
-        <v>46</v>
-      </c>
-      <c r="BZ4">
-        <v>75</v>
-      </c>
       <c r="CA4">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="s">
         <v>310</v>
@@ -2269,10 +2269,10 @@
         <v>2.04</v>
       </c>
       <c r="G5">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H5">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I5">
         <v>3.75</v>
@@ -2311,7 +2311,7 @@
         <v>1.67</v>
       </c>
       <c r="U5">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V5">
         <v>1.3</v>
@@ -2320,28 +2320,28 @@
         <v>1.78</v>
       </c>
       <c r="X5">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Y5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z5">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA5">
         <v>85</v>
       </c>
       <c r="AB5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC5">
         <v>9</v>
       </c>
       <c r="AD5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE5">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF5">
         <v>14.5</v>
@@ -2356,7 +2356,7 @@
         <v>46</v>
       </c>
       <c r="AJ5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK5">
         <v>21</v>
@@ -2368,7 +2368,7 @@
         <v>80</v>
       </c>
       <c r="AN5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO5">
         <v>42</v>
@@ -2392,7 +2392,7 @@
         <v>8</v>
       </c>
       <c r="AV5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW5">
         <v>32</v>
@@ -2416,28 +2416,28 @@
         <v>17.5</v>
       </c>
       <c r="BD5">
-        <v>25</v>
+        <v>9.6</v>
       </c>
       <c r="BE5">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF5">
         <v>10.5</v>
       </c>
       <c r="BG5">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BH5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI5">
         <v>3.25</v>
       </c>
       <c r="BJ5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BK5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -2446,7 +2446,7 @@
         <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO5">
         <v>4</v>
@@ -2464,7 +2464,7 @@
         <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU5">
         <v>5.5</v>
@@ -2508,10 +2508,10 @@
         <v>239</v>
       </c>
       <c r="F6">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="G6">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H6">
         <v>2.48</v>
@@ -2520,7 +2520,7 @@
         <v>2.54</v>
       </c>
       <c r="J6">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <v>4.1</v>
@@ -2547,7 +2547,7 @@
         <v>1.72</v>
       </c>
       <c r="S6">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T6">
         <v>1.5</v>
@@ -2559,7 +2559,7 @@
         <v>1.65</v>
       </c>
       <c r="W6">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X6">
         <v>27</v>
@@ -2628,7 +2628,7 @@
         <v>30</v>
       </c>
       <c r="AT6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU6">
         <v>9</v>
@@ -2661,7 +2661,7 @@
         <v>26</v>
       </c>
       <c r="BE6">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BF6">
         <v>13</v>
@@ -2670,16 +2670,16 @@
         <v>11</v>
       </c>
       <c r="BH6">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BI6">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BJ6">
         <v>12</v>
       </c>
       <c r="BK6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2691,7 +2691,7 @@
         <v>8.4</v>
       </c>
       <c r="BO6">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BP6">
         <v>1000</v>
@@ -2706,10 +2706,10 @@
         <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BU6">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV6">
         <v>1000</v>
@@ -2750,127 +2750,127 @@
         <v>240</v>
       </c>
       <c r="F7">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G7">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="H7">
         <v>6.2</v>
       </c>
       <c r="I7">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J7">
         <v>4.7</v>
       </c>
       <c r="K7">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>1.32</v>
       </c>
       <c r="M7">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N7">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="O7">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P7">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="Q7">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="R7">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="S7">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="T7">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="U7">
         <v>2.12</v>
       </c>
       <c r="V7">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W7">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="X7">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="Y7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z7">
         <v>70</v>
       </c>
       <c r="AA7">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AB7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC7">
         <v>11.5</v>
       </c>
       <c r="AD7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE7">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG7">
         <v>10</v>
       </c>
       <c r="AH7">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI7">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AK7">
         <v>15.5</v>
       </c>
       <c r="AL7">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM7">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN7">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO7">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP7">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AQ7">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AR7">
-        <v>7.6</v>
+        <v>22</v>
       </c>
       <c r="AS7">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT7">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU7">
         <v>10</v>
@@ -2879,7 +2879,7 @@
         <v>20</v>
       </c>
       <c r="AW7">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX7">
         <v>9.199999999999999</v>
@@ -2888,40 +2888,40 @@
         <v>9</v>
       </c>
       <c r="AZ7">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA7">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BB7">
         <v>12.5</v>
       </c>
       <c r="BC7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD7">
         <v>27</v>
       </c>
       <c r="BE7">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF7">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BG7">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH7">
         <v>4.7</v>
       </c>
       <c r="BI7">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ7">
         <v>18</v>
       </c>
       <c r="BK7">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2930,13 +2930,13 @@
         <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BO7">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP7">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ7">
         <v>6.8</v>
@@ -2948,10 +2948,10 @@
         <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BU7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BV7">
         <v>1000</v>
@@ -2998,7 +2998,7 @@
         <v>5</v>
       </c>
       <c r="H8">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="I8">
         <v>1.94</v>
@@ -3010,19 +3010,19 @@
         <v>3.8</v>
       </c>
       <c r="L8">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M8">
         <v>1.08</v>
       </c>
       <c r="N8">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O8">
         <v>1.37</v>
       </c>
       <c r="P8">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q8">
         <v>2.1</v>
@@ -3034,7 +3034,7 @@
         <v>3.85</v>
       </c>
       <c r="T8">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U8">
         <v>1.97</v>
@@ -3046,7 +3046,7 @@
         <v>1.25</v>
       </c>
       <c r="X8">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Y8">
         <v>8.199999999999999</v>
@@ -3058,7 +3058,7 @@
         <v>25</v>
       </c>
       <c r="AB8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AC8">
         <v>8.4</v>
@@ -3070,16 +3070,16 @@
         <v>25</v>
       </c>
       <c r="AF8">
+        <v>38</v>
+      </c>
+      <c r="AG8">
+        <v>23</v>
+      </c>
+      <c r="AH8">
+        <v>21</v>
+      </c>
+      <c r="AI8">
         <v>42</v>
-      </c>
-      <c r="AG8">
-        <v>22</v>
-      </c>
-      <c r="AH8">
-        <v>24</v>
-      </c>
-      <c r="AI8">
-        <v>46</v>
       </c>
       <c r="AJ8">
         <v>140</v>
@@ -3094,22 +3094,22 @@
         <v>140</v>
       </c>
       <c r="AN8">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AO8">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AP8">
         <v>11</v>
       </c>
       <c r="AQ8">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR8">
         <v>9.800000000000001</v>
       </c>
       <c r="AS8">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AT8">
         <v>13.5</v>
@@ -3121,7 +3121,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW8">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX8">
         <v>13</v>
@@ -3130,25 +3130,25 @@
         <v>16.5</v>
       </c>
       <c r="AZ8">
-        <v>4.8</v>
+        <v>17.5</v>
       </c>
       <c r="BA8">
-        <v>16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB8">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC8">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="BD8">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="BE8">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF8">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="BG8">
         <v>13</v>
@@ -3240,22 +3240,22 @@
         <v>3.85</v>
       </c>
       <c r="H9">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I9">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="J9">
-        <v>3.15</v>
+        <v>1.1</v>
       </c>
       <c r="K9">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L9">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N9">
         <v>3</v>
@@ -3264,7 +3264,7 @@
         <v>1.32</v>
       </c>
       <c r="P9">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q9">
         <v>1.92</v>
@@ -3282,7 +3282,7 @@
         <v>1.81</v>
       </c>
       <c r="V9">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W9">
         <v>1.35</v>
@@ -3476,145 +3476,145 @@
         <v>243</v>
       </c>
       <c r="F10">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="G10">
         <v>7.4</v>
       </c>
       <c r="H10">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="I10">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="J10">
+        <v>3.55</v>
+      </c>
+      <c r="K10">
+        <v>4.2</v>
+      </c>
+      <c r="L10">
+        <v>1.39</v>
+      </c>
+      <c r="M10">
+        <v>1.08</v>
+      </c>
+      <c r="N10">
+        <v>3.25</v>
+      </c>
+      <c r="O10">
+        <v>1.32</v>
+      </c>
+      <c r="P10">
+        <v>1.79</v>
+      </c>
+      <c r="Q10">
+        <v>2.06</v>
+      </c>
+      <c r="R10">
+        <v>1.29</v>
+      </c>
+      <c r="S10">
         <v>3.5</v>
       </c>
-      <c r="K10">
-        <v>5.4</v>
-      </c>
-      <c r="L10">
-        <v>1.01</v>
-      </c>
-      <c r="M10">
-        <v>1.01</v>
-      </c>
-      <c r="N10">
-        <v>3.1</v>
-      </c>
-      <c r="O10">
-        <v>1.01</v>
-      </c>
-      <c r="P10">
-        <v>1.74</v>
-      </c>
-      <c r="Q10">
-        <v>2</v>
-      </c>
-      <c r="R10">
-        <v>1.23</v>
-      </c>
-      <c r="S10">
-        <v>2.82</v>
-      </c>
       <c r="T10">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U10">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V10">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="W10">
         <v>1.15</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AX10">
         <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA10">
         <v>1.01</v>
@@ -3635,13 +3635,13 @@
         <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH10">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
@@ -3677,7 +3677,7 @@
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
         <v>1000</v>
@@ -3718,64 +3718,64 @@
         <v>244</v>
       </c>
       <c r="F11">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="G11">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="H11">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J11">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K11">
-        <v>890</v>
+        <v>5.5</v>
       </c>
       <c r="L11">
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N11">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O11">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P11">
-        <v>1.94</v>
+        <v>2.22</v>
       </c>
       <c r="Q11">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R11">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="S11">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T11">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V11">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="W11">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="X11">
         <v>1000</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z11">
         <v>100</v>
@@ -3784,25 +3784,25 @@
         <v>1000</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC11">
-        <v>29</v>
+        <v>19.5</v>
       </c>
       <c r="AD11">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AE11">
         <v>1000</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG11">
         <v>23</v>
       </c>
       <c r="AH11">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AI11">
         <v>1000</v>
@@ -3820,64 +3820,64 @@
         <v>1000</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO11">
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="AQ11">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="AS11">
-        <v>55</v>
+        <v>2.08</v>
       </c>
       <c r="AT11">
         <v>6.6</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW11">
-        <v>42</v>
+        <v>2.08</v>
       </c>
       <c r="AX11">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AY11">
         <v>7.8</v>
       </c>
       <c r="AZ11">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BB11">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BC11">
         <v>9.4</v>
       </c>
       <c r="BD11">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3960,22 +3960,22 @@
         <v>245</v>
       </c>
       <c r="F12">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="G12">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H12">
         <v>3.5</v>
       </c>
       <c r="I12">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="J12">
         <v>2.4</v>
       </c>
       <c r="K12">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3987,7 +3987,7 @@
         <v>2.12</v>
       </c>
       <c r="O12">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="P12">
         <v>1.36</v>
@@ -4002,16 +4002,16 @@
         <v>5.9</v>
       </c>
       <c r="T12">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U12">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="V12">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W12">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X12">
         <v>970</v>
@@ -4071,55 +4071,55 @@
         <v>4.5</v>
       </c>
       <c r="AQ12">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AR12">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AS12">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AT12">
-        <v>6</v>
+        <v>1.53</v>
       </c>
       <c r="AU12">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AV12">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AW12">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AX12">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AY12">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AZ12">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="BA12">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="BB12">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="BC12">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="BD12">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="BE12">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="BF12">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="BG12">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="BH12">
         <v>970</v>
@@ -4205,7 +4205,7 @@
         <v>1.68</v>
       </c>
       <c r="G13">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H13">
         <v>3.35</v>
@@ -4217,7 +4217,7 @@
         <v>3.3</v>
       </c>
       <c r="K13">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -4235,13 +4235,13 @@
         <v>1.98</v>
       </c>
       <c r="Q13">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R13">
         <v>1.32</v>
       </c>
       <c r="S13">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -4253,7 +4253,7 @@
         <v>1.2</v>
       </c>
       <c r="W13">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4444,7 +4444,7 @@
         <v>247</v>
       </c>
       <c r="F14">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="G14">
         <v>1.85</v>
@@ -4459,7 +4459,7 @@
         <v>3.9</v>
       </c>
       <c r="K14">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4468,7 +4468,7 @@
         <v>1.05</v>
       </c>
       <c r="N14">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="O14">
         <v>1.26</v>
@@ -4477,13 +4477,13 @@
         <v>2</v>
       </c>
       <c r="Q14">
-        <v>1.38</v>
+        <v>1.79</v>
       </c>
       <c r="R14">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S14">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="T14">
         <v>1.01</v>
@@ -4686,7 +4686,7 @@
         <v>248</v>
       </c>
       <c r="F15">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="G15">
         <v>1.24</v>
@@ -4698,7 +4698,7 @@
         <v>1000</v>
       </c>
       <c r="J15">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="K15">
         <v>900</v>
@@ -4710,22 +4710,22 @@
         <v>1.02</v>
       </c>
       <c r="N15">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="O15">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="P15">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q15">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="R15">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S15">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T15">
         <v>1.01</v>
@@ -4737,7 +4737,7 @@
         <v>1.01</v>
       </c>
       <c r="W15">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4928,22 +4928,22 @@
         <v>249</v>
       </c>
       <c r="F16">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="G16">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="H16">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I16">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J16">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K16">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L16">
         <v>1.39</v>
@@ -4952,70 +4952,70 @@
         <v>1.07</v>
       </c>
       <c r="N16">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O16">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P16">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="Q16">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R16">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S16">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="T16">
+        <v>1.97</v>
+      </c>
+      <c r="U16">
         <v>1.94</v>
-      </c>
-      <c r="U16">
-        <v>1.93</v>
       </c>
       <c r="V16">
         <v>1.21</v>
       </c>
       <c r="W16">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="X16">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y16">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Z16">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="AB16">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AC16">
         <v>9</v>
       </c>
       <c r="AD16">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AF16">
         <v>10</v>
       </c>
       <c r="AG16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH16">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AJ16">
         <v>22</v>
@@ -5024,19 +5024,19 @@
         <v>21</v>
       </c>
       <c r="AL16">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="AN16">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AP16">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ16">
         <v>13.5</v>
@@ -5048,13 +5048,13 @@
         <v>42</v>
       </c>
       <c r="AT16">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU16">
         <v>7.6</v>
       </c>
       <c r="AV16">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AW16">
         <v>34</v>
@@ -5063,91 +5063,91 @@
         <v>8.4</v>
       </c>
       <c r="AY16">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ16">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA16">
         <v>40</v>
       </c>
       <c r="BB16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC16">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE16">
         <v>42</v>
       </c>
       <c r="BF16">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BG16">
         <v>38</v>
       </c>
       <c r="BH16">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="BI16">
-        <v>1.61</v>
+        <v>2.76</v>
       </c>
       <c r="BJ16">
         <v>970</v>
       </c>
       <c r="BK16">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="BN16">
         <v>970</v>
       </c>
       <c r="BO16">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="BP16">
-        <v>730</v>
+        <v>620</v>
       </c>
       <c r="BQ16">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="BT16">
         <v>970</v>
       </c>
       <c r="BU16">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="BZ16">
         <v>1000</v>
       </c>
       <c r="CA16">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="CB16" t="s">
         <v>310</v>
@@ -5170,34 +5170,34 @@
         <v>250</v>
       </c>
       <c r="F17">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="G17">
-        <v>110</v>
+        <v>13.5</v>
       </c>
       <c r="H17">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="I17">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="J17">
+        <v>5.8</v>
+      </c>
+      <c r="K17">
+        <v>7</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.03</v>
+      </c>
+      <c r="N17">
         <v>5</v>
       </c>
-      <c r="K17">
-        <v>110</v>
-      </c>
-      <c r="L17">
-        <v>1.01</v>
-      </c>
-      <c r="M17">
-        <v>1.01</v>
-      </c>
-      <c r="N17">
-        <v>2.68</v>
-      </c>
       <c r="O17">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P17">
         <v>2.54</v>
@@ -5206,100 +5206,100 @@
         <v>1.52</v>
       </c>
       <c r="R17">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="S17">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T17">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="U17">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="V17">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y17">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z17">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AA17">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AB17">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AC17">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD17">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE17">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AF17">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AG17">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AH17">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI17">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ17">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK17">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AL17">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM17">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN17">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AO17">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="AP17">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AQ17">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AR17">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AS17">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AU17">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW17">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AX17">
         <v>1.01</v>
@@ -5308,7 +5308,7 @@
         <v>1.01</v>
       </c>
       <c r="AZ17">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA17">
         <v>1.01</v>
@@ -5329,7 +5329,7 @@
         <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5415,7 +5415,7 @@
         <v>1.81</v>
       </c>
       <c r="G18">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="H18">
         <v>3.2</v>
@@ -5424,31 +5424,31 @@
         <v>5.3</v>
       </c>
       <c r="J18">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K18">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M18">
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>2.82</v>
+        <v>4</v>
       </c>
       <c r="O18">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P18">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q18">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R18">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S18">
         <v>2.58</v>
@@ -5463,7 +5463,7 @@
         <v>1.23</v>
       </c>
       <c r="W18">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5657,7 +5657,7 @@
         <v>2.52</v>
       </c>
       <c r="G19">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H19">
         <v>2.74</v>
@@ -5666,13 +5666,13 @@
         <v>3.2</v>
       </c>
       <c r="J19">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="K19">
         <v>3.75</v>
       </c>
       <c r="L19">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="M19">
         <v>1.07</v>
@@ -5687,16 +5687,16 @@
         <v>1.81</v>
       </c>
       <c r="Q19">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R19">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="S19">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T19">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U19">
         <v>2.06</v>
@@ -5705,7 +5705,7 @@
         <v>1.45</v>
       </c>
       <c r="W19">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X19">
         <v>16</v>
@@ -5762,37 +5762,37 @@
         <v>46</v>
       </c>
       <c r="AP19">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AQ19">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR19">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AS19">
         <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU19">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV19">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW19">
         <v>1.01</v>
       </c>
       <c r="AX19">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY19">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ19">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA19">
         <v>1.01</v>
@@ -5810,67 +5810,67 @@
         <v>1.01</v>
       </c>
       <c r="BF19">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BG19">
         <v>1.01</v>
       </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI19">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK19">
         <v>1.01</v>
       </c>
       <c r="BL19">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM19">
         <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO19">
         <v>1.01</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ19">
         <v>1.01</v>
       </c>
       <c r="BR19">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS19">
         <v>1.01</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU19">
         <v>1.01</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW19">
         <v>1.01</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY19">
         <v>1.01</v>
       </c>
       <c r="BZ19">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA19">
         <v>1.01</v>
@@ -6138,61 +6138,61 @@
         <v>254</v>
       </c>
       <c r="F21">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="G21">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H21">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="I21">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="J21">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K21">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L21">
         <v>1.01</v>
       </c>
       <c r="M21">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N21">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O21">
         <v>1.34</v>
       </c>
       <c r="P21">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q21">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R21">
         <v>1.28</v>
       </c>
       <c r="S21">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T21">
         <v>1.78</v>
       </c>
       <c r="U21">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="V21">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W21">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X21">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y21">
         <v>970</v>
@@ -6386,7 +6386,7 @@
         <v>2.24</v>
       </c>
       <c r="H22">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I22">
         <v>4.8</v>
@@ -6395,10 +6395,10 @@
         <v>3.2</v>
       </c>
       <c r="K22">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M22">
         <v>1.01</v>
@@ -6628,13 +6628,13 @@
         <v>1.36</v>
       </c>
       <c r="H23">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="I23">
         <v>1000</v>
       </c>
       <c r="J23">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K23">
         <v>930</v>
@@ -6646,7 +6646,7 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="O23">
         <v>1.23</v>
@@ -6655,10 +6655,10 @@
         <v>2.04</v>
       </c>
       <c r="Q23">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="R23">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="S23">
         <v>2.66</v>
@@ -6673,7 +6673,7 @@
         <v>1.01</v>
       </c>
       <c r="W23">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6870,7 +6870,7 @@
         <v>1.26</v>
       </c>
       <c r="H24">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I24">
         <v>18.5</v>
@@ -6903,7 +6903,7 @@
         <v>1.53</v>
       </c>
       <c r="S24">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T24">
         <v>2.52</v>
@@ -6921,7 +6921,7 @@
         <v>22</v>
       </c>
       <c r="Y24">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Z24">
         <v>200</v>
@@ -6972,10 +6972,10 @@
         <v>520</v>
       </c>
       <c r="AP24">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ24">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AR24">
         <v>46</v>
@@ -6996,7 +6996,7 @@
         <v>100</v>
       </c>
       <c r="AX24">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY24">
         <v>10.5</v>
@@ -7011,7 +7011,7 @@
         <v>7.6</v>
       </c>
       <c r="BC24">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD24">
         <v>42</v>
@@ -7032,10 +7032,10 @@
         <v>3.3</v>
       </c>
       <c r="BJ24">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BK24">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BL24">
         <v>1000</v>
@@ -7044,28 +7044,28 @@
         <v>36</v>
       </c>
       <c r="BN24">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="BO24">
         <v>2.96</v>
       </c>
       <c r="BP24">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="BQ24">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BR24">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS24">
         <v>12</v>
       </c>
       <c r="BT24">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BU24">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BV24">
         <v>1000</v>
@@ -7112,16 +7112,16 @@
         <v>6.6</v>
       </c>
       <c r="H25">
+        <v>1.59</v>
+      </c>
+      <c r="I25">
         <v>1.6</v>
       </c>
-      <c r="I25">
-        <v>1.61</v>
-      </c>
       <c r="J25">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K25">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L25">
         <v>1.38</v>
@@ -7130,7 +7130,7 @@
         <v>1.05</v>
       </c>
       <c r="N25">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O25">
         <v>1.27</v>
@@ -7154,13 +7154,13 @@
         <v>2.04</v>
       </c>
       <c r="V25">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="W25">
         <v>1.18</v>
       </c>
       <c r="X25">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y25">
         <v>9.199999999999999</v>
@@ -7244,7 +7244,7 @@
         <v>21</v>
       </c>
       <c r="AZ25">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA25">
         <v>30</v>
@@ -7348,112 +7348,112 @@
         <v>259</v>
       </c>
       <c r="F26">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="G26">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="H26">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="I26">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="J26">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="K26">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="L26">
         <v>1.01</v>
       </c>
       <c r="M26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N26">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="O26">
         <v>1.16</v>
       </c>
       <c r="P26">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q26">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="R26">
+        <v>1.64</v>
+      </c>
+      <c r="S26">
+        <v>2.2</v>
+      </c>
+      <c r="T26">
         <v>1.6</v>
       </c>
-      <c r="S26">
-        <v>2.12</v>
-      </c>
-      <c r="T26">
-        <v>1.01</v>
-      </c>
       <c r="U26">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="V26">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="W26">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X26">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y26">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z26">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA26">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AB26">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC26">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD26">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE26">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AF26">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG26">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AH26">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI26">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AJ26">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK26">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL26">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM26">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN26">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO26">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AP26">
         <v>1.01</v>
@@ -7596,7 +7596,7 @@
         <v>2</v>
       </c>
       <c r="H27">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I27">
         <v>5.3</v>
@@ -7835,16 +7835,16 @@
         <v>2.14</v>
       </c>
       <c r="G28">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="H28">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I28">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="J28">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="K28">
         <v>3.55</v>
@@ -7862,10 +7862,10 @@
         <v>1.39</v>
       </c>
       <c r="P28">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q28">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R28">
         <v>1.23</v>
@@ -7880,10 +7880,10 @@
         <v>1.95</v>
       </c>
       <c r="V28">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W28">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="X28">
         <v>22</v>
@@ -7994,7 +7994,7 @@
         <v>1.01</v>
       </c>
       <c r="BH28">
-        <v>3.45</v>
+        <v>970</v>
       </c>
       <c r="BI28">
         <v>1.01</v>
@@ -8074,22 +8074,22 @@
         <v>262</v>
       </c>
       <c r="F29">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="G29">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="H29">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="I29">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="J29">
         <v>4.5</v>
       </c>
       <c r="K29">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L29">
         <v>1.35</v>
@@ -8098,31 +8098,31 @@
         <v>1.05</v>
       </c>
       <c r="N29">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O29">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P29">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q29">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="R29">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S29">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="T29">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U29">
         <v>2.04</v>
       </c>
       <c r="V29">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="W29">
         <v>1.16</v>
@@ -8155,7 +8155,7 @@
         <v>65</v>
       </c>
       <c r="AG29">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AH29">
         <v>22</v>
@@ -8188,10 +8188,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR29">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AS29">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AT29">
         <v>19</v>
@@ -8206,7 +8206,7 @@
         <v>14</v>
       </c>
       <c r="AX29">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AY29">
         <v>20</v>
@@ -8215,13 +8215,13 @@
         <v>17.5</v>
       </c>
       <c r="BA29">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BB29">
+        <v>11</v>
+      </c>
+      <c r="BC29">
         <v>10.5</v>
-      </c>
-      <c r="BC29">
-        <v>10</v>
       </c>
       <c r="BD29">
         <v>10</v>
@@ -8230,7 +8230,7 @@
         <v>10.5</v>
       </c>
       <c r="BF29">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG29">
         <v>7</v>
@@ -8254,7 +8254,7 @@
         <v>1.01</v>
       </c>
       <c r="BN29">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BO29">
         <v>1.01</v>
@@ -8319,19 +8319,19 @@
         <v>1.5</v>
       </c>
       <c r="G30">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="H30">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I30">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J30">
         <v>4.5</v>
       </c>
       <c r="K30">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8346,7 +8346,7 @@
         <v>1.26</v>
       </c>
       <c r="P30">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q30">
         <v>1.79</v>
@@ -8358,28 +8358,28 @@
         <v>2.84</v>
       </c>
       <c r="T30">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U30">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V30">
         <v>1.13</v>
       </c>
       <c r="W30">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="X30">
         <v>22</v>
       </c>
       <c r="Y30">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z30">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AA30">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AB30">
         <v>9.199999999999999</v>
@@ -8388,7 +8388,7 @@
         <v>11</v>
       </c>
       <c r="AD30">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE30">
         <v>130</v>
@@ -8397,7 +8397,7 @@
         <v>9.4</v>
       </c>
       <c r="AG30">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH30">
         <v>27</v>
@@ -8418,7 +8418,7 @@
         <v>140</v>
       </c>
       <c r="AN30">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AO30">
         <v>150</v>
@@ -8430,10 +8430,10 @@
         <v>19.5</v>
       </c>
       <c r="AR30">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS30">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT30">
         <v>7.8</v>
@@ -8442,22 +8442,22 @@
         <v>9.6</v>
       </c>
       <c r="AV30">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AW30">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AX30">
         <v>8.199999999999999</v>
       </c>
       <c r="AY30">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ30">
         <v>18</v>
       </c>
       <c r="BA30">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB30">
         <v>11.5</v>
@@ -8466,16 +8466,16 @@
         <v>13</v>
       </c>
       <c r="BD30">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE30">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF30">
         <v>6.2</v>
       </c>
       <c r="BG30">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8484,7 +8484,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ30">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK30">
         <v>1.01</v>
@@ -8496,43 +8496,43 @@
         <v>1.01</v>
       </c>
       <c r="BN30">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO30">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BP30">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ30">
         <v>1.01</v>
       </c>
       <c r="BR30">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS30">
         <v>1.01</v>
       </c>
       <c r="BT30">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BU30">
         <v>1.01</v>
       </c>
       <c r="BV30">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BW30">
         <v>1.01</v>
       </c>
       <c r="BX30">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY30">
         <v>1.01</v>
       </c>
       <c r="BZ30">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA30">
         <v>1.01</v>
@@ -8561,19 +8561,19 @@
         <v>2.92</v>
       </c>
       <c r="G31">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H31">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="I31">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J31">
         <v>3.55</v>
       </c>
       <c r="K31">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L31">
         <v>1.31</v>
@@ -8591,16 +8591,16 @@
         <v>2.1</v>
       </c>
       <c r="Q31">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R31">
         <v>1.43</v>
       </c>
       <c r="S31">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="T31">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U31">
         <v>2.28</v>
@@ -8609,13 +8609,13 @@
         <v>1.64</v>
       </c>
       <c r="W31">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X31">
         <v>21</v>
       </c>
       <c r="Y31">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="Z31">
         <v>21</v>
@@ -8633,7 +8633,7 @@
         <v>14.5</v>
       </c>
       <c r="AE31">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AF31">
         <v>23</v>
@@ -8696,7 +8696,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ31">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA31">
         <v>1.01</v>
@@ -8723,61 +8723,61 @@
         <v>970</v>
       </c>
       <c r="BI31">
-        <v>1.15</v>
+        <v>1.95</v>
       </c>
       <c r="BJ31">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK31">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>1.16</v>
+        <v>1.96</v>
       </c>
       <c r="BN31">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BO31">
-        <v>1.58</v>
+        <v>5.1</v>
       </c>
       <c r="BP31">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ31">
-        <v>1.16</v>
+        <v>1.84</v>
       </c>
       <c r="BR31">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS31">
-        <v>1.16</v>
+        <v>1.87</v>
       </c>
       <c r="BT31">
-        <v>970</v>
+        <v>6.6</v>
       </c>
       <c r="BU31">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="BV31">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW31">
-        <v>1.16</v>
+        <v>1.81</v>
       </c>
       <c r="BX31">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY31">
-        <v>1.16</v>
+        <v>1.86</v>
       </c>
       <c r="BZ31">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA31">
-        <v>1.16</v>
+        <v>1.84</v>
       </c>
       <c r="CB31" t="s">
         <v>310</v>
@@ -8803,19 +8803,19 @@
         <v>2.3</v>
       </c>
       <c r="G32">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="H32">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="I32">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J32">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K32">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L32">
         <v>1.01</v>
@@ -8824,40 +8824,40 @@
         <v>1.05</v>
       </c>
       <c r="N32">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="O32">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P32">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q32">
         <v>1.68</v>
       </c>
       <c r="R32">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S32">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="T32">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="U32">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="V32">
         <v>1.44</v>
       </c>
       <c r="W32">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="X32">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y32">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Z32">
         <v>24</v>
@@ -8866,10 +8866,10 @@
         <v>55</v>
       </c>
       <c r="AB32">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC32">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD32">
         <v>14</v>
@@ -8878,7 +8878,7 @@
         <v>34</v>
       </c>
       <c r="AF32">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG32">
         <v>12</v>
@@ -8890,7 +8890,7 @@
         <v>40</v>
       </c>
       <c r="AJ32">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK32">
         <v>25</v>
@@ -8905,7 +8905,7 @@
         <v>16.5</v>
       </c>
       <c r="AO32">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AP32">
         <v>15.5</v>
@@ -8938,7 +8938,7 @@
         <v>10</v>
       </c>
       <c r="AZ32">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA32">
         <v>1.01</v>
@@ -9051,7 +9051,7 @@
         <v>7.8</v>
       </c>
       <c r="I33">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J33">
         <v>4.9</v>
@@ -9060,13 +9060,13 @@
         <v>5.4</v>
       </c>
       <c r="L33">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="M33">
         <v>1.04</v>
       </c>
       <c r="N33">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O33">
         <v>1.2</v>
@@ -9090,7 +9090,7 @@
         <v>2.1</v>
       </c>
       <c r="V33">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W33">
         <v>3.05</v>
@@ -9099,7 +9099,7 @@
         <v>26</v>
       </c>
       <c r="Y33">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z33">
         <v>80</v>
@@ -9114,7 +9114,7 @@
         <v>12</v>
       </c>
       <c r="AD33">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE33">
         <v>120</v>
@@ -9126,7 +9126,7 @@
         <v>10.5</v>
       </c>
       <c r="AH33">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI33">
         <v>100</v>
@@ -9153,7 +9153,7 @@
         <v>21</v>
       </c>
       <c r="AQ33">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="AR33">
         <v>11.5</v>
@@ -9168,7 +9168,7 @@
         <v>10.5</v>
       </c>
       <c r="AV33">
-        <v>9.4</v>
+        <v>25</v>
       </c>
       <c r="AW33">
         <v>12</v>
@@ -9192,7 +9192,7 @@
         <v>12.5</v>
       </c>
       <c r="BD33">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="BE33">
         <v>12</v>
@@ -9204,64 +9204,64 @@
         <v>12</v>
       </c>
       <c r="BH33">
-        <v>970</v>
+        <v>4.3</v>
       </c>
       <c r="BI33">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BJ33">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="BK33">
-        <v>2.12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL33">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM33">
-        <v>2.38</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN33">
-        <v>970</v>
+        <v>4.1</v>
       </c>
       <c r="BO33">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="BP33">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="BQ33">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="BR33">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS33">
-        <v>2.38</v>
+        <v>7.6</v>
       </c>
       <c r="BT33">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="BU33">
-        <v>2.2</v>
+        <v>10</v>
       </c>
       <c r="BV33">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW33">
-        <v>2.38</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX33">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY33">
-        <v>2.38</v>
+        <v>9</v>
       </c>
       <c r="BZ33">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA33">
-        <v>2.38</v>
+        <v>6.2</v>
       </c>
       <c r="CB33" t="s">
         <v>310</v>
@@ -9290,25 +9290,25 @@
         <v>4.1</v>
       </c>
       <c r="H34">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I34">
         <v>2.46</v>
       </c>
       <c r="J34">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K34">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L34">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M34">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N34">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="O34">
         <v>1.39</v>
@@ -9317,133 +9317,133 @@
         <v>1.72</v>
       </c>
       <c r="Q34">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="R34">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="S34">
-        <v>2.78</v>
+        <v>4</v>
       </c>
       <c r="T34">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U34">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V34">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W34">
         <v>1.32</v>
       </c>
       <c r="X34">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y34">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z34">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA34">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB34">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC34">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD34">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE34">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF34">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG34">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH34">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI34">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ34">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK34">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AL34">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM34">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN34">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO34">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP34">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AQ34">
-        <v>1.29</v>
+        <v>3.2</v>
       </c>
       <c r="AR34">
-        <v>1.32</v>
+        <v>3.7</v>
       </c>
       <c r="AS34">
-        <v>1.38</v>
+        <v>4.2</v>
       </c>
       <c r="AT34">
-        <v>1.31</v>
+        <v>3.55</v>
       </c>
       <c r="AU34">
-        <v>1.23</v>
+        <v>3.1</v>
       </c>
       <c r="AV34">
-        <v>1.31</v>
+        <v>3.5</v>
       </c>
       <c r="AW34">
-        <v>1.38</v>
+        <v>4.1</v>
       </c>
       <c r="AX34">
-        <v>1.29</v>
+        <v>4.1</v>
       </c>
       <c r="AY34">
-        <v>1.32</v>
+        <v>3.75</v>
       </c>
       <c r="AZ34">
-        <v>1.33</v>
+        <v>3.95</v>
       </c>
       <c r="BA34">
-        <v>1.38</v>
+        <v>4.3</v>
       </c>
       <c r="BB34">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC34">
-        <v>1.38</v>
+        <v>4.3</v>
       </c>
       <c r="BD34">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE34">
-        <v>1.35</v>
+        <v>4.6</v>
       </c>
       <c r="BF34">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG34">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9526,31 +9526,31 @@
         <v>268</v>
       </c>
       <c r="F35">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="G35">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H35">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="I35">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="J35">
+        <v>3.15</v>
+      </c>
+      <c r="K35">
+        <v>4.2</v>
+      </c>
+      <c r="L35">
+        <v>1.45</v>
+      </c>
+      <c r="M35">
+        <v>1.08</v>
+      </c>
+      <c r="N35">
         <v>3.35</v>
-      </c>
-      <c r="K35">
-        <v>4.3</v>
-      </c>
-      <c r="L35">
-        <v>1.4</v>
-      </c>
-      <c r="M35">
-        <v>1.06</v>
-      </c>
-      <c r="N35">
-        <v>3.3</v>
       </c>
       <c r="O35">
         <v>1.36</v>
@@ -9559,7 +9559,7 @@
         <v>1.72</v>
       </c>
       <c r="Q35">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R35">
         <v>1.27</v>
@@ -9574,13 +9574,13 @@
         <v>1.87</v>
       </c>
       <c r="V35">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="W35">
         <v>1.25</v>
       </c>
       <c r="X35">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y35">
         <v>970</v>
@@ -9727,7 +9727,7 @@
         <v>970</v>
       </c>
       <c r="BU35">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="BV35">
         <v>1000</v>
@@ -9768,16 +9768,16 @@
         <v>269</v>
       </c>
       <c r="F36">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G36">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="H36">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="I36">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J36">
         <v>4.4</v>
@@ -9810,22 +9810,22 @@
         <v>2.6</v>
       </c>
       <c r="T36">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U36">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V36">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W36">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="X36">
         <v>23</v>
       </c>
       <c r="Y36">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z36">
         <v>55</v>
@@ -9834,16 +9834,16 @@
         <v>160</v>
       </c>
       <c r="AB36">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC36">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD36">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE36">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AF36">
         <v>11.5</v>
@@ -9858,13 +9858,13 @@
         <v>75</v>
       </c>
       <c r="AJ36">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK36">
         <v>16.5</v>
       </c>
       <c r="AL36">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM36">
         <v>100</v>
@@ -9882,52 +9882,52 @@
         <v>20</v>
       </c>
       <c r="AR36">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AS36">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="AT36">
+        <v>9.4</v>
+      </c>
+      <c r="AU36">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV36">
+        <v>19</v>
+      </c>
+      <c r="AW36">
+        <v>26</v>
+      </c>
+      <c r="AX36">
         <v>9.6</v>
-      </c>
-      <c r="AU36">
-        <v>9.4</v>
-      </c>
-      <c r="AV36">
-        <v>18.5</v>
-      </c>
-      <c r="AW36">
-        <v>25</v>
-      </c>
-      <c r="AX36">
-        <v>9.800000000000001</v>
       </c>
       <c r="AY36">
         <v>9</v>
       </c>
       <c r="AZ36">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA36">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB36">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC36">
         <v>13.5</v>
       </c>
       <c r="BD36">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BE36">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BF36">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG36">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH36">
         <v>4.2</v>
@@ -9945,7 +9945,7 @@
         <v>120</v>
       </c>
       <c r="BM36">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BN36">
         <v>4.5</v>
@@ -9957,16 +9957,16 @@
         <v>10</v>
       </c>
       <c r="BQ36">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BR36">
         <v>25</v>
       </c>
       <c r="BS36">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BT36">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BU36">
         <v>8.199999999999999</v>
@@ -9975,19 +9975,19 @@
         <v>50</v>
       </c>
       <c r="BW36">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX36">
         <v>55</v>
       </c>
       <c r="BY36">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ36">
         <v>17</v>
       </c>
       <c r="CA36">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="CB36" t="s">
         <v>310</v>
@@ -10016,7 +10016,7 @@
         <v>2.6</v>
       </c>
       <c r="H37">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="I37">
         <v>3.1</v>
@@ -10169,7 +10169,7 @@
         <v>13.5</v>
       </c>
       <c r="BG37">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BH37">
         <v>970</v>
@@ -10178,7 +10178,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ37">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK37">
         <v>6.4</v>
@@ -10196,37 +10196,37 @@
         <v>1.01</v>
       </c>
       <c r="BP37">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ37">
         <v>1.01</v>
       </c>
       <c r="BR37">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS37">
         <v>1.01</v>
       </c>
       <c r="BT37">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU37">
         <v>1.01</v>
       </c>
       <c r="BV37">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW37">
         <v>1.01</v>
       </c>
       <c r="BX37">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY37">
         <v>1.01</v>
       </c>
       <c r="BZ37">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA37">
         <v>1.01</v>
@@ -10270,13 +10270,13 @@
         <v>10.5</v>
       </c>
       <c r="L38">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="M38">
         <v>1.01</v>
       </c>
       <c r="N38">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="O38">
         <v>1.09</v>
@@ -10285,22 +10285,22 @@
         <v>4.1</v>
       </c>
       <c r="Q38">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="R38">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="S38">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="T38">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U38">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V38">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W38">
         <v>6</v>
@@ -10309,7 +10309,7 @@
         <v>1000</v>
       </c>
       <c r="Y38">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="Z38">
         <v>1000</v>
@@ -10324,7 +10324,7 @@
         <v>27</v>
       </c>
       <c r="AD38">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AE38">
         <v>1000</v>
@@ -10333,7 +10333,7 @@
         <v>11.5</v>
       </c>
       <c r="AG38">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH38">
         <v>80</v>
@@ -10348,13 +10348,13 @@
         <v>13</v>
       </c>
       <c r="AL38">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM38">
         <v>1000</v>
       </c>
       <c r="AN38">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="AO38">
         <v>1000</v>
@@ -10363,19 +10363,19 @@
         <v>44</v>
       </c>
       <c r="AQ38">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AR38">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AS38">
         <v>75</v>
       </c>
       <c r="AT38">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU38">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV38">
         <v>30</v>
@@ -10384,16 +10384,16 @@
         <v>46</v>
       </c>
       <c r="AX38">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AY38">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ38">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BA38">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="BB38">
         <v>9.4</v>
@@ -10402,13 +10402,13 @@
         <v>11.5</v>
       </c>
       <c r="BD38">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE38">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="BF38">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="BG38">
         <v>44</v>
@@ -10494,58 +10494,58 @@
         <v>272</v>
       </c>
       <c r="F39">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G39">
         <v>4.8</v>
       </c>
       <c r="H39">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="I39">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="J39">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K39">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L39">
         <v>1.01</v>
       </c>
       <c r="M39">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N39">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O39">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P39">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q39">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R39">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S39">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="T39">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="U39">
         <v>2.24</v>
       </c>
       <c r="V39">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="W39">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X39">
         <v>1000</v>
@@ -10736,46 +10736,46 @@
         <v>273</v>
       </c>
       <c r="F40">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="G40">
+        <v>1.82</v>
+      </c>
+      <c r="H40">
+        <v>4.4</v>
+      </c>
+      <c r="I40">
+        <v>7.4</v>
+      </c>
+      <c r="J40">
+        <v>3.6</v>
+      </c>
+      <c r="K40">
+        <v>6.4</v>
+      </c>
+      <c r="L40">
+        <v>1.01</v>
+      </c>
+      <c r="M40">
+        <v>1.01</v>
+      </c>
+      <c r="N40">
+        <v>3.05</v>
+      </c>
+      <c r="O40">
+        <v>1.01</v>
+      </c>
+      <c r="P40">
         <v>1.84</v>
       </c>
-      <c r="H40">
-        <v>4.2</v>
-      </c>
-      <c r="I40">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J40">
-        <v>3.55</v>
-      </c>
-      <c r="K40">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L40">
-        <v>1.32</v>
-      </c>
-      <c r="M40">
-        <v>1.01</v>
-      </c>
-      <c r="N40">
-        <v>3.2</v>
-      </c>
-      <c r="O40">
-        <v>1.01</v>
-      </c>
-      <c r="P40">
+      <c r="Q40">
         <v>1.9</v>
       </c>
-      <c r="Q40">
-        <v>1.83</v>
-      </c>
       <c r="R40">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S40">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="T40">
         <v>1.01</v>
@@ -10784,7 +10784,7 @@
         <v>1.01</v>
       </c>
       <c r="V40">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="W40">
         <v>2.2</v>
@@ -10978,7 +10978,7 @@
         <v>274</v>
       </c>
       <c r="F41">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G41">
         <v>2.86</v>
@@ -11113,7 +11113,7 @@
         <v>14</v>
       </c>
       <c r="AY41">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ41">
         <v>18</v>
@@ -11143,22 +11143,22 @@
         <v>970</v>
       </c>
       <c r="BI41">
-        <v>1.44</v>
+        <v>1.86</v>
       </c>
       <c r="BJ41">
         <v>15</v>
       </c>
       <c r="BK41">
-        <v>2.34</v>
+        <v>1.66</v>
       </c>
       <c r="BL41">
         <v>1000</v>
       </c>
       <c r="BM41">
-        <v>1.44</v>
+        <v>1.86</v>
       </c>
       <c r="BN41">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO41">
         <v>3.9</v>
@@ -11167,37 +11167,37 @@
         <v>34</v>
       </c>
       <c r="BQ41">
-        <v>1.38</v>
+        <v>1.77</v>
       </c>
       <c r="BR41">
         <v>60</v>
       </c>
       <c r="BS41">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="BT41">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BU41">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="BV41">
         <v>38</v>
       </c>
       <c r="BW41">
-        <v>1.39</v>
+        <v>1.78</v>
       </c>
       <c r="BX41">
         <v>65</v>
       </c>
       <c r="BY41">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="BZ41">
         <v>65</v>
       </c>
       <c r="CA41">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="CB41" t="s">
         <v>310</v>
@@ -11220,10 +11220,10 @@
         <v>275</v>
       </c>
       <c r="F42">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G42">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H42">
         <v>4.2</v>
@@ -11232,10 +11232,10 @@
         <v>4.5</v>
       </c>
       <c r="J42">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K42">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L42">
         <v>1.27</v>
@@ -11259,13 +11259,13 @@
         <v>1.53</v>
       </c>
       <c r="S42">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T42">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U42">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V42">
         <v>1.29</v>
@@ -11274,7 +11274,7 @@
         <v>2.04</v>
       </c>
       <c r="X42">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y42">
         <v>75</v>
@@ -11286,34 +11286,34 @@
         <v>1000</v>
       </c>
       <c r="AB42">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AC42">
         <v>970</v>
       </c>
       <c r="AD42">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AE42">
         <v>150</v>
       </c>
       <c r="AF42">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AG42">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH42">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AI42">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ42">
         <v>85</v>
       </c>
       <c r="AK42">
-        <v>29</v>
+        <v>970</v>
       </c>
       <c r="AL42">
         <v>95</v>
@@ -11328,16 +11328,16 @@
         <v>1000</v>
       </c>
       <c r="AP42">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ42">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR42">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS42">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT42">
         <v>10</v>
@@ -11361,10 +11361,10 @@
         <v>11.5</v>
       </c>
       <c r="BA42">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB42">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC42">
         <v>13.5</v>
@@ -11373,13 +11373,13 @@
         <v>7.2</v>
       </c>
       <c r="BE42">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BF42">
         <v>6.4</v>
       </c>
       <c r="BG42">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BH42">
         <v>970</v>
@@ -11471,139 +11471,139 @@
         <v>1.67</v>
       </c>
       <c r="I43">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="J43">
         <v>3.9</v>
       </c>
       <c r="K43">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L43">
         <v>1.01</v>
       </c>
       <c r="M43">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N43">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="O43">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P43">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q43">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="R43">
         <v>1.43</v>
       </c>
       <c r="S43">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="T43">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U43">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V43">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="W43">
         <v>1.2</v>
       </c>
       <c r="X43">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y43">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z43">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AA43">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AB43">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC43">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD43">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE43">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AF43">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG43">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH43">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI43">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ43">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK43">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL43">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM43">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN43">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO43">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP43">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AQ43">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AR43">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AS43">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AT43">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AU43">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV43">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW43">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AX43">
         <v>1.01</v>
       </c>
       <c r="AY43">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AZ43">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB43">
         <v>1.01</v>
@@ -11621,7 +11621,7 @@
         <v>1.01</v>
       </c>
       <c r="BG43">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH43">
         <v>1000</v>
@@ -11716,10 +11716,10 @@
         <v>3</v>
       </c>
       <c r="J44">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K44">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L44">
         <v>1.01</v>
@@ -11728,22 +11728,22 @@
         <v>1.04</v>
       </c>
       <c r="N44">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O44">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P44">
         <v>2.3</v>
       </c>
       <c r="Q44">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="R44">
         <v>1.53</v>
       </c>
       <c r="S44">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T44">
         <v>1.56</v>
@@ -11779,7 +11779,7 @@
         <v>13.5</v>
       </c>
       <c r="AE44">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AF44">
         <v>21</v>
@@ -11812,7 +11812,7 @@
         <v>19</v>
       </c>
       <c r="AP44">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ44">
         <v>13</v>
@@ -11863,7 +11863,7 @@
         <v>13</v>
       </c>
       <c r="BG44">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BH44">
         <v>1000</v>
@@ -11946,7 +11946,7 @@
         <v>278</v>
       </c>
       <c r="F45">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G45">
         <v>2.02</v>
@@ -11958,7 +11958,7 @@
         <v>4.5</v>
       </c>
       <c r="J45">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K45">
         <v>3.85</v>
@@ -11970,25 +11970,25 @@
         <v>1.07</v>
       </c>
       <c r="N45">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O45">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P45">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q45">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="R45">
         <v>1.37</v>
       </c>
       <c r="S45">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T45">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U45">
         <v>2.1</v>
@@ -12000,7 +12000,7 @@
         <v>1.98</v>
       </c>
       <c r="X45">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y45">
         <v>16</v>
@@ -12015,7 +12015,7 @@
         <v>10.5</v>
       </c>
       <c r="AC45">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD45">
         <v>17.5</v>
@@ -12075,19 +12075,19 @@
         <v>15</v>
       </c>
       <c r="AW45">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AX45">
         <v>11</v>
       </c>
       <c r="AY45">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ45">
         <v>16</v>
       </c>
       <c r="BA45">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BB45">
         <v>16.5</v>
@@ -12105,67 +12105,67 @@
         <v>12</v>
       </c>
       <c r="BG45">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BH45">
         <v>1000</v>
       </c>
       <c r="BI45">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BJ45">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK45">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BL45">
         <v>1000</v>
       </c>
       <c r="BM45">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BN45">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO45">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BP45">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ45">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BR45">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS45">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BT45">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU45">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV45">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW45">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BX45">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY45">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BZ45">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA45">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="CB45" t="s">
         <v>310</v>
@@ -12191,7 +12191,7 @@
         <v>2.16</v>
       </c>
       <c r="G46">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="H46">
         <v>2.74</v>
@@ -12200,7 +12200,7 @@
         <v>3.55</v>
       </c>
       <c r="J46">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K46">
         <v>5.7</v>
@@ -12212,10 +12212,10 @@
         <v>1.01</v>
       </c>
       <c r="N46">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O46">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="P46">
         <v>1.81</v>
@@ -12227,7 +12227,7 @@
         <v>1.27</v>
       </c>
       <c r="S46">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T46">
         <v>1.01</v>
@@ -12239,7 +12239,7 @@
         <v>1.39</v>
       </c>
       <c r="W46">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="X46">
         <v>1000</v>
@@ -12430,22 +12430,22 @@
         <v>280</v>
       </c>
       <c r="F47">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="G47">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H47">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I47">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J47">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K47">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L47">
         <v>1.01</v>
@@ -12454,121 +12454,121 @@
         <v>1.04</v>
       </c>
       <c r="N47">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="O47">
         <v>1.2</v>
       </c>
       <c r="P47">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="Q47">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="R47">
+        <v>1.6</v>
+      </c>
+      <c r="S47">
+        <v>2.38</v>
+      </c>
+      <c r="T47">
         <v>1.51</v>
       </c>
-      <c r="S47">
-        <v>2.46</v>
-      </c>
-      <c r="T47">
-        <v>1.58</v>
-      </c>
       <c r="U47">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="V47">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W47">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X47">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y47">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z47">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA47">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB47">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC47">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AD47">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE47">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF47">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG47">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AH47">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI47">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ47">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK47">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL47">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM47">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN47">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO47">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP47">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AQ47">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AR47">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AS47">
         <v>1.01</v>
       </c>
       <c r="AT47">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AU47">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV47">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW47">
         <v>1.01</v>
       </c>
       <c r="AX47">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AY47">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ47">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA47">
         <v>1.01</v>
@@ -12577,19 +12577,19 @@
         <v>1.01</v>
       </c>
       <c r="BC47">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD47">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE47">
         <v>1.01</v>
       </c>
       <c r="BF47">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG47">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BH47">
         <v>1000</v>
@@ -12681,7 +12681,7 @@
         <v>17</v>
       </c>
       <c r="I48">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J48">
         <v>7</v>
@@ -12690,7 +12690,7 @@
         <v>8</v>
       </c>
       <c r="L48">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M48">
         <v>1.04</v>
@@ -12705,10 +12705,10 @@
         <v>2.48</v>
       </c>
       <c r="Q48">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="R48">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S48">
         <v>2.48</v>
@@ -12741,7 +12741,7 @@
         <v>9</v>
       </c>
       <c r="AC48">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AD48">
         <v>75</v>
@@ -12941,139 +12941,139 @@
         <v>3.6</v>
       </c>
       <c r="O49">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P49">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q49">
         <v>2.04</v>
       </c>
       <c r="R49">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S49">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="T49">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="U49">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V49">
         <v>1.59</v>
       </c>
       <c r="W49">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X49">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Y49">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Z49">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AA49">
-        <v>140</v>
+        <v>48</v>
       </c>
       <c r="AB49">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AC49">
+        <v>7.6</v>
+      </c>
+      <c r="AD49">
+        <v>12.5</v>
+      </c>
+      <c r="AE49">
+        <v>32</v>
+      </c>
+      <c r="AF49">
+        <v>21</v>
+      </c>
+      <c r="AG49">
+        <v>14</v>
+      </c>
+      <c r="AH49">
+        <v>18</v>
+      </c>
+      <c r="AI49">
+        <v>60</v>
+      </c>
+      <c r="AJ49">
+        <v>70</v>
+      </c>
+      <c r="AK49">
+        <v>40</v>
+      </c>
+      <c r="AL49">
+        <v>65</v>
+      </c>
+      <c r="AM49">
+        <v>1000</v>
+      </c>
+      <c r="AN49">
+        <v>36</v>
+      </c>
+      <c r="AO49">
+        <v>27</v>
+      </c>
+      <c r="AP49">
+        <v>11.5</v>
+      </c>
+      <c r="AQ49">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR49">
+        <v>14.5</v>
+      </c>
+      <c r="AS49">
+        <v>7.4</v>
+      </c>
+      <c r="AT49">
         <v>10</v>
       </c>
-      <c r="AD49">
-        <v>13.5</v>
-      </c>
-      <c r="AE49">
-        <v>1000</v>
-      </c>
-      <c r="AF49">
-        <v>1000</v>
-      </c>
-      <c r="AG49">
-        <v>970</v>
-      </c>
-      <c r="AH49">
-        <v>970</v>
-      </c>
-      <c r="AI49">
-        <v>1000</v>
-      </c>
-      <c r="AJ49">
-        <v>1000</v>
-      </c>
-      <c r="AK49">
-        <v>1000</v>
-      </c>
-      <c r="AL49">
-        <v>1000</v>
-      </c>
-      <c r="AM49">
-        <v>1000</v>
-      </c>
-      <c r="AN49">
-        <v>1000</v>
-      </c>
-      <c r="AO49">
-        <v>1000</v>
-      </c>
-      <c r="AP49">
-        <v>9</v>
-      </c>
-      <c r="AQ49">
+      <c r="AU49">
+        <v>7</v>
+      </c>
+      <c r="AV49">
+        <v>10.5</v>
+      </c>
+      <c r="AW49">
+        <v>20</v>
+      </c>
+      <c r="AX49">
+        <v>17</v>
+      </c>
+      <c r="AY49">
+        <v>11.5</v>
+      </c>
+      <c r="AZ49">
+        <v>15</v>
+      </c>
+      <c r="BA49">
+        <v>7.6</v>
+      </c>
+      <c r="BB49">
         <v>8</v>
       </c>
-      <c r="AR49">
-        <v>10.5</v>
-      </c>
-      <c r="AS49">
-        <v>1.68</v>
-      </c>
-      <c r="AT49">
-        <v>8.4</v>
-      </c>
-      <c r="AU49">
-        <v>5.7</v>
-      </c>
-      <c r="AV49">
-        <v>8.4</v>
-      </c>
-      <c r="AW49">
-        <v>1.7</v>
-      </c>
-      <c r="AX49">
-        <v>11.5</v>
-      </c>
-      <c r="AY49">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ49">
-        <v>10.5</v>
-      </c>
-      <c r="BA49">
-        <v>1.7</v>
-      </c>
-      <c r="BB49">
-        <v>1.7</v>
-      </c>
       <c r="BC49">
-        <v>1.7</v>
+        <v>7.2</v>
       </c>
       <c r="BD49">
-        <v>1.7</v>
+        <v>8</v>
       </c>
       <c r="BE49">
-        <v>1.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF49">
-        <v>1.7</v>
+        <v>7.2</v>
       </c>
       <c r="BG49">
-        <v>1.7</v>
+        <v>19.5</v>
       </c>
       <c r="BH49">
         <v>970</v>
@@ -13401,7 +13401,7 @@
         <v>2.22</v>
       </c>
       <c r="G51">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H51">
         <v>2.76</v>
@@ -13434,7 +13434,7 @@
         <v>1.43</v>
       </c>
       <c r="R51">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="S51">
         <v>2.08</v>
@@ -13449,7 +13449,7 @@
         <v>1.45</v>
       </c>
       <c r="W51">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X51">
         <v>1000</v>
@@ -13643,13 +13643,13 @@
         <v>2.62</v>
       </c>
       <c r="G52">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="H52">
         <v>2.24</v>
       </c>
       <c r="I52">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="J52">
         <v>4.5</v>
@@ -13664,34 +13664,34 @@
         <v>1.02</v>
       </c>
       <c r="N52">
-        <v>3.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O52">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="P52">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="Q52">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="R52">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="S52">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="T52">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="U52">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="V52">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="W52">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="X52">
         <v>1000</v>
@@ -13882,7 +13882,7 @@
         <v>286</v>
       </c>
       <c r="F53">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="G53">
         <v>1.51</v>
@@ -13903,25 +13903,25 @@
         <v>1.3</v>
       </c>
       <c r="M53">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N53">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O53">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P53">
         <v>2.2</v>
       </c>
       <c r="Q53">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="R53">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="S53">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="T53">
         <v>1.92</v>
@@ -14124,7 +14124,7 @@
         <v>287</v>
       </c>
       <c r="F54">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="G54">
         <v>3.85</v>
@@ -14133,28 +14133,28 @@
         <v>2.32</v>
       </c>
       <c r="I54">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J54">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K54">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L54">
         <v>1.48</v>
       </c>
       <c r="M54">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N54">
         <v>3.1</v>
       </c>
       <c r="O54">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P54">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -14163,7 +14163,7 @@
         <v>1.23</v>
       </c>
       <c r="S54">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="T54">
         <v>1.81</v>
@@ -14172,127 +14172,127 @@
         <v>1.89</v>
       </c>
       <c r="V54">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="W54">
         <v>1.35</v>
       </c>
       <c r="X54">
+        <v>11.5</v>
+      </c>
+      <c r="Y54">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z54">
+        <v>14.5</v>
+      </c>
+      <c r="AA54">
+        <v>34</v>
+      </c>
+      <c r="AB54">
+        <v>12.5</v>
+      </c>
+      <c r="AC54">
+        <v>7.4</v>
+      </c>
+      <c r="AD54">
         <v>12</v>
       </c>
-      <c r="Y54">
+      <c r="AE54">
+        <v>30</v>
+      </c>
+      <c r="AF54">
+        <v>26</v>
+      </c>
+      <c r="AG54">
+        <v>16</v>
+      </c>
+      <c r="AH54">
+        <v>20</v>
+      </c>
+      <c r="AI54">
+        <v>110</v>
+      </c>
+      <c r="AJ54">
+        <v>90</v>
+      </c>
+      <c r="AK54">
+        <v>60</v>
+      </c>
+      <c r="AL54">
+        <v>75</v>
+      </c>
+      <c r="AM54">
+        <v>150</v>
+      </c>
+      <c r="AN54">
+        <v>70</v>
+      </c>
+      <c r="AO54">
+        <v>25</v>
+      </c>
+      <c r="AP54">
+        <v>9.6</v>
+      </c>
+      <c r="AQ54">
+        <v>8</v>
+      </c>
+      <c r="AR54">
+        <v>12</v>
+      </c>
+      <c r="AS54">
+        <v>11.5</v>
+      </c>
+      <c r="AT54">
+        <v>10.5</v>
+      </c>
+      <c r="AU54">
+        <v>6.4</v>
+      </c>
+      <c r="AV54">
+        <v>10</v>
+      </c>
+      <c r="AW54">
+        <v>10</v>
+      </c>
+      <c r="AX54">
+        <v>20</v>
+      </c>
+      <c r="AY54">
         <v>13.5</v>
       </c>
-      <c r="Z54">
-        <v>23</v>
-      </c>
-      <c r="AA54">
-        <v>1000</v>
-      </c>
-      <c r="AB54">
-        <v>19.5</v>
-      </c>
-      <c r="AC54">
-        <v>7.6</v>
-      </c>
-      <c r="AD54">
+      <c r="AZ54">
+        <v>16.5</v>
+      </c>
+      <c r="BA54">
         <v>17</v>
       </c>
-      <c r="AE54">
-        <v>1000</v>
-      </c>
-      <c r="AF54">
-        <v>85</v>
-      </c>
-      <c r="AG54">
-        <v>34</v>
-      </c>
-      <c r="AH54">
-        <v>80</v>
-      </c>
-      <c r="AI54">
-        <v>1000</v>
-      </c>
-      <c r="AJ54">
-        <v>1000</v>
-      </c>
-      <c r="AK54">
-        <v>1000</v>
-      </c>
-      <c r="AL54">
-        <v>1000</v>
-      </c>
-      <c r="AM54">
-        <v>1000</v>
-      </c>
-      <c r="AN54">
-        <v>1000</v>
-      </c>
-      <c r="AO54">
-        <v>1000</v>
-      </c>
-      <c r="AP54">
-        <v>8.4</v>
-      </c>
-      <c r="AQ54">
-        <v>7.6</v>
-      </c>
-      <c r="AR54">
-        <v>10</v>
-      </c>
-      <c r="AS54">
-        <v>13</v>
-      </c>
-      <c r="AT54">
-        <v>10</v>
-      </c>
-      <c r="AU54">
-        <v>5.5</v>
-      </c>
-      <c r="AV54">
-        <v>9.4</v>
-      </c>
-      <c r="AW54">
-        <v>12</v>
-      </c>
-      <c r="AX54">
-        <v>5.3</v>
-      </c>
-      <c r="AY54">
-        <v>12</v>
-      </c>
-      <c r="AZ54">
-        <v>13</v>
-      </c>
-      <c r="BA54">
-        <v>18.5</v>
-      </c>
       <c r="BB54">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BC54">
+        <v>17</v>
+      </c>
+      <c r="BD54">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE54">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF54">
+        <v>9</v>
+      </c>
+      <c r="BG54">
         <v>18</v>
       </c>
-      <c r="BD54">
-        <v>20</v>
-      </c>
-      <c r="BE54">
-        <v>2.02</v>
-      </c>
-      <c r="BF54">
-        <v>2.02</v>
-      </c>
-      <c r="BG54">
-        <v>2.02</v>
-      </c>
       <c r="BH54">
-        <v>3.35</v>
+        <v>970</v>
       </c>
       <c r="BI54">
         <v>1.01</v>
       </c>
       <c r="BJ54">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="BK54">
         <v>1.01</v>
@@ -14304,7 +14304,7 @@
         <v>1.01</v>
       </c>
       <c r="BN54">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="BO54">
         <v>1.01</v>
@@ -14322,7 +14322,7 @@
         <v>1.01</v>
       </c>
       <c r="BT54">
-        <v>6.2</v>
+        <v>970</v>
       </c>
       <c r="BU54">
         <v>1.01</v>
@@ -14366,19 +14366,19 @@
         <v>288</v>
       </c>
       <c r="F55">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="G55">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="H55">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="I55">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="J55">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K55">
         <v>3.85</v>
@@ -14390,28 +14390,28 @@
         <v>1.05</v>
       </c>
       <c r="N55">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O55">
         <v>1.24</v>
       </c>
       <c r="P55">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q55">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="R55">
         <v>1.47</v>
       </c>
       <c r="S55">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="T55">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="U55">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="V55">
         <v>1.6</v>
@@ -14531,13 +14531,13 @@
         <v>970</v>
       </c>
       <c r="BI55">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BJ55">
         <v>1000</v>
       </c>
       <c r="BK55">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BL55">
         <v>1000</v>
@@ -14549,7 +14549,7 @@
         <v>970</v>
       </c>
       <c r="BO55">
-        <v>1.16</v>
+        <v>1.6</v>
       </c>
       <c r="BP55">
         <v>1000</v>
@@ -14567,7 +14567,7 @@
         <v>970</v>
       </c>
       <c r="BU55">
-        <v>1.12</v>
+        <v>1.57</v>
       </c>
       <c r="BV55">
         <v>1000</v>
@@ -14611,13 +14611,13 @@
         <v>1.28</v>
       </c>
       <c r="G56">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H56">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I56">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="J56">
         <v>6.6</v>
@@ -14659,7 +14659,7 @@
         <v>1.07</v>
       </c>
       <c r="W56">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="X56">
         <v>27</v>
@@ -14722,7 +14722,7 @@
         <v>40</v>
       </c>
       <c r="AR56">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AS56">
         <v>55</v>
@@ -14734,7 +14734,7 @@
         <v>13.5</v>
       </c>
       <c r="AV56">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AW56">
         <v>48</v>
@@ -14850,61 +14850,61 @@
         <v>290</v>
       </c>
       <c r="F57">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G57">
         <v>3.6</v>
       </c>
       <c r="H57">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="I57">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="J57">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K57">
         <v>3.9</v>
       </c>
       <c r="L57">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M57">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N57">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="O57">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="P57">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="Q57">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="R57">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="S57">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="T57">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="U57">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="V57">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W57">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X57">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Y57">
         <v>22</v>
@@ -14916,7 +14916,7 @@
         <v>1000</v>
       </c>
       <c r="AB57">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AC57">
         <v>970</v>
@@ -14934,7 +14934,7 @@
         <v>46</v>
       </c>
       <c r="AH57">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AI57">
         <v>1000</v>
@@ -14955,7 +14955,7 @@
         <v>1000</v>
       </c>
       <c r="AO57">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP57">
         <v>1.01</v>
@@ -15092,40 +15092,40 @@
         <v>291</v>
       </c>
       <c r="F58">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G58">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="H58">
+        <v>4.5</v>
+      </c>
+      <c r="I58">
+        <v>5</v>
+      </c>
+      <c r="J58">
+        <v>3.55</v>
+      </c>
+      <c r="K58">
         <v>4.4</v>
-      </c>
-      <c r="I58">
-        <v>5.2</v>
-      </c>
-      <c r="J58">
-        <v>3.35</v>
-      </c>
-      <c r="K58">
-        <v>4.6</v>
       </c>
       <c r="L58">
         <v>1.37</v>
       </c>
       <c r="M58">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N58">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O58">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P58">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="Q58">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R58">
         <v>1.32</v>
@@ -15134,25 +15134,25 @@
         <v>3.35</v>
       </c>
       <c r="T58">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="U58">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="V58">
         <v>1.25</v>
       </c>
       <c r="W58">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X58">
-        <v>34</v>
+        <v>17.5</v>
       </c>
       <c r="Y58">
         <v>85</v>
       </c>
       <c r="Z58">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA58">
         <v>1000</v>
@@ -15161,157 +15161,157 @@
         <v>970</v>
       </c>
       <c r="AC58">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AD58">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE58">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF58">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AG58">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AH58">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI58">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ58">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK58">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL58">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM58">
         <v>1000</v>
       </c>
       <c r="AN58">
+        <v>14</v>
+      </c>
+      <c r="AO58">
+        <v>100</v>
+      </c>
+      <c r="AP58">
+        <v>12</v>
+      </c>
+      <c r="AQ58">
+        <v>14.5</v>
+      </c>
+      <c r="AR58">
+        <v>22</v>
+      </c>
+      <c r="AS58">
+        <v>1.01</v>
+      </c>
+      <c r="AT58">
+        <v>8</v>
+      </c>
+      <c r="AU58">
+        <v>7.8</v>
+      </c>
+      <c r="AV58">
+        <v>16</v>
+      </c>
+      <c r="AW58">
+        <v>1.01</v>
+      </c>
+      <c r="AX58">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY58">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ58">
+        <v>16.5</v>
+      </c>
+      <c r="BA58">
+        <v>1.01</v>
+      </c>
+      <c r="BB58">
+        <v>17.5</v>
+      </c>
+      <c r="BC58">
+        <v>18</v>
+      </c>
+      <c r="BD58">
         <v>23</v>
       </c>
-      <c r="AO58">
-        <v>1000</v>
-      </c>
-      <c r="AP58">
-        <v>7.8</v>
-      </c>
-      <c r="AQ58">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR58">
-        <v>1.01</v>
-      </c>
-      <c r="AS58">
-        <v>1.01</v>
-      </c>
-      <c r="AT58">
-        <v>6.4</v>
-      </c>
-      <c r="AU58">
-        <v>6.4</v>
-      </c>
-      <c r="AV58">
-        <v>9.6</v>
-      </c>
-      <c r="AW58">
-        <v>1.01</v>
-      </c>
-      <c r="AX58">
-        <v>1.01</v>
-      </c>
-      <c r="AY58">
-        <v>1.01</v>
-      </c>
-      <c r="AZ58">
-        <v>1.01</v>
-      </c>
-      <c r="BA58">
-        <v>1.01</v>
-      </c>
-      <c r="BB58">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC58">
-        <v>9.6</v>
-      </c>
-      <c r="BD58">
-        <v>1.01</v>
-      </c>
       <c r="BE58">
         <v>1.01</v>
       </c>
       <c r="BF58">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG58">
         <v>1.01</v>
       </c>
       <c r="BH58">
-        <v>970</v>
+        <v>3.6</v>
       </c>
       <c r="BI58">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BJ58">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK58">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BL58">
         <v>1000</v>
       </c>
       <c r="BM58">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BN58">
         <v>970</v>
       </c>
       <c r="BO58">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BP58">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ58">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BR58">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS58">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BT58">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU58">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BV58">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW58">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BX58">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY58">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BZ58">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA58">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="CB58" t="s">
         <v>310</v>
@@ -15337,19 +15337,19 @@
         <v>2.4</v>
       </c>
       <c r="G59">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H59">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="I59">
         <v>3.25</v>
       </c>
       <c r="J59">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K59">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L59">
         <v>1.37</v>
@@ -15358,28 +15358,28 @@
         <v>1.07</v>
       </c>
       <c r="N59">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="O59">
         <v>1.32</v>
       </c>
       <c r="P59">
+        <v>1.87</v>
+      </c>
+      <c r="Q59">
         <v>1.91</v>
       </c>
-      <c r="Q59">
-        <v>1.95</v>
-      </c>
       <c r="R59">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S59">
         <v>3.3</v>
       </c>
       <c r="T59">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="U59">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V59">
         <v>1.45</v>
@@ -15388,10 +15388,10 @@
         <v>1.64</v>
       </c>
       <c r="X59">
+        <v>15.5</v>
+      </c>
+      <c r="Y59">
         <v>970</v>
-      </c>
-      <c r="Y59">
-        <v>18.5</v>
       </c>
       <c r="Z59">
         <v>80</v>
@@ -15403,10 +15403,10 @@
         <v>970</v>
       </c>
       <c r="AC59">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD59">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="AE59">
         <v>1000</v>
@@ -15415,7 +15415,7 @@
         <v>60</v>
       </c>
       <c r="AG59">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AH59">
         <v>80</v>
@@ -15442,58 +15442,58 @@
         <v>1000</v>
       </c>
       <c r="AP59">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ59">
-        <v>1.51</v>
+        <v>9.4</v>
       </c>
       <c r="AR59">
-        <v>12.5</v>
+        <v>1.82</v>
       </c>
       <c r="AS59">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AT59">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU59">
         <v>6.2</v>
       </c>
       <c r="AV59">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="AW59">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AX59">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AY59">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AZ59">
-        <v>1.62</v>
+        <v>5.3</v>
       </c>
       <c r="BA59">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BB59">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BC59">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BD59">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BE59">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="BF59">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="BG59">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="BH59">
         <v>970</v>
@@ -15594,13 +15594,13 @@
         <v>4.6</v>
       </c>
       <c r="L60">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M60">
         <v>1.01</v>
       </c>
       <c r="N60">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O60">
         <v>1.25</v>
@@ -15612,7 +15612,7 @@
         <v>1.78</v>
       </c>
       <c r="R60">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S60">
         <v>2.92</v>
@@ -15624,7 +15624,7 @@
         <v>1.01</v>
       </c>
       <c r="V60">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W60">
         <v>1.37</v>
@@ -15818,16 +15818,16 @@
         <v>294</v>
       </c>
       <c r="F61">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="G61">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H61">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I61">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J61">
         <v>3.65</v>
@@ -15848,10 +15848,10 @@
         <v>1.28</v>
       </c>
       <c r="P61">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q61">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R61">
         <v>1.44</v>
@@ -15866,10 +15866,10 @@
         <v>2.38</v>
       </c>
       <c r="V61">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W61">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X61">
         <v>16.5</v>
@@ -15890,7 +15890,7 @@
         <v>8</v>
       </c>
       <c r="AD61">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE61">
         <v>34</v>
@@ -15905,7 +15905,7 @@
         <v>15.5</v>
       </c>
       <c r="AI61">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AJ61">
         <v>34</v>
@@ -15926,7 +15926,7 @@
         <v>28</v>
       </c>
       <c r="AP61">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ61">
         <v>13</v>
@@ -15980,64 +15980,64 @@
         <v>25</v>
       </c>
       <c r="BH61">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="BI61">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="BJ61">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK61">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BL61">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM61">
         <v>24</v>
       </c>
       <c r="BN61">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO61">
         <v>4.9</v>
       </c>
       <c r="BP61">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ61">
-        <v>2.6</v>
+        <v>15</v>
       </c>
       <c r="BR61">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS61">
         <v>11.5</v>
       </c>
       <c r="BT61">
-        <v>970</v>
+        <v>6.4</v>
       </c>
       <c r="BU61">
         <v>5.9</v>
       </c>
       <c r="BV61">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW61">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX61">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY61">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ61">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA61">
-        <v>2.6</v>
+        <v>10.5</v>
       </c>
       <c r="CB61" t="s">
         <v>310</v>
@@ -16066,10 +16066,10 @@
         <v>2</v>
       </c>
       <c r="H62">
+        <v>3.8</v>
+      </c>
+      <c r="I62">
         <v>3.9</v>
-      </c>
-      <c r="I62">
-        <v>3.95</v>
       </c>
       <c r="J62">
         <v>4.1</v>
@@ -16090,16 +16090,16 @@
         <v>1.21</v>
       </c>
       <c r="P62">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q62">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="R62">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S62">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="T62">
         <v>1.59</v>
@@ -16117,7 +16117,7 @@
         <v>24</v>
       </c>
       <c r="Y62">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z62">
         <v>32</v>
@@ -16126,7 +16126,7 @@
         <v>75</v>
       </c>
       <c r="AB62">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC62">
         <v>9.6</v>
@@ -16138,7 +16138,7 @@
         <v>40</v>
       </c>
       <c r="AF62">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG62">
         <v>10.5</v>
@@ -16192,13 +16192,13 @@
         <v>34</v>
       </c>
       <c r="AX62">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY62">
         <v>9.6</v>
       </c>
       <c r="AZ62">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA62">
         <v>36</v>
@@ -16207,7 +16207,7 @@
         <v>21</v>
       </c>
       <c r="BC62">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD62">
         <v>24</v>
@@ -16216,7 +16216,7 @@
         <v>50</v>
       </c>
       <c r="BF62">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG62">
         <v>25</v>
@@ -16225,61 +16225,61 @@
         <v>4.8</v>
       </c>
       <c r="BI62">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ62">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="BK62">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL62">
         <v>1000</v>
       </c>
       <c r="BM62">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN62">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BO62">
         <v>4</v>
       </c>
       <c r="BP62">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="BQ62">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BR62">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS62">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BT62">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU62">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV62">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW62">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BX62">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY62">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BZ62">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA62">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB62" t="s">
         <v>310</v>
@@ -16314,13 +16314,13 @@
         <v>110</v>
       </c>
       <c r="J63">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="K63">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L63">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="M63">
         <v>1.01</v>
@@ -16338,7 +16338,7 @@
         <v>1.22</v>
       </c>
       <c r="R63">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="S63">
         <v>1.61</v>
@@ -16547,13 +16547,13 @@
         <v>2.52</v>
       </c>
       <c r="G64">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H64">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I64">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J64">
         <v>3.15</v>
@@ -16562,7 +16562,7 @@
         <v>3.3</v>
       </c>
       <c r="L64">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M64">
         <v>1.1</v>
@@ -16574,7 +16574,7 @@
         <v>1.45</v>
       </c>
       <c r="P64">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q64">
         <v>2.32</v>
@@ -16595,7 +16595,7 @@
         <v>1.42</v>
       </c>
       <c r="W64">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X64">
         <v>10.5</v>
@@ -16610,31 +16610,31 @@
         <v>70</v>
       </c>
       <c r="AB64">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC64">
         <v>7.4</v>
       </c>
       <c r="AD64">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AE64">
         <v>55</v>
       </c>
       <c r="AF64">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG64">
         <v>12.5</v>
       </c>
       <c r="AH64">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI64">
         <v>75</v>
       </c>
       <c r="AJ64">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AK64">
         <v>40</v>
@@ -16649,7 +16649,7 @@
         <v>36</v>
       </c>
       <c r="AO64">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP64">
         <v>9</v>
@@ -16661,7 +16661,7 @@
         <v>18.5</v>
       </c>
       <c r="AS64">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT64">
         <v>7.8</v>
@@ -16673,37 +16673,37 @@
         <v>12.5</v>
       </c>
       <c r="AW64">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX64">
         <v>14</v>
       </c>
       <c r="AY64">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ64">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA64">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB64">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC64">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BD64">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE64">
+        <v>10</v>
+      </c>
+      <c r="BF64">
         <v>8</v>
       </c>
-      <c r="BE64">
+      <c r="BG64">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BF64">
-        <v>7.4</v>
-      </c>
-      <c r="BG64">
-        <v>8</v>
       </c>
       <c r="BH64">
         <v>970</v>
@@ -16789,13 +16789,13 @@
         <v>1.48</v>
       </c>
       <c r="G65">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="H65">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="I65">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J65">
         <v>4.7</v>
@@ -16810,13 +16810,13 @@
         <v>1.05</v>
       </c>
       <c r="N65">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O65">
         <v>1.26</v>
       </c>
       <c r="P65">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q65">
         <v>1.78</v>
@@ -16825,7 +16825,7 @@
         <v>1.46</v>
       </c>
       <c r="S65">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T65">
         <v>1.97</v>
@@ -16837,13 +16837,13 @@
         <v>1.13</v>
       </c>
       <c r="W65">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="X65">
         <v>22</v>
       </c>
       <c r="Y65">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z65">
         <v>90</v>
@@ -16870,7 +16870,7 @@
         <v>10.5</v>
       </c>
       <c r="AH65">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI65">
         <v>120</v>
@@ -16900,10 +16900,10 @@
         <v>20</v>
       </c>
       <c r="AR65">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AS65">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT65">
         <v>7.6</v>
@@ -16912,10 +16912,10 @@
         <v>9.6</v>
       </c>
       <c r="AV65">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AW65">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AX65">
         <v>7.8</v>
@@ -16927,7 +16927,7 @@
         <v>20</v>
       </c>
       <c r="BA65">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB65">
         <v>11.5</v>
@@ -16936,34 +16936,34 @@
         <v>13</v>
       </c>
       <c r="BD65">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE65">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BF65">
         <v>6.2</v>
       </c>
       <c r="BG65">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH65">
         <v>4.7</v>
       </c>
       <c r="BI65">
-        <v>1.44</v>
+        <v>2.18</v>
       </c>
       <c r="BJ65">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK65">
-        <v>2.16</v>
+        <v>3.4</v>
       </c>
       <c r="BL65">
         <v>1000</v>
       </c>
       <c r="BM65">
-        <v>1.97</v>
+        <v>3.6</v>
       </c>
       <c r="BN65">
         <v>5.2</v>
@@ -16975,37 +16975,37 @@
         <v>970</v>
       </c>
       <c r="BQ65">
-        <v>1.82</v>
+        <v>3.1</v>
       </c>
       <c r="BR65">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS65">
-        <v>1.97</v>
+        <v>3.3</v>
       </c>
       <c r="BT65">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BU65">
-        <v>2.16</v>
+        <v>3.4</v>
       </c>
       <c r="BV65">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BW65">
-        <v>2.16</v>
+        <v>3.55</v>
       </c>
       <c r="BX65">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BY65">
-        <v>2.16</v>
+        <v>3.55</v>
       </c>
       <c r="BZ65">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA65">
-        <v>1.97</v>
+        <v>3.65</v>
       </c>
       <c r="CB65" t="s">
         <v>310</v>
@@ -17028,34 +17028,34 @@
         <v>299</v>
       </c>
       <c r="F66">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G66">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H66">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="I66">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J66">
         <v>2.96</v>
       </c>
       <c r="K66">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="L66">
         <v>1.01</v>
       </c>
       <c r="M66">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N66">
         <v>2.52</v>
       </c>
       <c r="O66">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="P66">
         <v>1.46</v>
@@ -17064,82 +17064,82 @@
         <v>2.56</v>
       </c>
       <c r="R66">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="S66">
-        <v>3.05</v>
+        <v>5.4</v>
       </c>
       <c r="T66">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U66">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="V66">
         <v>1.26</v>
       </c>
       <c r="W66">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X66">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y66">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z66">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA66">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB66">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC66">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD66">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE66">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF66">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG66">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH66">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI66">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ66">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK66">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL66">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM66">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN66">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO66">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP66">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ66">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AR66">
         <v>1.01</v>
@@ -17148,25 +17148,25 @@
         <v>1.01</v>
       </c>
       <c r="AT66">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU66">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AV66">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW66">
         <v>1.01</v>
       </c>
       <c r="AX66">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AY66">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ66">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA66">
         <v>1.01</v>
@@ -17270,10 +17270,10 @@
         <v>300</v>
       </c>
       <c r="F67">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="G67">
-        <v>140</v>
+        <v>880</v>
       </c>
       <c r="H67">
         <v>1.11</v>
@@ -17294,7 +17294,7 @@
         <v>1.01</v>
       </c>
       <c r="N67">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="O67">
         <v>1.01</v>
@@ -17318,10 +17318,10 @@
         <v>1.01</v>
       </c>
       <c r="V67">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W67">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X67">
         <v>1000</v>
@@ -17512,16 +17512,16 @@
         <v>301</v>
       </c>
       <c r="F68">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G68">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="H68">
         <v>3.55</v>
       </c>
       <c r="I68">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J68">
         <v>2.92</v>
@@ -17533,7 +17533,7 @@
         <v>1.64</v>
       </c>
       <c r="M68">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N68">
         <v>2.38</v>
@@ -17542,7 +17542,7 @@
         <v>1.67</v>
       </c>
       <c r="P68">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -17551,28 +17551,28 @@
         <v>1.15</v>
       </c>
       <c r="S68">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="T68">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="U68">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V68">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W68">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="X68">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y68">
         <v>9</v>
       </c>
       <c r="Z68">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA68">
         <v>1000</v>
@@ -17581,55 +17581,55 @@
         <v>7</v>
       </c>
       <c r="AC68">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD68">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE68">
         <v>1000</v>
       </c>
       <c r="AF68">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG68">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH68">
+        <v>29</v>
+      </c>
+      <c r="AI68">
+        <v>1000</v>
+      </c>
+      <c r="AJ68">
         <v>44</v>
       </c>
-      <c r="AI68">
-        <v>1000</v>
-      </c>
-      <c r="AJ68">
-        <v>48</v>
-      </c>
       <c r="AK68">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="AL68">
         <v>1000</v>
       </c>
       <c r="AM68">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AN68">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="AO68">
         <v>1000</v>
       </c>
       <c r="AP68">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ68">
         <v>8</v>
       </c>
       <c r="AR68">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AS68">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AT68">
         <v>6.4</v>
@@ -17641,34 +17641,34 @@
         <v>15.5</v>
       </c>
       <c r="AW68">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AX68">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY68">
         <v>12.5</v>
       </c>
       <c r="AZ68">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BA68">
         <v>40</v>
       </c>
       <c r="BB68">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC68">
         <v>24</v>
       </c>
       <c r="BD68">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="BE68">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="BF68">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BG68">
         <v>38</v>
@@ -17760,7 +17760,7 @@
         <v>3.5</v>
       </c>
       <c r="H69">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I69">
         <v>2.9</v>
@@ -17769,7 +17769,7 @@
         <v>2.76</v>
       </c>
       <c r="K69">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="L69">
         <v>1.72</v>
@@ -17781,25 +17781,25 @@
         <v>2.22</v>
       </c>
       <c r="O69">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="P69">
         <v>1.38</v>
       </c>
       <c r="Q69">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R69">
         <v>1.13</v>
       </c>
       <c r="S69">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="T69">
         <v>2.56</v>
       </c>
       <c r="U69">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V69">
         <v>1.53</v>
@@ -17829,7 +17829,7 @@
         <v>17</v>
       </c>
       <c r="AE69">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AF69">
         <v>24</v>
@@ -17841,28 +17841,28 @@
         <v>36</v>
       </c>
       <c r="AI69">
-        <v>950</v>
+        <v>910</v>
       </c>
       <c r="AJ69">
-        <v>830</v>
+        <v>790</v>
       </c>
       <c r="AK69">
-        <v>830</v>
+        <v>790</v>
       </c>
       <c r="AL69">
-        <v>950</v>
+        <v>910</v>
       </c>
       <c r="AM69">
-        <v>870</v>
+        <v>760</v>
       </c>
       <c r="AN69">
-        <v>950</v>
+        <v>910</v>
       </c>
       <c r="AO69">
-        <v>820</v>
+        <v>780</v>
       </c>
       <c r="AP69">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AQ69">
         <v>6.4</v>
@@ -17919,61 +17919,61 @@
         <v>2.42</v>
       </c>
       <c r="BI69">
-        <v>2.02</v>
+        <v>1.36</v>
       </c>
       <c r="BJ69">
         <v>1000</v>
       </c>
       <c r="BK69">
-        <v>8.800000000000001</v>
+        <v>1.33</v>
       </c>
       <c r="BL69">
         <v>1000</v>
       </c>
       <c r="BM69">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BN69">
         <v>9.199999999999999</v>
       </c>
       <c r="BO69">
-        <v>4.8</v>
+        <v>1.17</v>
       </c>
       <c r="BP69">
         <v>1000</v>
       </c>
       <c r="BQ69">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BR69">
         <v>1000</v>
       </c>
       <c r="BS69">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BT69">
         <v>7.2</v>
       </c>
       <c r="BU69">
-        <v>4.6</v>
+        <v>2.18</v>
       </c>
       <c r="BV69">
         <v>1000</v>
       </c>
       <c r="BW69">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BX69">
         <v>1000</v>
       </c>
       <c r="BY69">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BZ69">
         <v>1000</v>
       </c>
       <c r="CA69">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="CB69" t="s">
         <v>310</v>
@@ -17996,19 +17996,19 @@
         <v>303</v>
       </c>
       <c r="F70">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="G70">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="H70">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I70">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="J70">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K70">
         <v>3.65</v>
@@ -18017,145 +18017,145 @@
         <v>1.4</v>
       </c>
       <c r="M70">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N70">
         <v>3.55</v>
       </c>
       <c r="O70">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="P70">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q70">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R70">
         <v>1.32</v>
       </c>
       <c r="S70">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T70">
         <v>1.87</v>
       </c>
       <c r="U70">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V70">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="W70">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X70">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="Y70">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z70">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA70">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB70">
         <v>13.5</v>
       </c>
       <c r="AC70">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD70">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE70">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AF70">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG70">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH70">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AI70">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AJ70">
-        <v>980</v>
+        <v>940</v>
       </c>
       <c r="AK70">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="AL70">
-        <v>830</v>
+        <v>510</v>
       </c>
       <c r="AM70">
-        <v>980</v>
+        <v>940</v>
       </c>
       <c r="AN70">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="AO70">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AP70">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ70">
         <v>8.4</v>
       </c>
       <c r="AR70">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS70">
+        <v>18</v>
+      </c>
+      <c r="AT70">
+        <v>10</v>
+      </c>
+      <c r="AU70">
+        <v>7</v>
+      </c>
+      <c r="AV70">
+        <v>10.5</v>
+      </c>
+      <c r="AW70">
         <v>17</v>
       </c>
-      <c r="AT70">
-        <v>11.5</v>
-      </c>
-      <c r="AU70">
-        <v>7.2</v>
-      </c>
-      <c r="AV70">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW70">
-        <v>16</v>
-      </c>
       <c r="AX70">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY70">
         <v>13</v>
       </c>
       <c r="AZ70">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA70">
+        <v>26</v>
+      </c>
+      <c r="BB70">
+        <v>32</v>
+      </c>
+      <c r="BC70">
         <v>25</v>
       </c>
-      <c r="BB70">
-        <v>34</v>
-      </c>
-      <c r="BC70">
-        <v>26</v>
-      </c>
       <c r="BD70">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE70">
         <v>40</v>
       </c>
       <c r="BF70">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BG70">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BH70">
         <v>970</v>
@@ -18241,7 +18241,7 @@
         <v>1.1</v>
       </c>
       <c r="G71">
-        <v>1000</v>
+        <v>2.62</v>
       </c>
       <c r="H71">
         <v>3</v>
@@ -18262,7 +18262,7 @@
         <v>1.08</v>
       </c>
       <c r="N71">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="O71">
         <v>1.35</v>
@@ -18271,10 +18271,10 @@
         <v>1.79</v>
       </c>
       <c r="Q71">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R71">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S71">
         <v>3.4</v>
@@ -18289,7 +18289,7 @@
         <v>1.4</v>
       </c>
       <c r="W71">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="X71">
         <v>1000</v>
@@ -18480,13 +18480,13 @@
         <v>305</v>
       </c>
       <c r="F72">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G72">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H72">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I72">
         <v>4.3</v>
@@ -18504,16 +18504,16 @@
         <v>1.09</v>
       </c>
       <c r="N72">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="O72">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="P72">
         <v>1.48</v>
       </c>
       <c r="Q72">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R72">
         <v>1.18</v>
@@ -18534,112 +18534,112 @@
         <v>1.64</v>
       </c>
       <c r="X72">
+        <v>8.4</v>
+      </c>
+      <c r="Y72">
+        <v>10</v>
+      </c>
+      <c r="Z72">
+        <v>29</v>
+      </c>
+      <c r="AA72">
+        <v>100</v>
+      </c>
+      <c r="AB72">
+        <v>7.4</v>
+      </c>
+      <c r="AC72">
+        <v>7.2</v>
+      </c>
+      <c r="AD72">
+        <v>19.5</v>
+      </c>
+      <c r="AE72">
+        <v>75</v>
+      </c>
+      <c r="AF72">
+        <v>14</v>
+      </c>
+      <c r="AG72">
+        <v>12.5</v>
+      </c>
+      <c r="AH72">
+        <v>27</v>
+      </c>
+      <c r="AI72">
+        <v>100</v>
+      </c>
+      <c r="AJ72">
+        <v>44</v>
+      </c>
+      <c r="AK72">
+        <v>42</v>
+      </c>
+      <c r="AL72">
+        <v>75</v>
+      </c>
+      <c r="AM72">
+        <v>220</v>
+      </c>
+      <c r="AN72">
+        <v>44</v>
+      </c>
+      <c r="AO72">
+        <v>110</v>
+      </c>
+      <c r="AP72">
+        <v>7.6</v>
+      </c>
+      <c r="AQ72">
+        <v>9</v>
+      </c>
+      <c r="AR72">
+        <v>21</v>
+      </c>
+      <c r="AS72">
+        <v>9.4</v>
+      </c>
+      <c r="AT72">
+        <v>6.6</v>
+      </c>
+      <c r="AU72">
+        <v>6.4</v>
+      </c>
+      <c r="AV72">
+        <v>14.5</v>
+      </c>
+      <c r="AW72">
+        <v>9</v>
+      </c>
+      <c r="AX72">
+        <v>12.5</v>
+      </c>
+      <c r="AY72">
         <v>11</v>
       </c>
-      <c r="Y72">
-        <v>970</v>
-      </c>
-      <c r="Z72">
-        <v>1000</v>
-      </c>
-      <c r="AA72">
-        <v>1000</v>
-      </c>
-      <c r="AB72">
-        <v>11</v>
-      </c>
-      <c r="AC72">
+      <c r="AZ72">
+        <v>20</v>
+      </c>
+      <c r="BA72">
         <v>9.4</v>
       </c>
-      <c r="AD72">
-        <v>1000</v>
-      </c>
-      <c r="AE72">
-        <v>1000</v>
-      </c>
-      <c r="AF72">
-        <v>32</v>
-      </c>
-      <c r="AG72">
-        <v>29</v>
-      </c>
-      <c r="AH72">
-        <v>1000</v>
-      </c>
-      <c r="AI72">
-        <v>1000</v>
-      </c>
-      <c r="AJ72">
-        <v>1000</v>
-      </c>
-      <c r="AK72">
-        <v>1000</v>
-      </c>
-      <c r="AL72">
-        <v>1000</v>
-      </c>
-      <c r="AM72">
-        <v>1000</v>
-      </c>
-      <c r="AN72">
-        <v>1000</v>
-      </c>
-      <c r="AO72">
-        <v>1000</v>
-      </c>
-      <c r="AP72">
-        <v>6.2</v>
-      </c>
-      <c r="AQ72">
-        <v>7.2</v>
-      </c>
-      <c r="AR72">
-        <v>1.71</v>
-      </c>
-      <c r="AS72">
-        <v>1.71</v>
-      </c>
-      <c r="AT72">
-        <v>5.9</v>
-      </c>
-      <c r="AU72">
-        <v>5.4</v>
-      </c>
-      <c r="AV72">
-        <v>1.71</v>
-      </c>
-      <c r="AW72">
-        <v>1.71</v>
-      </c>
-      <c r="AX72">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY72">
-        <v>8.6</v>
-      </c>
-      <c r="AZ72">
-        <v>1.71</v>
-      </c>
-      <c r="BA72">
-        <v>1.71</v>
-      </c>
       <c r="BB72">
-        <v>1.71</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC72">
-        <v>1.71</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD72">
-        <v>1.71</v>
+        <v>9</v>
       </c>
       <c r="BE72">
-        <v>1.71</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF72">
-        <v>1.71</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG72">
-        <v>1.71</v>
+        <v>9.4</v>
       </c>
       <c r="BH72">
         <v>970</v>
@@ -18725,7 +18725,7 @@
         <v>1.73</v>
       </c>
       <c r="G73">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="H73">
         <v>4.7</v>
@@ -18752,10 +18752,10 @@
         <v>1.39</v>
       </c>
       <c r="P73">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q73">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R73">
         <v>1.13</v>
@@ -18773,7 +18773,7 @@
         <v>1.18</v>
       </c>
       <c r="W73">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="X73">
         <v>1000</v>
@@ -18967,19 +18967,19 @@
         <v>1.45</v>
       </c>
       <c r="G74">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="H74">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="I74">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="J74">
         <v>4.5</v>
       </c>
       <c r="K74">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="L74">
         <v>1.33</v>
@@ -19000,7 +19000,7 @@
         <v>1.64</v>
       </c>
       <c r="R74">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S74">
         <v>2.58</v>
@@ -19015,7 +19015,7 @@
         <v>1.11</v>
       </c>
       <c r="W74">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="X74">
         <v>21</v>
@@ -19042,7 +19042,7 @@
         <v>140</v>
       </c>
       <c r="AF74">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG74">
         <v>10.5</v>
@@ -19075,13 +19075,13 @@
         <v>18.5</v>
       </c>
       <c r="AQ74">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR74">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS74">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT74">
         <v>8.199999999999999</v>
@@ -19090,10 +19090,10 @@
         <v>10</v>
       </c>
       <c r="AV74">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="AW74">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX74">
         <v>8.199999999999999</v>
@@ -19114,10 +19114,10 @@
         <v>13</v>
       </c>
       <c r="BD74">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE74">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF74">
         <v>5.7</v>
@@ -19150,7 +19150,7 @@
         <v>1.01</v>
       </c>
       <c r="BP74">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BQ74">
         <v>1.01</v>
@@ -19206,19 +19206,19 @@
         <v>308</v>
       </c>
       <c r="F75">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="G75">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="H75">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="I75">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="J75">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="K75">
         <v>900</v>
@@ -19236,7 +19236,7 @@
         <v>1.01</v>
       </c>
       <c r="P75">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="Q75">
         <v>1.29</v>
@@ -19254,10 +19254,10 @@
         <v>1.01</v>
       </c>
       <c r="V75">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W75">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X75">
         <v>1000</v>
@@ -19448,13 +19448,13 @@
         <v>309</v>
       </c>
       <c r="F76">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G76">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H76">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="I76">
         <v>3.05</v>
@@ -19463,7 +19463,7 @@
         <v>3.55</v>
       </c>
       <c r="K76">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L76">
         <v>1.38</v>
@@ -19478,7 +19478,7 @@
         <v>1.28</v>
       </c>
       <c r="P76">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q76">
         <v>1.86</v>
@@ -19487,19 +19487,19 @@
         <v>1.42</v>
       </c>
       <c r="S76">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T76">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U76">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V76">
         <v>1.48</v>
       </c>
       <c r="W76">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X76">
         <v>16.5</v>
@@ -19511,22 +19511,22 @@
         <v>22</v>
       </c>
       <c r="AA76">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB76">
         <v>12.5</v>
       </c>
       <c r="AC76">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD76">
         <v>13.5</v>
       </c>
       <c r="AE76">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF76">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG76">
         <v>12.5</v>
@@ -19535,28 +19535,28 @@
         <v>17</v>
       </c>
       <c r="AI76">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ76">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK76">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL76">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM76">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN76">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO76">
         <v>26</v>
       </c>
       <c r="AP76">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ76">
         <v>11.5</v>
@@ -19565,7 +19565,7 @@
         <v>17.5</v>
       </c>
       <c r="AS76">
-        <v>8.4</v>
+        <v>26</v>
       </c>
       <c r="AT76">
         <v>10.5</v>
@@ -19577,7 +19577,7 @@
         <v>11.5</v>
       </c>
       <c r="AW76">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="AX76">
         <v>15</v>
@@ -19589,25 +19589,25 @@
         <v>14.5</v>
       </c>
       <c r="BA76">
-        <v>8.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="BB76">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="BC76">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BD76">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BE76">
-        <v>8.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="BF76">
         <v>16.5</v>
       </c>
       <c r="BG76">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BH76">
         <v>970</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-14.xlsx
@@ -946,7 +946,7 @@
     <t>Deportes Limache</t>
   </si>
   <si>
-    <t>2026-09-13 11:58:09</t>
+    <t>2026-09-13 14:14:59</t>
   </si>
 </sst>
 </file>
@@ -1540,73 +1540,73 @@
         <v>235</v>
       </c>
       <c r="F2">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="G2">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="H2">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="I2">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="J2">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K2">
         <v>5.3</v>
       </c>
       <c r="L2">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M2">
         <v>1.02</v>
       </c>
       <c r="N2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O2">
         <v>1.16</v>
       </c>
       <c r="P2">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="Q2">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R2">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="S2">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T2">
         <v>1.54</v>
       </c>
       <c r="U2">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V2">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="W2">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="X2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y2">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AB2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AC2">
         <v>13</v>
@@ -1615,91 +1615,91 @@
         <v>11.5</v>
       </c>
       <c r="AE2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AF2">
         <v>55</v>
       </c>
       <c r="AG2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AH2">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AK2">
+        <v>80</v>
+      </c>
+      <c r="AL2">
         <v>65</v>
       </c>
-      <c r="AL2">
-        <v>60</v>
-      </c>
       <c r="AM2">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AN2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO2">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AP2">
-        <v>6</v>
+        <v>18.5</v>
       </c>
       <c r="AQ2">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS2">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AT2">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="AU2">
         <v>9.800000000000001</v>
       </c>
       <c r="AV2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW2">
         <v>12.5</v>
       </c>
       <c r="AX2">
-        <v>6.4</v>
+        <v>38</v>
       </c>
       <c r="AY2">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AZ2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB2">
-        <v>6.8</v>
+        <v>75</v>
       </c>
       <c r="BC2">
-        <v>6.4</v>
+        <v>38</v>
       </c>
       <c r="BD2">
-        <v>6.4</v>
+        <v>32</v>
       </c>
       <c r="BE2">
-        <v>6.6</v>
+        <v>50</v>
       </c>
       <c r="BF2">
-        <v>6.2</v>
+        <v>29</v>
       </c>
       <c r="BG2">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1803,7 +1803,7 @@
         <v>1.44</v>
       </c>
       <c r="M3">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N3">
         <v>3.6</v>
@@ -1839,13 +1839,13 @@
         <v>13</v>
       </c>
       <c r="Y3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z3">
         <v>30</v>
       </c>
       <c r="AA3">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AB3">
         <v>9.6</v>
@@ -1860,7 +1860,7 @@
         <v>55</v>
       </c>
       <c r="AF3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG3">
         <v>11.5</v>
@@ -1869,7 +1869,7 @@
         <v>22</v>
       </c>
       <c r="AI3">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ3">
         <v>32</v>
@@ -1899,7 +1899,7 @@
         <v>21</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="AT3">
         <v>8.199999999999999</v>
@@ -1911,7 +1911,7 @@
         <v>13</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AX3">
         <v>12.5</v>
@@ -1923,85 +1923,85 @@
         <v>15</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>75</v>
       </c>
       <c r="BF3">
         <v>18</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="CB3" t="s">
         <v>310</v>
@@ -2030,7 +2030,7 @@
         <v>2.8</v>
       </c>
       <c r="H4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I4">
         <v>3.35</v>
@@ -2039,7 +2039,7 @@
         <v>2.92</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="L4">
         <v>1.69</v>
@@ -2048,7 +2048,7 @@
         <v>1.16</v>
       </c>
       <c r="N4">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O4">
         <v>1.67</v>
@@ -2084,7 +2084,7 @@
         <v>8.4</v>
       </c>
       <c r="Z4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA4">
         <v>70</v>
@@ -2111,25 +2111,25 @@
         <v>27</v>
       </c>
       <c r="AI4">
-        <v>480</v>
+        <v>370</v>
       </c>
       <c r="AJ4">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AK4">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AL4">
-        <v>480</v>
+        <v>380</v>
       </c>
       <c r="AM4">
         <v>300</v>
       </c>
       <c r="AN4">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP4">
         <v>6.6</v>
@@ -2138,13 +2138,13 @@
         <v>7.6</v>
       </c>
       <c r="AR4">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS4">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AT4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU4">
         <v>6.4</v>
@@ -2174,76 +2174,76 @@
         <v>40</v>
       </c>
       <c r="BD4">
+        <v>48</v>
+      </c>
+      <c r="BE4">
+        <v>60</v>
+      </c>
+      <c r="BF4">
         <v>36</v>
       </c>
-      <c r="BE4">
-        <v>70</v>
-      </c>
-      <c r="BF4">
-        <v>32</v>
-      </c>
       <c r="BG4">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BH4">
-        <v>2.68</v>
+        <v>2.48</v>
       </c>
       <c r="BI4">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="BJ4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BK4">
+        <v>5.7</v>
+      </c>
+      <c r="BL4">
+        <v>290</v>
+      </c>
+      <c r="BM4">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BL4">
-        <v>280</v>
-      </c>
-      <c r="BM4">
-        <v>1.01</v>
       </c>
       <c r="BN4">
         <v>6.2</v>
       </c>
       <c r="BO4">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BP4">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BT4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BU4">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BV4">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BZ4">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="CB4" t="s">
         <v>310</v>
@@ -2266,22 +2266,22 @@
         <v>238</v>
       </c>
       <c r="F5">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G5">
         <v>2.14</v>
       </c>
       <c r="H5">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I5">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="J5">
         <v>3.8</v>
       </c>
       <c r="K5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>1.34</v>
@@ -2311,7 +2311,7 @@
         <v>1.67</v>
       </c>
       <c r="U5">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V5">
         <v>1.3</v>
@@ -2329,7 +2329,7 @@
         <v>29</v>
       </c>
       <c r="AA5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB5">
         <v>12</v>
@@ -2371,7 +2371,7 @@
         <v>12</v>
       </c>
       <c r="AO5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP5">
         <v>16.5</v>
@@ -2413,10 +2413,10 @@
         <v>22</v>
       </c>
       <c r="BC5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD5">
-        <v>9.6</v>
+        <v>23</v>
       </c>
       <c r="BE5">
         <v>11.5</v>
@@ -2425,67 +2425,67 @@
         <v>10.5</v>
       </c>
       <c r="BG5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BH5">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BI5">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="BJ5">
+        <v>9</v>
+      </c>
+      <c r="BK5">
+        <v>8</v>
+      </c>
+      <c r="BL5">
+        <v>110</v>
+      </c>
+      <c r="BM5">
+        <v>21</v>
+      </c>
+      <c r="BN5">
+        <v>5.1</v>
+      </c>
+      <c r="BO5">
+        <v>4.6</v>
+      </c>
+      <c r="BP5">
         <v>14</v>
       </c>
-      <c r="BK5">
-        <v>6.6</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>1.01</v>
-      </c>
-      <c r="BN5">
-        <v>6</v>
-      </c>
-      <c r="BO5">
-        <v>4</v>
-      </c>
-      <c r="BP5">
-        <v>1000</v>
-      </c>
       <c r="BQ5">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BT5">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BU5">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="CB5" t="s">
         <v>310</v>
@@ -2517,7 +2517,7 @@
         <v>2.48</v>
       </c>
       <c r="I6">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -2553,7 +2553,7 @@
         <v>1.5</v>
       </c>
       <c r="U6">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="V6">
         <v>1.65</v>
@@ -2565,7 +2565,7 @@
         <v>27</v>
       </c>
       <c r="Y6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z6">
         <v>21</v>
@@ -2574,28 +2574,28 @@
         <v>36</v>
       </c>
       <c r="AB6">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE6">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF6">
         <v>24</v>
       </c>
       <c r="AG6">
+        <v>13</v>
+      </c>
+      <c r="AH6">
         <v>13.5</v>
       </c>
-      <c r="AH6">
-        <v>14</v>
-      </c>
       <c r="AI6">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AJ6">
         <v>44</v>
@@ -2607,7 +2607,7 @@
         <v>29</v>
       </c>
       <c r="AM6">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AN6">
         <v>14.5</v>
@@ -2616,10 +2616,10 @@
         <v>12</v>
       </c>
       <c r="AP6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AR6">
         <v>19</v>
@@ -2628,13 +2628,13 @@
         <v>30</v>
       </c>
       <c r="AT6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AU6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW6">
         <v>20</v>
@@ -2661,16 +2661,16 @@
         <v>26</v>
       </c>
       <c r="BE6">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BF6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG6">
         <v>11</v>
       </c>
       <c r="BH6">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BI6">
         <v>3.85</v>
@@ -2709,7 +2709,7 @@
         <v>7</v>
       </c>
       <c r="BU6">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV6">
         <v>1000</v>
@@ -2753,7 +2753,7 @@
         <v>1.55</v>
       </c>
       <c r="G7">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="H7">
         <v>6.2</v>
@@ -2768,7 +2768,7 @@
         <v>5</v>
       </c>
       <c r="L7">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="M7">
         <v>1.05</v>
@@ -2780,16 +2780,16 @@
         <v>1.24</v>
       </c>
       <c r="P7">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q7">
         <v>1.72</v>
       </c>
       <c r="R7">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S7">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T7">
         <v>1.85</v>
@@ -2801,31 +2801,31 @@
         <v>1.18</v>
       </c>
       <c r="W7">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="X7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z7">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA7">
         <v>190</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD7">
         <v>23</v>
       </c>
       <c r="AE7">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF7">
         <v>10</v>
@@ -2852,13 +2852,13 @@
         <v>120</v>
       </c>
       <c r="AN7">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AO7">
         <v>95</v>
       </c>
       <c r="AP7">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="AQ7">
         <v>20</v>
@@ -2867,10 +2867,10 @@
         <v>22</v>
       </c>
       <c r="AS7">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="AT7">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU7">
         <v>10</v>
@@ -2879,7 +2879,7 @@
         <v>20</v>
       </c>
       <c r="AW7">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AX7">
         <v>9.199999999999999</v>
@@ -2891,7 +2891,7 @@
         <v>19.5</v>
       </c>
       <c r="BA7">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BB7">
         <v>12.5</v>
@@ -2903,25 +2903,25 @@
         <v>27</v>
       </c>
       <c r="BE7">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="BF7">
         <v>6.6</v>
       </c>
       <c r="BG7">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BH7">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI7">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BJ7">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BK7">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2930,10 +2930,10 @@
         <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO7">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP7">
         <v>15.5</v>
@@ -2948,10 +2948,10 @@
         <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BU7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BV7">
         <v>1000</v>
@@ -2992,19 +2992,19 @@
         <v>241</v>
       </c>
       <c r="F8">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H8">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="I8">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="J8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K8">
         <v>3.8</v>
@@ -3019,7 +3019,7 @@
         <v>3.55</v>
       </c>
       <c r="O8">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P8">
         <v>1.87</v>
@@ -3028,13 +3028,13 @@
         <v>2.1</v>
       </c>
       <c r="R8">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S8">
         <v>3.85</v>
       </c>
       <c r="T8">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U8">
         <v>1.97</v>
@@ -3043,7 +3043,7 @@
         <v>2.06</v>
       </c>
       <c r="W8">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X8">
         <v>13.5</v>
@@ -3055,10 +3055,10 @@
         <v>11.5</v>
       </c>
       <c r="AA8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AC8">
         <v>8.4</v>
@@ -3067,7 +3067,7 @@
         <v>11</v>
       </c>
       <c r="AE8">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AF8">
         <v>38</v>
@@ -3097,7 +3097,7 @@
         <v>95</v>
       </c>
       <c r="AO8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP8">
         <v>11</v>
@@ -3109,7 +3109,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT8">
         <v>13.5</v>
@@ -3124,91 +3124,91 @@
         <v>18.5</v>
       </c>
       <c r="AX8">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="AY8">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AZ8">
         <v>17.5</v>
       </c>
       <c r="BA8">
-        <v>8.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="BB8">
-        <v>8.800000000000001</v>
+        <v>70</v>
       </c>
       <c r="BC8">
-        <v>8.4</v>
+        <v>44</v>
       </c>
       <c r="BD8">
-        <v>8.4</v>
+        <v>46</v>
       </c>
       <c r="BE8">
-        <v>8.800000000000001</v>
+        <v>85</v>
       </c>
       <c r="BF8">
+        <v>55</v>
+      </c>
+      <c r="BG8">
+        <v>12</v>
+      </c>
+      <c r="BH8">
+        <v>3.7</v>
+      </c>
+      <c r="BI8">
+        <v>2.74</v>
+      </c>
+      <c r="BJ8">
+        <v>12</v>
+      </c>
+      <c r="BK8">
+        <v>1.01</v>
+      </c>
+      <c r="BL8">
+        <v>170</v>
+      </c>
+      <c r="BM8">
+        <v>1.01</v>
+      </c>
+      <c r="BN8">
         <v>8.6</v>
       </c>
-      <c r="BG8">
-        <v>13</v>
-      </c>
-      <c r="BH8">
-        <v>1000</v>
-      </c>
-      <c r="BI8">
-        <v>1.01</v>
-      </c>
-      <c r="BJ8">
-        <v>1000</v>
-      </c>
-      <c r="BK8">
-        <v>1.01</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>1.01</v>
-      </c>
-      <c r="BN8">
-        <v>1000</v>
-      </c>
       <c r="BO8">
         <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BQ8">
         <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS8">
         <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BW8">
         <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY8">
         <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA8">
         <v>1.01</v>
@@ -3237,13 +3237,13 @@
         <v>3</v>
       </c>
       <c r="G9">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H9">
         <v>2.22</v>
       </c>
       <c r="I9">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J9">
         <v>1.1</v>
@@ -3267,7 +3267,7 @@
         <v>1.83</v>
       </c>
       <c r="Q9">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R9">
         <v>1.25</v>
@@ -3282,10 +3282,10 @@
         <v>1.81</v>
       </c>
       <c r="V9">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W9">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3476,7 +3476,7 @@
         <v>243</v>
       </c>
       <c r="F10">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="G10">
         <v>7.4</v>
@@ -3488,7 +3488,7 @@
         <v>1.82</v>
       </c>
       <c r="J10">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K10">
         <v>4.2</v>
@@ -3518,10 +3518,10 @@
         <v>3.5</v>
       </c>
       <c r="T10">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="U10">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
         <v>2.2</v>
@@ -3584,37 +3584,37 @@
         <v>15</v>
       </c>
       <c r="AP10">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
         <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
         <v>1.01</v>
@@ -3635,7 +3635,7 @@
         <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3760,10 +3760,10 @@
         <v>2.38</v>
       </c>
       <c r="T11">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="U11">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="V11">
         <v>1.12</v>
@@ -3775,10 +3775,10 @@
         <v>1000</v>
       </c>
       <c r="Y11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z11">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AA11">
         <v>1000</v>
@@ -3811,7 +3811,7 @@
         <v>29</v>
       </c>
       <c r="AK11">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
         <v>1000</v>
@@ -3826,16 +3826,16 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AQ11">
         <v>15.5</v>
       </c>
       <c r="AR11">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AS11">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AT11">
         <v>6.6</v>
@@ -3847,7 +3847,7 @@
         <v>17</v>
       </c>
       <c r="AW11">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AX11">
         <v>6.2</v>
@@ -3856,28 +3856,28 @@
         <v>7.8</v>
       </c>
       <c r="AZ11">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA11">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BB11">
         <v>8.6</v>
       </c>
       <c r="BC11">
-        <v>9.4</v>
+        <v>2</v>
       </c>
       <c r="BD11">
-        <v>14.5</v>
+        <v>2</v>
       </c>
       <c r="BE11">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BF11">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BG11">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3960,7 +3960,7 @@
         <v>245</v>
       </c>
       <c r="F12">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="G12">
         <v>3.2</v>
@@ -3969,13 +3969,13 @@
         <v>3.5</v>
       </c>
       <c r="I12">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="J12">
         <v>2.4</v>
       </c>
       <c r="K12">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3993,7 +3993,7 @@
         <v>1.36</v>
       </c>
       <c r="Q12">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R12">
         <v>1.13</v>
@@ -4005,10 +4005,10 @@
         <v>2.24</v>
       </c>
       <c r="U12">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="V12">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
         <v>1.45</v>
@@ -4071,7 +4071,7 @@
         <v>4.5</v>
       </c>
       <c r="AQ12">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR12">
         <v>1.77</v>
@@ -4110,10 +4110,10 @@
         <v>1.77</v>
       </c>
       <c r="BD12">
+        <v>1.77</v>
+      </c>
+      <c r="BE12">
         <v>1.87</v>
-      </c>
-      <c r="BE12">
-        <v>2</v>
       </c>
       <c r="BF12">
         <v>1.77</v>
@@ -4217,7 +4217,7 @@
         <v>3.3</v>
       </c>
       <c r="K13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -4229,7 +4229,7 @@
         <v>3</v>
       </c>
       <c r="O13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P13">
         <v>1.98</v>
@@ -4241,7 +4241,7 @@
         <v>1.32</v>
       </c>
       <c r="S13">
-        <v>2.2</v>
+        <v>2.72</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -4444,166 +4444,166 @@
         <v>247</v>
       </c>
       <c r="F14">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="G14">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="H14">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I14">
+        <v>5.4</v>
+      </c>
+      <c r="J14">
+        <v>3.95</v>
+      </c>
+      <c r="K14">
+        <v>4.1</v>
+      </c>
+      <c r="L14">
+        <v>1.01</v>
+      </c>
+      <c r="M14">
+        <v>1.06</v>
+      </c>
+      <c r="N14">
+        <v>4</v>
+      </c>
+      <c r="O14">
+        <v>1.29</v>
+      </c>
+      <c r="P14">
+        <v>2.04</v>
+      </c>
+      <c r="Q14">
+        <v>1.86</v>
+      </c>
+      <c r="R14">
+        <v>1.41</v>
+      </c>
+      <c r="S14">
+        <v>3.2</v>
+      </c>
+      <c r="T14">
+        <v>1.82</v>
+      </c>
+      <c r="U14">
+        <v>2.12</v>
+      </c>
+      <c r="V14">
+        <v>1.22</v>
+      </c>
+      <c r="W14">
+        <v>2.24</v>
+      </c>
+      <c r="X14">
+        <v>19</v>
+      </c>
+      <c r="Y14">
+        <v>22</v>
+      </c>
+      <c r="Z14">
+        <v>48</v>
+      </c>
+      <c r="AA14">
+        <v>140</v>
+      </c>
+      <c r="AB14">
+        <v>10.5</v>
+      </c>
+      <c r="AC14">
+        <v>9.4</v>
+      </c>
+      <c r="AD14">
+        <v>23</v>
+      </c>
+      <c r="AE14">
+        <v>80</v>
+      </c>
+      <c r="AF14">
+        <v>11.5</v>
+      </c>
+      <c r="AG14">
+        <v>10.5</v>
+      </c>
+      <c r="AH14">
+        <v>23</v>
+      </c>
+      <c r="AI14">
+        <v>80</v>
+      </c>
+      <c r="AJ14">
+        <v>22</v>
+      </c>
+      <c r="AK14">
+        <v>22</v>
+      </c>
+      <c r="AL14">
+        <v>40</v>
+      </c>
+      <c r="AM14">
+        <v>120</v>
+      </c>
+      <c r="AN14">
+        <v>12.5</v>
+      </c>
+      <c r="AO14">
+        <v>85</v>
+      </c>
+      <c r="AP14">
+        <v>14</v>
+      </c>
+      <c r="AQ14">
+        <v>15.5</v>
+      </c>
+      <c r="AR14">
         <v>6</v>
       </c>
-      <c r="J14">
-        <v>3.9</v>
-      </c>
-      <c r="K14">
-        <v>4.3</v>
-      </c>
-      <c r="L14">
-        <v>1.01</v>
-      </c>
-      <c r="M14">
-        <v>1.05</v>
-      </c>
-      <c r="N14">
-        <v>3.5</v>
-      </c>
-      <c r="O14">
-        <v>1.26</v>
-      </c>
-      <c r="P14">
-        <v>2</v>
-      </c>
-      <c r="Q14">
-        <v>1.79</v>
-      </c>
-      <c r="R14">
-        <v>1.32</v>
-      </c>
-      <c r="S14">
-        <v>2.54</v>
-      </c>
-      <c r="T14">
-        <v>1.01</v>
-      </c>
-      <c r="U14">
-        <v>2.1</v>
-      </c>
-      <c r="V14">
-        <v>1.2</v>
-      </c>
-      <c r="W14">
-        <v>2.16</v>
-      </c>
-      <c r="X14">
-        <v>1000</v>
-      </c>
-      <c r="Y14">
-        <v>1000</v>
-      </c>
-      <c r="Z14">
-        <v>1000</v>
-      </c>
-      <c r="AA14">
-        <v>1000</v>
-      </c>
-      <c r="AB14">
-        <v>1000</v>
-      </c>
-      <c r="AC14">
-        <v>1000</v>
-      </c>
-      <c r="AD14">
-        <v>1000</v>
-      </c>
-      <c r="AE14">
-        <v>1000</v>
-      </c>
-      <c r="AF14">
-        <v>1000</v>
-      </c>
-      <c r="AG14">
-        <v>1000</v>
-      </c>
-      <c r="AH14">
-        <v>1000</v>
-      </c>
-      <c r="AI14">
-        <v>1000</v>
-      </c>
-      <c r="AJ14">
-        <v>1000</v>
-      </c>
-      <c r="AK14">
-        <v>1000</v>
-      </c>
-      <c r="AL14">
-        <v>1000</v>
-      </c>
-      <c r="AM14">
-        <v>1000</v>
-      </c>
-      <c r="AN14">
-        <v>1000</v>
-      </c>
-      <c r="AO14">
-        <v>1000</v>
-      </c>
-      <c r="AP14">
-        <v>1.01</v>
-      </c>
-      <c r="AQ14">
-        <v>1.01</v>
-      </c>
-      <c r="AR14">
-        <v>1.01</v>
-      </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ14">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4624,7 +4624,7 @@
         <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BO14">
         <v>1.01</v>
@@ -4686,19 +4686,19 @@
         <v>248</v>
       </c>
       <c r="F15">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="G15">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="H15">
         <v>3</v>
       </c>
       <c r="I15">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="J15">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="K15">
         <v>900</v>
@@ -4710,16 +4710,16 @@
         <v>1.02</v>
       </c>
       <c r="N15">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="O15">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="P15">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="Q15">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="R15">
         <v>1.54</v>
@@ -4728,16 +4728,16 @@
         <v>2.18</v>
       </c>
       <c r="T15">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="U15">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="V15">
         <v>1.01</v>
       </c>
       <c r="W15">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4764,7 +4764,7 @@
         <v>1000</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG15">
         <v>1000</v>
@@ -4776,7 +4776,7 @@
         <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK15">
         <v>1000</v>
@@ -4794,58 +4794,58 @@
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AS15">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4928,163 +4928,163 @@
         <v>249</v>
       </c>
       <c r="F16">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="G16">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="H16">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="I16">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="J16">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K16">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L16">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="M16">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N16">
         <v>3.65</v>
       </c>
       <c r="O16">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P16">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="Q16">
         <v>2.06</v>
       </c>
       <c r="R16">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S16">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="T16">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U16">
         <v>1.94</v>
       </c>
       <c r="V16">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W16">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="X16">
         <v>16.5</v>
       </c>
       <c r="Y16">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="Z16">
         <v>50</v>
       </c>
       <c r="AA16">
-        <v>960</v>
+        <v>900</v>
       </c>
       <c r="AB16">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AC16">
         <v>9</v>
       </c>
       <c r="AD16">
+        <v>28</v>
+      </c>
+      <c r="AE16">
+        <v>190</v>
+      </c>
+      <c r="AF16">
+        <v>9.6</v>
+      </c>
+      <c r="AG16">
+        <v>10.5</v>
+      </c>
+      <c r="AH16">
         <v>26</v>
       </c>
-      <c r="AE16">
-        <v>290</v>
-      </c>
-      <c r="AF16">
-        <v>10</v>
-      </c>
-      <c r="AG16">
-        <v>11</v>
-      </c>
-      <c r="AH16">
+      <c r="AI16">
+        <v>480</v>
+      </c>
+      <c r="AJ16">
+        <v>18.5</v>
+      </c>
+      <c r="AK16">
+        <v>20</v>
+      </c>
+      <c r="AL16">
+        <v>55</v>
+      </c>
+      <c r="AM16">
+        <v>900</v>
+      </c>
+      <c r="AN16">
+        <v>11.5</v>
+      </c>
+      <c r="AO16">
+        <v>840</v>
+      </c>
+      <c r="AP16">
+        <v>11.5</v>
+      </c>
+      <c r="AQ16">
+        <v>15.5</v>
+      </c>
+      <c r="AR16">
         <v>25</v>
       </c>
-      <c r="AI16">
-        <v>540</v>
-      </c>
-      <c r="AJ16">
-        <v>22</v>
-      </c>
-      <c r="AK16">
-        <v>21</v>
-      </c>
-      <c r="AL16">
-        <v>80</v>
-      </c>
-      <c r="AM16">
-        <v>960</v>
-      </c>
-      <c r="AN16">
-        <v>12</v>
-      </c>
-      <c r="AO16">
-        <v>900</v>
-      </c>
-      <c r="AP16">
-        <v>12.5</v>
-      </c>
-      <c r="AQ16">
-        <v>13.5</v>
-      </c>
-      <c r="AR16">
-        <v>23</v>
-      </c>
       <c r="AS16">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT16">
         <v>7.4</v>
       </c>
       <c r="AU16">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV16">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW16">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AX16">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY16">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ16">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA16">
         <v>40</v>
       </c>
       <c r="BB16">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC16">
         <v>16.5</v>
       </c>
       <c r="BD16">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BE16">
         <v>42</v>
       </c>
       <c r="BF16">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG16">
         <v>38</v>
@@ -5099,31 +5099,31 @@
         <v>970</v>
       </c>
       <c r="BK16">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BN16">
         <v>970</v>
       </c>
       <c r="BO16">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="BP16">
-        <v>620</v>
+        <v>490</v>
       </c>
       <c r="BQ16">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BT16">
         <v>970</v>
@@ -5135,19 +5135,19 @@
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BZ16">
         <v>1000</v>
       </c>
       <c r="CA16">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="CB16" t="s">
         <v>310</v>
@@ -5170,7 +5170,7 @@
         <v>250</v>
       </c>
       <c r="F17">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="G17">
         <v>13.5</v>
@@ -5179,10 +5179,10 @@
         <v>1.28</v>
       </c>
       <c r="I17">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="J17">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="K17">
         <v>7</v>
@@ -5212,13 +5212,13 @@
         <v>2.28</v>
       </c>
       <c r="T17">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U17">
         <v>1.85</v>
       </c>
       <c r="V17">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="W17">
         <v>1.08</v>
@@ -5278,43 +5278,43 @@
         <v>5</v>
       </c>
       <c r="AP17">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>8</v>
+        <v>1.02</v>
       </c>
       <c r="AR17">
-        <v>7</v>
+        <v>1.02</v>
       </c>
       <c r="AS17">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="AT17">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AU17">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="AV17">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AW17">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AX17">
         <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AZ17">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA17">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="BC17">
         <v>1.01</v>
@@ -5329,7 +5329,7 @@
         <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5412,28 +5412,28 @@
         <v>251</v>
       </c>
       <c r="F18">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="G18">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="H18">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="I18">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="J18">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K18">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="L18">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N18">
         <v>4</v>
@@ -5442,136 +5442,136 @@
         <v>1.27</v>
       </c>
       <c r="P18">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="Q18">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="R18">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S18">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="T18">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U18">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V18">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="W18">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="X18">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y18">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z18">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA18">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB18">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC18">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD18">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE18">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF18">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG18">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH18">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI18">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ18">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK18">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL18">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM18">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN18">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO18">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP18">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ18">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR18">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AS18">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="AT18">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU18">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV18">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW18">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AX18">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY18">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ18">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA18">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BB18">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BC18">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BD18">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BE18">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BF18">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG18">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5654,19 +5654,19 @@
         <v>252</v>
       </c>
       <c r="F19">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G19">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H19">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I19">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J19">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K19">
         <v>3.75</v>
@@ -5678,16 +5678,16 @@
         <v>1.07</v>
       </c>
       <c r="N19">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O19">
         <v>1.34</v>
       </c>
       <c r="P19">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q19">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R19">
         <v>1.31</v>
@@ -5696,22 +5696,22 @@
         <v>3.4</v>
       </c>
       <c r="T19">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U19">
         <v>2.06</v>
       </c>
       <c r="V19">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W19">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X19">
         <v>16</v>
       </c>
       <c r="Y19">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z19">
         <v>21</v>
@@ -5765,55 +5765,55 @@
         <v>9.6</v>
       </c>
       <c r="AQ19">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR19">
         <v>14</v>
       </c>
       <c r="AS19">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT19">
         <v>7.8</v>
       </c>
       <c r="AU19">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV19">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AW19">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AX19">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY19">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ19">
         <v>12.5</v>
       </c>
       <c r="BA19">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB19">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC19">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BD19">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE19">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BF19">
         <v>19.5</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH19">
         <v>3.8</v>
@@ -5905,7 +5905,7 @@
         <v>1.94</v>
       </c>
       <c r="I20">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="J20">
         <v>3.1</v>
@@ -5917,13 +5917,13 @@
         <v>1.41</v>
       </c>
       <c r="M20">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N20">
         <v>2.68</v>
       </c>
       <c r="O20">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="P20">
         <v>1.65</v>
@@ -5944,7 +5944,7 @@
         <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="W20">
         <v>1.22</v>
@@ -6138,7 +6138,7 @@
         <v>254</v>
       </c>
       <c r="F21">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G21">
         <v>3.95</v>
@@ -6153,7 +6153,7 @@
         <v>3.15</v>
       </c>
       <c r="K21">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -6162,7 +6162,7 @@
         <v>1.07</v>
       </c>
       <c r="N21">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="O21">
         <v>1.34</v>
@@ -6171,7 +6171,7 @@
         <v>1.82</v>
       </c>
       <c r="Q21">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="R21">
         <v>1.28</v>
@@ -6180,7 +6180,7 @@
         <v>3.45</v>
       </c>
       <c r="T21">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="U21">
         <v>1.96</v>
@@ -6192,10 +6192,10 @@
         <v>1.34</v>
       </c>
       <c r="X21">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y21">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z21">
         <v>38</v>
@@ -6204,25 +6204,25 @@
         <v>1000</v>
       </c>
       <c r="AB21">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AC21">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD21">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="AE21">
         <v>1000</v>
       </c>
       <c r="AF21">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG21">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH21">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI21">
         <v>1000</v>
@@ -6249,7 +6249,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ21">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AR21">
         <v>8.6</v>
@@ -6261,7 +6261,7 @@
         <v>8.4</v>
       </c>
       <c r="AU21">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV21">
         <v>8.199999999999999</v>
@@ -6270,16 +6270,16 @@
         <v>1.01</v>
       </c>
       <c r="AX21">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY21">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ21">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA21">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BB21">
         <v>1.01</v>
@@ -6383,109 +6383,109 @@
         <v>2</v>
       </c>
       <c r="G22">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H22">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="I22">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J22">
         <v>3.2</v>
       </c>
       <c r="K22">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="L22">
         <v>1.33</v>
       </c>
       <c r="M22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N22">
         <v>3.1</v>
       </c>
       <c r="O22">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="P22">
         <v>1.84</v>
       </c>
       <c r="Q22">
-        <v>2.02</v>
+        <v>1.49</v>
       </c>
       <c r="R22">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S22">
         <v>3.25</v>
       </c>
       <c r="T22">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U22">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V22">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W22">
         <v>1.8</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF22">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN22">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP22">
         <v>1.01</v>
@@ -6625,16 +6625,16 @@
         <v>1.21</v>
       </c>
       <c r="G23">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="H23">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="I23">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J23">
-        <v>3.8</v>
+        <v>5.9</v>
       </c>
       <c r="K23">
         <v>930</v>
@@ -6646,22 +6646,22 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="O23">
         <v>1.23</v>
       </c>
       <c r="P23">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="Q23">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R23">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S23">
-        <v>2.66</v>
+        <v>2.14</v>
       </c>
       <c r="T23">
         <v>1.01</v>
@@ -6673,7 +6673,7 @@
         <v>1.01</v>
       </c>
       <c r="W23">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6864,7 +6864,7 @@
         <v>257</v>
       </c>
       <c r="F24">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="G24">
         <v>1.26</v>
@@ -6873,7 +6873,7 @@
         <v>17</v>
       </c>
       <c r="I24">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="J24">
         <v>6.8</v>
@@ -6900,10 +6900,10 @@
         <v>1.7</v>
       </c>
       <c r="R24">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S24">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T24">
         <v>2.52</v>
@@ -6915,7 +6915,7 @@
         <v>1.05</v>
       </c>
       <c r="W24">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="X24">
         <v>22</v>
@@ -6975,10 +6975,10 @@
         <v>19.5</v>
       </c>
       <c r="AQ24">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AR24">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AS24">
         <v>100</v>
@@ -6990,7 +6990,7 @@
         <v>14</v>
       </c>
       <c r="AV24">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AW24">
         <v>100</v>
@@ -6999,7 +6999,7 @@
         <v>6.6</v>
       </c>
       <c r="AY24">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ24">
         <v>36</v>
@@ -7014,7 +7014,7 @@
         <v>14</v>
       </c>
       <c r="BD24">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BE24">
         <v>50</v>
@@ -7026,55 +7026,55 @@
         <v>90</v>
       </c>
       <c r="BH24">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BI24">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="BJ24">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BK24">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BL24">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="BM24">
         <v>36</v>
       </c>
       <c r="BN24">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BO24">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="BP24">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BQ24">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BR24">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BS24">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BT24">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="BU24">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BV24">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="BW24">
         <v>27</v>
       </c>
       <c r="BX24">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BY24">
         <v>26</v>
@@ -7136,10 +7136,10 @@
         <v>1.27</v>
       </c>
       <c r="P25">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q25">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R25">
         <v>1.45</v>
@@ -7157,13 +7157,13 @@
         <v>2.66</v>
       </c>
       <c r="W25">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X25">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y25">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z25">
         <v>10</v>
@@ -7175,22 +7175,22 @@
         <v>22</v>
       </c>
       <c r="AC25">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD25">
         <v>9.800000000000001</v>
       </c>
       <c r="AE25">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF25">
         <v>55</v>
       </c>
       <c r="AG25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH25">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI25">
         <v>36</v>
@@ -7211,7 +7211,7 @@
         <v>100</v>
       </c>
       <c r="AO25">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP25">
         <v>16</v>
@@ -7253,10 +7253,10 @@
         <v>44</v>
       </c>
       <c r="BC25">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="BD25">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BE25">
         <v>100</v>
@@ -7265,58 +7265,58 @@
         <v>85</v>
       </c>
       <c r="BG25">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH25">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI25">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BJ25">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK25">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL25">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM25">
         <v>30</v>
       </c>
       <c r="BN25">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO25">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP25">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BQ25">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR25">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS25">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT25">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BU25">
-        <v>2.88</v>
+        <v>3.65</v>
       </c>
       <c r="BV25">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BW25">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="BX25">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY25">
         <v>11</v>
@@ -7348,22 +7348,22 @@
         <v>259</v>
       </c>
       <c r="F26">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="G26">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="H26">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="I26">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="J26">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K26">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="L26">
         <v>1.01</v>
@@ -7372,37 +7372,37 @@
         <v>1.02</v>
       </c>
       <c r="N26">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O26">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P26">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="Q26">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="R26">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="S26">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="T26">
         <v>1.6</v>
       </c>
       <c r="U26">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="V26">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="W26">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X26">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y26">
         <v>15</v>
@@ -7417,7 +7417,7 @@
         <v>34</v>
       </c>
       <c r="AC26">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD26">
         <v>12.5</v>
@@ -7426,31 +7426,31 @@
         <v>18</v>
       </c>
       <c r="AF26">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AG26">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AH26">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI26">
         <v>30</v>
       </c>
       <c r="AJ26">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AK26">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL26">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM26">
         <v>80</v>
       </c>
       <c r="AN26">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO26">
         <v>7</v>
@@ -7459,7 +7459,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ26">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR26">
         <v>1.01</v>
@@ -7489,7 +7489,7 @@
         <v>1.01</v>
       </c>
       <c r="BA26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BB26">
         <v>1.01</v>
@@ -7590,19 +7590,19 @@
         <v>260</v>
       </c>
       <c r="F27">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="H27">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I27">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J27">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K27">
         <v>3.75</v>
@@ -7620,10 +7620,10 @@
         <v>1.4</v>
       </c>
       <c r="P27">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q27">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="R27">
         <v>1.27</v>
@@ -7641,13 +7641,13 @@
         <v>1.23</v>
       </c>
       <c r="W27">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X27">
         <v>14</v>
       </c>
       <c r="Y27">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z27">
         <v>44</v>
@@ -7659,10 +7659,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC27">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD27">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE27">
         <v>90</v>
@@ -7671,7 +7671,7 @@
         <v>13.5</v>
       </c>
       <c r="AG27">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH27">
         <v>26</v>
@@ -7695,7 +7695,7 @@
         <v>20</v>
       </c>
       <c r="AO27">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP27">
         <v>10</v>
@@ -7704,10 +7704,10 @@
         <v>12.5</v>
       </c>
       <c r="AR27">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AS27">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AT27">
         <v>6.6</v>
@@ -7716,40 +7716,40 @@
         <v>7</v>
       </c>
       <c r="AV27">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW27">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AX27">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY27">
         <v>9</v>
       </c>
       <c r="AZ27">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA27">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB27">
         <v>16</v>
       </c>
       <c r="BC27">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD27">
-        <v>4.3</v>
+        <v>36</v>
       </c>
       <c r="BE27">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF27">
         <v>14</v>
       </c>
       <c r="BG27">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7835,16 +7835,16 @@
         <v>2.14</v>
       </c>
       <c r="G28">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H28">
         <v>3.95</v>
       </c>
       <c r="I28">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J28">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K28">
         <v>3.55</v>
@@ -7853,43 +7853,43 @@
         <v>1.4</v>
       </c>
       <c r="M28">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N28">
         <v>3.05</v>
       </c>
       <c r="O28">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P28">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="Q28">
         <v>2.16</v>
       </c>
       <c r="R28">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="S28">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="T28">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="U28">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="V28">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W28">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="X28">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="Y28">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="Z28">
         <v>1000</v>
@@ -7898,10 +7898,10 @@
         <v>1000</v>
       </c>
       <c r="AB28">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AC28">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AD28">
         <v>1000</v>
@@ -7910,88 +7910,88 @@
         <v>1000</v>
       </c>
       <c r="AF28">
+        <v>13.5</v>
+      </c>
+      <c r="AG28">
+        <v>11</v>
+      </c>
+      <c r="AH28">
+        <v>1000</v>
+      </c>
+      <c r="AI28">
+        <v>1000</v>
+      </c>
+      <c r="AJ28">
+        <v>36</v>
+      </c>
+      <c r="AK28">
+        <v>1000</v>
+      </c>
+      <c r="AL28">
+        <v>1000</v>
+      </c>
+      <c r="AM28">
+        <v>1000</v>
+      </c>
+      <c r="AN28">
+        <v>1000</v>
+      </c>
+      <c r="AO28">
+        <v>1000</v>
+      </c>
+      <c r="AP28">
+        <v>10</v>
+      </c>
+      <c r="AQ28">
+        <v>11</v>
+      </c>
+      <c r="AR28">
+        <v>20</v>
+      </c>
+      <c r="AS28">
+        <v>60</v>
+      </c>
+      <c r="AT28">
+        <v>7.6</v>
+      </c>
+      <c r="AU28">
+        <v>6.8</v>
+      </c>
+      <c r="AV28">
+        <v>14.5</v>
+      </c>
+      <c r="AW28">
+        <v>38</v>
+      </c>
+      <c r="AX28">
+        <v>11.5</v>
+      </c>
+      <c r="AY28">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ28">
+        <v>17</v>
+      </c>
+      <c r="BA28">
+        <v>46</v>
+      </c>
+      <c r="BB28">
+        <v>21</v>
+      </c>
+      <c r="BC28">
+        <v>19</v>
+      </c>
+      <c r="BD28">
         <v>32</v>
       </c>
-      <c r="AG28">
-        <v>970</v>
-      </c>
-      <c r="AH28">
-        <v>1000</v>
-      </c>
-      <c r="AI28">
-        <v>1000</v>
-      </c>
-      <c r="AJ28">
-        <v>1000</v>
-      </c>
-      <c r="AK28">
-        <v>1000</v>
-      </c>
-      <c r="AL28">
-        <v>1000</v>
-      </c>
-      <c r="AM28">
-        <v>1000</v>
-      </c>
-      <c r="AN28">
-        <v>1000</v>
-      </c>
-      <c r="AO28">
-        <v>1000</v>
-      </c>
-      <c r="AP28">
-        <v>7.8</v>
-      </c>
-      <c r="AQ28">
-        <v>1.01</v>
-      </c>
-      <c r="AR28">
-        <v>1.01</v>
-      </c>
-      <c r="AS28">
-        <v>1.01</v>
-      </c>
-      <c r="AT28">
-        <v>6.4</v>
-      </c>
-      <c r="AU28">
-        <v>5.3</v>
-      </c>
-      <c r="AV28">
-        <v>1.01</v>
-      </c>
-      <c r="AW28">
-        <v>1.01</v>
-      </c>
-      <c r="AX28">
-        <v>1.01</v>
-      </c>
-      <c r="AY28">
-        <v>7.4</v>
-      </c>
-      <c r="AZ28">
-        <v>1.01</v>
-      </c>
-      <c r="BA28">
-        <v>1.01</v>
-      </c>
-      <c r="BB28">
-        <v>1.01</v>
-      </c>
-      <c r="BC28">
-        <v>1.01</v>
-      </c>
-      <c r="BD28">
-        <v>1.01</v>
-      </c>
       <c r="BE28">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BG28">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BH28">
         <v>970</v>
@@ -8074,13 +8074,13 @@
         <v>262</v>
       </c>
       <c r="F29">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="G29">
         <v>7.2</v>
       </c>
       <c r="H29">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="I29">
         <v>1.59</v>
@@ -8092,7 +8092,7 @@
         <v>4.7</v>
       </c>
       <c r="L29">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M29">
         <v>1.05</v>
@@ -8107,7 +8107,7 @@
         <v>2.18</v>
       </c>
       <c r="Q29">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R29">
         <v>1.47</v>
@@ -8155,7 +8155,7 @@
         <v>65</v>
       </c>
       <c r="AG29">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH29">
         <v>22</v>
@@ -8188,16 +8188,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR29">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS29">
         <v>13</v>
       </c>
       <c r="AT29">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU29">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV29">
         <v>9</v>
@@ -8206,7 +8206,7 @@
         <v>14</v>
       </c>
       <c r="AX29">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AY29">
         <v>20</v>
@@ -8215,16 +8215,16 @@
         <v>17.5</v>
       </c>
       <c r="BA29">
-        <v>15.5</v>
+        <v>27</v>
       </c>
       <c r="BB29">
         <v>11</v>
       </c>
       <c r="BC29">
+        <v>11</v>
+      </c>
+      <c r="BD29">
         <v>10.5</v>
-      </c>
-      <c r="BD29">
-        <v>10</v>
       </c>
       <c r="BE29">
         <v>10.5</v>
@@ -8319,7 +8319,7 @@
         <v>1.5</v>
       </c>
       <c r="G30">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="H30">
         <v>7</v>
@@ -8331,10 +8331,10 @@
         <v>4.5</v>
       </c>
       <c r="K30">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L30">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M30">
         <v>1.05</v>
@@ -8355,7 +8355,7 @@
         <v>1.46</v>
       </c>
       <c r="S30">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T30">
         <v>1.92</v>
@@ -8367,7 +8367,7 @@
         <v>1.13</v>
       </c>
       <c r="W30">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="X30">
         <v>22</v>
@@ -8442,7 +8442,7 @@
         <v>9.6</v>
       </c>
       <c r="AV30">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AW30">
         <v>8</v>
@@ -8454,7 +8454,7 @@
         <v>9</v>
       </c>
       <c r="AZ30">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA30">
         <v>7.8</v>
@@ -8466,7 +8466,7 @@
         <v>13</v>
       </c>
       <c r="BD30">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BE30">
         <v>8</v>
@@ -8499,7 +8499,7 @@
         <v>5.3</v>
       </c>
       <c r="BO30">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BP30">
         <v>12.5</v>
@@ -8520,7 +8520,7 @@
         <v>1.01</v>
       </c>
       <c r="BV30">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BW30">
         <v>1.01</v>
@@ -8561,10 +8561,10 @@
         <v>2.92</v>
       </c>
       <c r="G31">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H31">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="I31">
         <v>2.56</v>
@@ -8576,7 +8576,7 @@
         <v>3.85</v>
       </c>
       <c r="L31">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M31">
         <v>1.06</v>
@@ -8591,7 +8591,7 @@
         <v>2.1</v>
       </c>
       <c r="Q31">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R31">
         <v>1.43</v>
@@ -8600,7 +8600,7 @@
         <v>3.05</v>
       </c>
       <c r="T31">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U31">
         <v>2.28</v>
@@ -8609,10 +8609,10 @@
         <v>1.64</v>
       </c>
       <c r="W31">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X31">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Y31">
         <v>12.5</v>
@@ -8627,10 +8627,10 @@
         <v>14.5</v>
       </c>
       <c r="AC31">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD31">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AE31">
         <v>27</v>
@@ -8639,7 +8639,7 @@
         <v>23</v>
       </c>
       <c r="AG31">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH31">
         <v>17</v>
@@ -8663,7 +8663,7 @@
         <v>32</v>
       </c>
       <c r="AO31">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AP31">
         <v>15</v>
@@ -8675,7 +8675,7 @@
         <v>14.5</v>
       </c>
       <c r="AS31">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AT31">
         <v>12</v>
@@ -8687,7 +8687,7 @@
         <v>10</v>
       </c>
       <c r="AW31">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX31">
         <v>16</v>
@@ -8699,16 +8699,16 @@
         <v>14</v>
       </c>
       <c r="BA31">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BB31">
         <v>1.01</v>
       </c>
       <c r="BC31">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BD31">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BE31">
         <v>1.01</v>
@@ -8729,13 +8729,13 @@
         <v>13</v>
       </c>
       <c r="BK31">
-        <v>1.7</v>
+        <v>6.2</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="BN31">
         <v>9</v>
@@ -8762,7 +8762,7 @@
         <v>4.5</v>
       </c>
       <c r="BV31">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BW31">
         <v>1.81</v>
@@ -8803,13 +8803,13 @@
         <v>2.3</v>
       </c>
       <c r="G32">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H32">
         <v>3.05</v>
       </c>
       <c r="I32">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J32">
         <v>3.65</v>
@@ -8818,22 +8818,22 @@
         <v>3.9</v>
       </c>
       <c r="L32">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M32">
         <v>1.05</v>
       </c>
       <c r="N32">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="O32">
         <v>1.27</v>
       </c>
       <c r="P32">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q32">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="R32">
         <v>1.45</v>
@@ -8851,13 +8851,13 @@
         <v>1.44</v>
       </c>
       <c r="W32">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="X32">
         <v>20</v>
       </c>
       <c r="Y32">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z32">
         <v>24</v>
@@ -8866,10 +8866,10 @@
         <v>55</v>
       </c>
       <c r="AB32">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AC32">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD32">
         <v>14</v>
@@ -9051,7 +9051,7 @@
         <v>7.8</v>
       </c>
       <c r="I33">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J33">
         <v>4.9</v>
@@ -9066,7 +9066,7 @@
         <v>1.04</v>
       </c>
       <c r="N33">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="O33">
         <v>1.2</v>
@@ -9075,37 +9075,37 @@
         <v>2.52</v>
       </c>
       <c r="Q33">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R33">
         <v>1.62</v>
       </c>
       <c r="S33">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T33">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U33">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V33">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W33">
         <v>3.05</v>
       </c>
       <c r="X33">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y33">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z33">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA33">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AB33">
         <v>11</v>
@@ -9117,7 +9117,7 @@
         <v>32</v>
       </c>
       <c r="AE33">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF33">
         <v>10.5</v>
@@ -9129,40 +9129,40 @@
         <v>24</v>
       </c>
       <c r="AI33">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ33">
         <v>13</v>
       </c>
       <c r="AK33">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL33">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM33">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN33">
         <v>5.5</v>
       </c>
       <c r="AO33">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP33">
         <v>21</v>
       </c>
       <c r="AQ33">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="AR33">
-        <v>11.5</v>
+        <v>38</v>
       </c>
       <c r="AS33">
         <v>12.5</v>
       </c>
       <c r="AT33">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU33">
         <v>10.5</v>
@@ -9171,37 +9171,37 @@
         <v>25</v>
       </c>
       <c r="AW33">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="AX33">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY33">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ33">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="BA33">
-        <v>11.5</v>
+        <v>34</v>
       </c>
       <c r="BB33">
         <v>11.5</v>
       </c>
       <c r="BC33">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD33">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="BE33">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="BF33">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG33">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="BH33">
         <v>4.3</v>
@@ -9210,7 +9210,7 @@
         <v>4</v>
       </c>
       <c r="BJ33">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BK33">
         <v>9.199999999999999</v>
@@ -9219,7 +9219,7 @@
         <v>130</v>
       </c>
       <c r="BM33">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BN33">
         <v>4.1</v>
@@ -9237,7 +9237,7 @@
         <v>24</v>
       </c>
       <c r="BS33">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT33">
         <v>13</v>
@@ -9249,19 +9249,19 @@
         <v>70</v>
       </c>
       <c r="BW33">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BX33">
         <v>65</v>
       </c>
       <c r="BY33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BZ33">
         <v>14</v>
       </c>
       <c r="CA33">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="CB33" t="s">
         <v>310</v>
@@ -9296,7 +9296,7 @@
         <v>2.46</v>
       </c>
       <c r="J34">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="K34">
         <v>3.55</v>
@@ -9317,7 +9317,7 @@
         <v>1.72</v>
       </c>
       <c r="Q34">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="R34">
         <v>1.26</v>
@@ -9341,22 +9341,22 @@
         <v>13.5</v>
       </c>
       <c r="Y34">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z34">
         <v>17</v>
       </c>
       <c r="AA34">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB34">
         <v>14.5</v>
       </c>
       <c r="AC34">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD34">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE34">
         <v>34</v>
@@ -9365,22 +9365,22 @@
         <v>32</v>
       </c>
       <c r="AG34">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH34">
         <v>24</v>
       </c>
       <c r="AI34">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="AJ34">
         <v>95</v>
       </c>
       <c r="AK34">
+        <v>130</v>
+      </c>
+      <c r="AL34">
         <v>190</v>
-      </c>
-      <c r="AL34">
-        <v>95</v>
       </c>
       <c r="AM34">
         <v>150</v>
@@ -9392,58 +9392,58 @@
         <v>29</v>
       </c>
       <c r="AP34">
-        <v>3.5</v>
+        <v>9.6</v>
       </c>
       <c r="AQ34">
-        <v>3.2</v>
+        <v>7.2</v>
       </c>
       <c r="AR34">
-        <v>3.7</v>
+        <v>11.5</v>
       </c>
       <c r="AS34">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="AT34">
-        <v>3.55</v>
+        <v>10</v>
       </c>
       <c r="AU34">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="AV34">
-        <v>3.5</v>
+        <v>9.6</v>
       </c>
       <c r="AW34">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="AX34">
-        <v>4.1</v>
+        <v>21</v>
       </c>
       <c r="AY34">
-        <v>3.75</v>
+        <v>13</v>
       </c>
       <c r="AZ34">
-        <v>3.95</v>
+        <v>16</v>
       </c>
       <c r="BA34">
-        <v>4.3</v>
+        <v>17</v>
       </c>
       <c r="BB34">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="BC34">
-        <v>4.3</v>
+        <v>20</v>
       </c>
       <c r="BD34">
-        <v>4.4</v>
+        <v>28</v>
       </c>
       <c r="BE34">
-        <v>4.6</v>
+        <v>42</v>
       </c>
       <c r="BF34">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BG34">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9529,7 +9529,7 @@
         <v>3.95</v>
       </c>
       <c r="G35">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H35">
         <v>1.93</v>
@@ -9538,10 +9538,10 @@
         <v>2.14</v>
       </c>
       <c r="J35">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K35">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="L35">
         <v>1.45</v>
@@ -9550,7 +9550,7 @@
         <v>1.08</v>
       </c>
       <c r="N35">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="O35">
         <v>1.36</v>
@@ -9559,7 +9559,7 @@
         <v>1.72</v>
       </c>
       <c r="Q35">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="R35">
         <v>1.27</v>
@@ -9568,16 +9568,16 @@
         <v>3.6</v>
       </c>
       <c r="T35">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="U35">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="V35">
         <v>1.88</v>
       </c>
       <c r="W35">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X35">
         <v>22</v>
@@ -9777,13 +9777,13 @@
         <v>5.9</v>
       </c>
       <c r="I36">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J36">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K36">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L36">
         <v>1.31</v>
@@ -9798,13 +9798,13 @@
         <v>1.22</v>
       </c>
       <c r="P36">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q36">
         <v>1.64</v>
       </c>
       <c r="R36">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="S36">
         <v>2.6</v>
@@ -9813,7 +9813,7 @@
         <v>1.73</v>
       </c>
       <c r="U36">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V36">
         <v>1.18</v>
@@ -9831,19 +9831,19 @@
         <v>55</v>
       </c>
       <c r="AA36">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB36">
         <v>11</v>
       </c>
       <c r="AC36">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD36">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE36">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF36">
         <v>11.5</v>
@@ -9855,19 +9855,19 @@
         <v>20</v>
       </c>
       <c r="AI36">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ36">
         <v>16</v>
       </c>
       <c r="AK36">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL36">
         <v>30</v>
       </c>
       <c r="AM36">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN36">
         <v>7</v>
@@ -9882,13 +9882,13 @@
         <v>20</v>
       </c>
       <c r="AR36">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AS36">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="AT36">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU36">
         <v>9.199999999999999</v>
@@ -9897,19 +9897,19 @@
         <v>19</v>
       </c>
       <c r="AW36">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AX36">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY36">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ36">
         <v>16.5</v>
       </c>
       <c r="BA36">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BB36">
         <v>13.5</v>
@@ -9918,16 +9918,16 @@
         <v>13.5</v>
       </c>
       <c r="BD36">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="BE36">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BF36">
         <v>6.2</v>
       </c>
       <c r="BG36">
-        <v>9.4</v>
+        <v>34</v>
       </c>
       <c r="BH36">
         <v>4.2</v>
@@ -9945,7 +9945,7 @@
         <v>120</v>
       </c>
       <c r="BM36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BN36">
         <v>4.5</v>
@@ -9957,16 +9957,16 @@
         <v>10</v>
       </c>
       <c r="BQ36">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BR36">
         <v>25</v>
       </c>
       <c r="BS36">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BT36">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU36">
         <v>8.199999999999999</v>
@@ -9975,19 +9975,19 @@
         <v>50</v>
       </c>
       <c r="BW36">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX36">
         <v>55</v>
       </c>
       <c r="BY36">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ36">
         <v>17</v>
       </c>
       <c r="CA36">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="CB36" t="s">
         <v>310</v>
@@ -10010,22 +10010,22 @@
         <v>270</v>
       </c>
       <c r="F37">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G37">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H37">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="I37">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J37">
         <v>3.7</v>
       </c>
       <c r="K37">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L37">
         <v>1.28</v>
@@ -10043,25 +10043,25 @@
         <v>2.24</v>
       </c>
       <c r="Q37">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R37">
         <v>1.5</v>
       </c>
       <c r="S37">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T37">
         <v>1.6</v>
       </c>
       <c r="U37">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V37">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W37">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X37">
         <v>23</v>
@@ -10082,7 +10082,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD37">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE37">
         <v>32</v>
@@ -10094,13 +10094,13 @@
         <v>12.5</v>
       </c>
       <c r="AH37">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI37">
         <v>50</v>
       </c>
       <c r="AJ37">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AK37">
         <v>26</v>
@@ -10127,7 +10127,7 @@
         <v>18.5</v>
       </c>
       <c r="AS37">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AT37">
         <v>11.5</v>
@@ -10139,13 +10139,13 @@
         <v>11.5</v>
       </c>
       <c r="AW37">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AX37">
         <v>15.5</v>
       </c>
       <c r="AY37">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ37">
         <v>13.5</v>
@@ -10157,7 +10157,7 @@
         <v>21</v>
       </c>
       <c r="BC37">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BD37">
         <v>21</v>
@@ -10169,7 +10169,7 @@
         <v>13.5</v>
       </c>
       <c r="BG37">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BH37">
         <v>970</v>
@@ -10258,10 +10258,10 @@
         <v>1.2</v>
       </c>
       <c r="H38">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="I38">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J38">
         <v>9.4</v>
@@ -10270,25 +10270,25 @@
         <v>10.5</v>
       </c>
       <c r="L38">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="M38">
         <v>1.01</v>
       </c>
       <c r="N38">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="O38">
         <v>1.09</v>
       </c>
       <c r="P38">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q38">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="R38">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
         <v>1.71</v>
@@ -10297,10 +10297,10 @@
         <v>1.84</v>
       </c>
       <c r="U38">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V38">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W38">
         <v>6</v>
@@ -10309,7 +10309,7 @@
         <v>1000</v>
       </c>
       <c r="Y38">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="Z38">
         <v>1000</v>
@@ -10324,7 +10324,7 @@
         <v>27</v>
       </c>
       <c r="AD38">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AE38">
         <v>1000</v>
@@ -10336,7 +10336,7 @@
         <v>14</v>
       </c>
       <c r="AH38">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AI38">
         <v>1000</v>
@@ -10354,16 +10354,16 @@
         <v>1000</v>
       </c>
       <c r="AN38">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="AO38">
         <v>1000</v>
       </c>
       <c r="AP38">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AQ38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AR38">
         <v>46</v>
@@ -10390,10 +10390,10 @@
         <v>12</v>
       </c>
       <c r="AZ38">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BA38">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="BB38">
         <v>9.4</v>
@@ -10402,10 +10402,10 @@
         <v>11.5</v>
       </c>
       <c r="BD38">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="BE38">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="BF38">
         <v>2.44</v>
@@ -10494,22 +10494,22 @@
         <v>272</v>
       </c>
       <c r="F39">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="G39">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H39">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="I39">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="J39">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K39">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="L39">
         <v>1.01</v>
@@ -10518,124 +10518,124 @@
         <v>1.04</v>
       </c>
       <c r="N39">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="O39">
         <v>1.22</v>
       </c>
       <c r="P39">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="Q39">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="R39">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="S39">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T39">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="U39">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="V39">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="W39">
         <v>1.27</v>
       </c>
       <c r="X39">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y39">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z39">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA39">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB39">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AC39">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AD39">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE39">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF39">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AG39">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH39">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI39">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ39">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK39">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL39">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM39">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN39">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO39">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AP39">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AQ39">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR39">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS39">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AT39">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AU39">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV39">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW39">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AX39">
         <v>1.01</v>
       </c>
       <c r="AY39">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AZ39">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA39">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BB39">
         <v>1.01</v>
@@ -10653,7 +10653,7 @@
         <v>1.01</v>
       </c>
       <c r="BG39">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH39">
         <v>1000</v>
@@ -10739,43 +10739,43 @@
         <v>1.62</v>
       </c>
       <c r="G40">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="H40">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I40">
         <v>7.4</v>
       </c>
       <c r="J40">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K40">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="L40">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M40">
         <v>1.01</v>
       </c>
       <c r="N40">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="O40">
         <v>1.01</v>
       </c>
       <c r="P40">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="Q40">
         <v>1.9</v>
       </c>
       <c r="R40">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S40">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T40">
         <v>1.01</v>
@@ -10784,10 +10784,10 @@
         <v>1.01</v>
       </c>
       <c r="V40">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W40">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X40">
         <v>1000</v>
@@ -10993,7 +10993,7 @@
         <v>3.05</v>
       </c>
       <c r="K41">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L41">
         <v>1.51</v>
@@ -11002,7 +11002,7 @@
         <v>1.11</v>
       </c>
       <c r="N41">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O41">
         <v>1.5</v>
@@ -11041,10 +11041,10 @@
         <v>21</v>
       </c>
       <c r="AA41">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB41">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC41">
         <v>7.2</v>
@@ -11095,7 +11095,7 @@
         <v>16.5</v>
       </c>
       <c r="AS41">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT41">
         <v>7.6</v>
@@ -11107,7 +11107,7 @@
         <v>12</v>
       </c>
       <c r="AW41">
-        <v>8.4</v>
+        <v>36</v>
       </c>
       <c r="AX41">
         <v>14</v>
@@ -11119,43 +11119,43 @@
         <v>18</v>
       </c>
       <c r="BA41">
+        <v>9</v>
+      </c>
+      <c r="BB41">
         <v>8.6</v>
       </c>
-      <c r="BB41">
+      <c r="BC41">
+        <v>32</v>
+      </c>
+      <c r="BD41">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE41">
+        <v>9.6</v>
+      </c>
+      <c r="BF41">
         <v>8.4</v>
       </c>
-      <c r="BC41">
-        <v>7.8</v>
-      </c>
-      <c r="BD41">
+      <c r="BG41">
         <v>8.6</v>
-      </c>
-      <c r="BE41">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF41">
-        <v>8</v>
-      </c>
-      <c r="BG41">
-        <v>8.4</v>
       </c>
       <c r="BH41">
         <v>970</v>
       </c>
       <c r="BI41">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="BJ41">
         <v>15</v>
       </c>
       <c r="BK41">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="BL41">
         <v>1000</v>
       </c>
       <c r="BM41">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="BN41">
         <v>6.6</v>
@@ -11167,10 +11167,10 @@
         <v>34</v>
       </c>
       <c r="BQ41">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="BR41">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS41">
         <v>1.82</v>
@@ -11179,13 +11179,13 @@
         <v>7</v>
       </c>
       <c r="BU41">
-        <v>1.62</v>
+        <v>2.76</v>
       </c>
       <c r="BV41">
         <v>38</v>
       </c>
       <c r="BW41">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="BX41">
         <v>65</v>
@@ -11220,10 +11220,10 @@
         <v>275</v>
       </c>
       <c r="F42">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G42">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="H42">
         <v>4.2</v>
@@ -11244,7 +11244,7 @@
         <v>1.04</v>
       </c>
       <c r="N42">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O42">
         <v>1.2</v>
@@ -11256,130 +11256,130 @@
         <v>1.63</v>
       </c>
       <c r="R42">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="S42">
+        <v>2.54</v>
+      </c>
+      <c r="T42">
+        <v>1.61</v>
+      </c>
+      <c r="U42">
         <v>2.5</v>
       </c>
-      <c r="T42">
-        <v>1.52</v>
-      </c>
-      <c r="U42">
-        <v>2.38</v>
-      </c>
       <c r="V42">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W42">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X42">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y42">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="Z42">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="AA42">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB42">
+        <v>13</v>
+      </c>
+      <c r="AC42">
+        <v>9.4</v>
+      </c>
+      <c r="AD42">
         <v>18</v>
       </c>
-      <c r="AC42">
-        <v>970</v>
-      </c>
-      <c r="AD42">
-        <v>32</v>
-      </c>
       <c r="AE42">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AF42">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AG42">
+        <v>11</v>
+      </c>
+      <c r="AH42">
+        <v>16.5</v>
+      </c>
+      <c r="AI42">
+        <v>55</v>
+      </c>
+      <c r="AJ42">
+        <v>23</v>
+      </c>
+      <c r="AK42">
+        <v>18.5</v>
+      </c>
+      <c r="AL42">
+        <v>36</v>
+      </c>
+      <c r="AM42">
+        <v>70</v>
+      </c>
+      <c r="AN42">
+        <v>9</v>
+      </c>
+      <c r="AO42">
+        <v>44</v>
+      </c>
+      <c r="AP42">
+        <v>18.5</v>
+      </c>
+      <c r="AQ42">
+        <v>18.5</v>
+      </c>
+      <c r="AR42">
+        <v>9.4</v>
+      </c>
+      <c r="AS42">
+        <v>42</v>
+      </c>
+      <c r="AT42">
         <v>11.5</v>
       </c>
-      <c r="AH42">
-        <v>40</v>
-      </c>
-      <c r="AI42">
-        <v>140</v>
-      </c>
-      <c r="AJ42">
-        <v>85</v>
-      </c>
-      <c r="AK42">
-        <v>970</v>
-      </c>
-      <c r="AL42">
-        <v>95</v>
-      </c>
-      <c r="AM42">
-        <v>1000</v>
-      </c>
-      <c r="AN42">
-        <v>970</v>
-      </c>
-      <c r="AO42">
-        <v>1000</v>
-      </c>
-      <c r="AP42">
-        <v>1.92</v>
-      </c>
-      <c r="AQ42">
-        <v>6.2</v>
-      </c>
-      <c r="AR42">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS42">
-        <v>18.5</v>
-      </c>
-      <c r="AT42">
+      <c r="AU42">
+        <v>8.4</v>
+      </c>
+      <c r="AV42">
+        <v>15.5</v>
+      </c>
+      <c r="AW42">
+        <v>11.5</v>
+      </c>
+      <c r="AX42">
+        <v>12.5</v>
+      </c>
+      <c r="AY42">
+        <v>9.6</v>
+      </c>
+      <c r="AZ42">
+        <v>13.5</v>
+      </c>
+      <c r="BA42">
         <v>10</v>
       </c>
-      <c r="AU42">
-        <v>7.2</v>
-      </c>
-      <c r="AV42">
-        <v>13.5</v>
-      </c>
-      <c r="AW42">
-        <v>10</v>
-      </c>
-      <c r="AX42">
-        <v>10</v>
-      </c>
-      <c r="AY42">
-        <v>8.4</v>
-      </c>
-      <c r="AZ42">
-        <v>11.5</v>
-      </c>
-      <c r="BA42">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BB42">
-        <v>6.6</v>
+        <v>19</v>
       </c>
       <c r="BC42">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD42">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="BE42">
-        <v>2.08</v>
+        <v>30</v>
       </c>
       <c r="BF42">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BG42">
-        <v>2.08</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH42">
         <v>970</v>
@@ -11489,25 +11489,25 @@
         <v>4.2</v>
       </c>
       <c r="O43">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P43">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q43">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R43">
         <v>1.43</v>
       </c>
       <c r="S43">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="T43">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="U43">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V43">
         <v>2.22</v>
@@ -11594,7 +11594,7 @@
         <v>13</v>
       </c>
       <c r="AX43">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AY43">
         <v>15.5</v>
@@ -11603,22 +11603,22 @@
         <v>14.5</v>
       </c>
       <c r="BA43">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB43">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BC43">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD43">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE43">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF43">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG43">
         <v>7.2</v>
@@ -11707,10 +11707,10 @@
         <v>2.42</v>
       </c>
       <c r="G44">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H44">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I44">
         <v>3</v>
@@ -11824,7 +11824,7 @@
         <v>25</v>
       </c>
       <c r="AT44">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU44">
         <v>8</v>
@@ -11872,7 +11872,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ44">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK44">
         <v>1.01</v>
@@ -11896,25 +11896,25 @@
         <v>1.01</v>
       </c>
       <c r="BR44">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS44">
         <v>1.01</v>
       </c>
       <c r="BT44">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU44">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BV44">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW44">
         <v>1.01</v>
       </c>
       <c r="BX44">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY44">
         <v>1.01</v>
@@ -11964,13 +11964,13 @@
         <v>3.85</v>
       </c>
       <c r="L45">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M45">
         <v>1.07</v>
       </c>
       <c r="N45">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O45">
         <v>1.33</v>
@@ -11979,13 +11979,13 @@
         <v>1.95</v>
       </c>
       <c r="Q45">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R45">
         <v>1.37</v>
       </c>
       <c r="S45">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T45">
         <v>1.83</v>
@@ -11994,7 +11994,7 @@
         <v>2.1</v>
       </c>
       <c r="V45">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W45">
         <v>1.98</v>
@@ -12024,10 +12024,10 @@
         <v>70</v>
       </c>
       <c r="AF45">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG45">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH45">
         <v>18.5</v>
@@ -12060,10 +12060,10 @@
         <v>13.5</v>
       </c>
       <c r="AR45">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AS45">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT45">
         <v>8.199999999999999</v>
@@ -12075,7 +12075,7 @@
         <v>15</v>
       </c>
       <c r="AW45">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AX45">
         <v>11</v>
@@ -12087,25 +12087,25 @@
         <v>16</v>
       </c>
       <c r="BA45">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB45">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BC45">
         <v>18.5</v>
       </c>
       <c r="BD45">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE45">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF45">
         <v>12</v>
       </c>
       <c r="BG45">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH45">
         <v>1000</v>
@@ -12117,7 +12117,7 @@
         <v>14.5</v>
       </c>
       <c r="BK45">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BL45">
         <v>1000</v>
@@ -12135,7 +12135,7 @@
         <v>20</v>
       </c>
       <c r="BQ45">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="BR45">
         <v>40</v>
@@ -12153,7 +12153,7 @@
         <v>50</v>
       </c>
       <c r="BW45">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="BX45">
         <v>65</v>
@@ -12162,7 +12162,7 @@
         <v>1.78</v>
       </c>
       <c r="BZ45">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CA45">
         <v>1.74</v>
@@ -12188,13 +12188,13 @@
         <v>279</v>
       </c>
       <c r="F46">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G46">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="H46">
-        <v>2.74</v>
+        <v>2.98</v>
       </c>
       <c r="I46">
         <v>3.55</v>
@@ -12203,151 +12203,151 @@
         <v>3.45</v>
       </c>
       <c r="K46">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="L46">
         <v>1.31</v>
       </c>
       <c r="M46">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N46">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O46">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="P46">
         <v>1.81</v>
       </c>
       <c r="Q46">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="R46">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S46">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T46">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U46">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V46">
         <v>1.39</v>
       </c>
       <c r="W46">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="X46">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y46">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z46">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA46">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB46">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC46">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD46">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE46">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF46">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG46">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH46">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI46">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ46">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK46">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL46">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM46">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN46">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO46">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP46">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ46">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AR46">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AS46">
         <v>1.01</v>
       </c>
       <c r="AT46">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU46">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV46">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW46">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AX46">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY46">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ46">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA46">
         <v>1.01</v>
       </c>
       <c r="BB46">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BC46">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BD46">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BE46">
         <v>1.01</v>
       </c>
       <c r="BF46">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG46">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BH46">
         <v>1000</v>
@@ -12430,19 +12430,19 @@
         <v>280</v>
       </c>
       <c r="F47">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G47">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H47">
         <v>3</v>
       </c>
       <c r="I47">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J47">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K47">
         <v>4.3</v>
@@ -12454,40 +12454,40 @@
         <v>1.04</v>
       </c>
       <c r="N47">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O47">
         <v>1.2</v>
       </c>
       <c r="P47">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="Q47">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="R47">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S47">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="T47">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="U47">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="V47">
         <v>1.42</v>
       </c>
       <c r="W47">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X47">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Y47">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z47">
         <v>36</v>
@@ -12508,7 +12508,7 @@
         <v>36</v>
       </c>
       <c r="AF47">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG47">
         <v>12</v>
@@ -12520,7 +12520,7 @@
         <v>40</v>
       </c>
       <c r="AJ47">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK47">
         <v>22</v>
@@ -12532,7 +12532,7 @@
         <v>65</v>
       </c>
       <c r="AN47">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AO47">
         <v>23</v>
@@ -12556,7 +12556,7 @@
         <v>8.4</v>
       </c>
       <c r="AV47">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW47">
         <v>1.01</v>
@@ -12586,7 +12586,7 @@
         <v>1.01</v>
       </c>
       <c r="BF47">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG47">
         <v>16</v>
@@ -12705,19 +12705,19 @@
         <v>2.48</v>
       </c>
       <c r="Q48">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R48">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S48">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T48">
         <v>2.4</v>
       </c>
       <c r="U48">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V48">
         <v>1.05</v>
@@ -12726,7 +12726,7 @@
         <v>5</v>
       </c>
       <c r="X48">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y48">
         <v>60</v>
@@ -12914,22 +12914,22 @@
         <v>282</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="G49">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="H49">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="I49">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="J49">
+        <v>3.35</v>
+      </c>
+      <c r="K49">
         <v>3.4</v>
-      </c>
-      <c r="K49">
-        <v>3.5</v>
       </c>
       <c r="L49">
         <v>1.42</v>
@@ -12938,49 +12938,49 @@
         <v>1.08</v>
       </c>
       <c r="N49">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O49">
         <v>1.35</v>
       </c>
       <c r="P49">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q49">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R49">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S49">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="T49">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U49">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V49">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="W49">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="X49">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y49">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z49">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AA49">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AB49">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC49">
         <v>7.6</v>
@@ -12992,46 +12992,46 @@
         <v>32</v>
       </c>
       <c r="AF49">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG49">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH49">
         <v>18</v>
       </c>
       <c r="AI49">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AJ49">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="AK49">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AL49">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AM49">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN49">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO49">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AP49">
         <v>11.5</v>
       </c>
       <c r="AQ49">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR49">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AS49">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="AT49">
         <v>10</v>
@@ -13040,10 +13040,10 @@
         <v>7</v>
       </c>
       <c r="AV49">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW49">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AX49">
         <v>17</v>
@@ -13052,28 +13052,28 @@
         <v>11.5</v>
       </c>
       <c r="AZ49">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA49">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="BB49">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="BC49">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="BD49">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="BE49">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="BF49">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="BG49">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BH49">
         <v>970</v>
@@ -13082,7 +13082,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ49">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BK49">
         <v>1.01</v>
@@ -13183,19 +13183,19 @@
         <v>1.24</v>
       </c>
       <c r="O50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P50">
         <v>1.24</v>
       </c>
       <c r="Q50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R50">
         <v>1.12</v>
       </c>
       <c r="S50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="T50">
         <v>1.01</v>
@@ -13401,7 +13401,7 @@
         <v>2.22</v>
       </c>
       <c r="G51">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H51">
         <v>2.76</v>
@@ -13428,7 +13428,7 @@
         <v>1.13</v>
       </c>
       <c r="P51">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="Q51">
         <v>1.43</v>
@@ -13449,7 +13449,7 @@
         <v>1.45</v>
       </c>
       <c r="W51">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X51">
         <v>1000</v>
@@ -13470,7 +13470,7 @@
         <v>22</v>
       </c>
       <c r="AD51">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AE51">
         <v>1000</v>
@@ -13503,7 +13503,7 @@
         <v>970</v>
       </c>
       <c r="AO51">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP51">
         <v>1.01</v>
@@ -13643,19 +13643,19 @@
         <v>2.62</v>
       </c>
       <c r="G52">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="H52">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="I52">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="J52">
         <v>4.5</v>
       </c>
       <c r="K52">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L52">
         <v>1.01</v>
@@ -13664,88 +13664,88 @@
         <v>1.02</v>
       </c>
       <c r="N52">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="O52">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P52">
         <v>4</v>
       </c>
       <c r="Q52">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="R52">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="S52">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="T52">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="U52">
         <v>3.6</v>
       </c>
       <c r="V52">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W52">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X52">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="Y52">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z52">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA52">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB52">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC52">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD52">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE52">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF52">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG52">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH52">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AI52">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AJ52">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK52">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL52">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AM52">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AN52">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AO52">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AP52">
         <v>1.01</v>
@@ -13763,43 +13763,43 @@
         <v>1.01</v>
       </c>
       <c r="AU52">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AV52">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW52">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AX52">
         <v>1.01</v>
       </c>
       <c r="AY52">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AZ52">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA52">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BB52">
         <v>1.01</v>
       </c>
       <c r="BC52">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD52">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BE52">
         <v>1.01</v>
       </c>
       <c r="BF52">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG52">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH52">
         <v>1000</v>
@@ -13808,7 +13808,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ52">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK52">
         <v>1.01</v>
@@ -13817,25 +13817,25 @@
         <v>1000</v>
       </c>
       <c r="BM52">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN52">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BO52">
         <v>1.01</v>
       </c>
       <c r="BP52">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ52">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR52">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS52">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BT52">
         <v>1000</v>
@@ -13844,22 +13844,22 @@
         <v>1.01</v>
       </c>
       <c r="BV52">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW52">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX52">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY52">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BZ52">
         <v>1000</v>
       </c>
       <c r="CA52">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="CB52" t="s">
         <v>310</v>
@@ -13882,7 +13882,7 @@
         <v>286</v>
       </c>
       <c r="F53">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="G53">
         <v>1.51</v>
@@ -14127,16 +14127,16 @@
         <v>3.55</v>
       </c>
       <c r="G54">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H54">
         <v>2.32</v>
       </c>
       <c r="I54">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J54">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K54">
         <v>3.45</v>
@@ -14148,31 +14148,31 @@
         <v>1.1</v>
       </c>
       <c r="N54">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O54">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P54">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="Q54">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R54">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="S54">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="T54">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="U54">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="V54">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W54">
         <v>1.35</v>
@@ -14211,10 +14211,10 @@
         <v>20</v>
       </c>
       <c r="AI54">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="AJ54">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AK54">
         <v>60</v>
@@ -14232,7 +14232,7 @@
         <v>25</v>
       </c>
       <c r="AP54">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ54">
         <v>8</v>
@@ -14241,7 +14241,7 @@
         <v>12</v>
       </c>
       <c r="AS54">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT54">
         <v>10.5</v>
@@ -14253,7 +14253,7 @@
         <v>10</v>
       </c>
       <c r="AW54">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AX54">
         <v>20</v>
@@ -14265,13 +14265,13 @@
         <v>16.5</v>
       </c>
       <c r="BA54">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BB54">
-        <v>28</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC54">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BD54">
         <v>9.199999999999999</v>
@@ -14283,7 +14283,7 @@
         <v>9</v>
       </c>
       <c r="BG54">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BH54">
         <v>970</v>
@@ -14375,10 +14375,10 @@
         <v>2.52</v>
       </c>
       <c r="I55">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="J55">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K55">
         <v>3.85</v>
@@ -14393,22 +14393,22 @@
         <v>4.4</v>
       </c>
       <c r="O55">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P55">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q55">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="R55">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="S55">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="T55">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U55">
         <v>2.34</v>
@@ -14435,7 +14435,7 @@
         <v>14</v>
       </c>
       <c r="AC55">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AD55">
         <v>12.5</v>
@@ -14614,10 +14614,10 @@
         <v>1.29</v>
       </c>
       <c r="H56">
+        <v>13.5</v>
+      </c>
+      <c r="I56">
         <v>14</v>
-      </c>
-      <c r="I56">
-        <v>14.5</v>
       </c>
       <c r="J56">
         <v>6.6</v>
@@ -14635,7 +14635,7 @@
         <v>6</v>
       </c>
       <c r="O56">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P56">
         <v>2.7</v>
@@ -14647,7 +14647,7 @@
         <v>1.68</v>
       </c>
       <c r="S56">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T56">
         <v>2.12</v>
@@ -14665,7 +14665,7 @@
         <v>27</v>
       </c>
       <c r="Y56">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Z56">
         <v>1000</v>
@@ -14734,7 +14734,7 @@
         <v>13.5</v>
       </c>
       <c r="AV56">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AW56">
         <v>48</v>
@@ -14850,22 +14850,22 @@
         <v>290</v>
       </c>
       <c r="F57">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G57">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H57">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I57">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="J57">
         <v>3.6</v>
       </c>
       <c r="K57">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L57">
         <v>1.34</v>
@@ -14892,16 +14892,16 @@
         <v>2.88</v>
       </c>
       <c r="T57">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U57">
         <v>2.38</v>
       </c>
       <c r="V57">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="W57">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X57">
         <v>1000</v>
@@ -15092,13 +15092,13 @@
         <v>291</v>
       </c>
       <c r="F58">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G58">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="H58">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I58">
         <v>5</v>
@@ -15131,10 +15131,10 @@
         <v>1.32</v>
       </c>
       <c r="S58">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T58">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="U58">
         <v>1.97</v>
@@ -15239,7 +15239,7 @@
         <v>17.5</v>
       </c>
       <c r="BC58">
-        <v>18</v>
+        <v>9.6</v>
       </c>
       <c r="BD58">
         <v>23</v>
@@ -15254,7 +15254,7 @@
         <v>1.01</v>
       </c>
       <c r="BH58">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI58">
         <v>2.92</v>
@@ -15263,55 +15263,55 @@
         <v>14.5</v>
       </c>
       <c r="BK58">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="BL58">
         <v>1000</v>
       </c>
       <c r="BM58">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="BN58">
         <v>970</v>
       </c>
       <c r="BO58">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="BP58">
         <v>19</v>
       </c>
       <c r="BQ58">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BR58">
         <v>40</v>
       </c>
       <c r="BS58">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BT58">
         <v>11</v>
       </c>
       <c r="BU58">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BV58">
         <v>60</v>
       </c>
       <c r="BW58">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="BX58">
         <v>70</v>
       </c>
       <c r="BY58">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="BZ58">
         <v>36</v>
       </c>
       <c r="CA58">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CB58" t="s">
         <v>310</v>
@@ -15334,64 +15334,64 @@
         <v>292</v>
       </c>
       <c r="F59">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="G59">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H59">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="I59">
+        <v>3.45</v>
+      </c>
+      <c r="J59">
         <v>3.25</v>
       </c>
-      <c r="J59">
+      <c r="K59">
         <v>3.4</v>
       </c>
-      <c r="K59">
-        <v>3.75</v>
-      </c>
       <c r="L59">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="M59">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N59">
-        <v>3.6</v>
+        <v>2.28</v>
       </c>
       <c r="O59">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="P59">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="Q59">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="R59">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S59">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="T59">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="U59">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="V59">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W59">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X59">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="Y59">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="Z59">
         <v>80</v>
@@ -15400,19 +15400,19 @@
         <v>1000</v>
       </c>
       <c r="AB59">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC59">
+        <v>8</v>
+      </c>
+      <c r="AD59">
         <v>970</v>
       </c>
-      <c r="AC59">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD59">
-        <v>26</v>
-      </c>
       <c r="AE59">
         <v>1000</v>
       </c>
       <c r="AF59">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AG59">
         <v>970</v>
@@ -15442,64 +15442,64 @@
         <v>1000</v>
       </c>
       <c r="AP59">
-        <v>1.65</v>
+        <v>4.6</v>
       </c>
       <c r="AQ59">
         <v>9.4</v>
       </c>
       <c r="AR59">
-        <v>1.82</v>
+        <v>5.2</v>
       </c>
       <c r="AS59">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT59">
+        <v>2.8</v>
+      </c>
+      <c r="AU59">
+        <v>6.6</v>
+      </c>
+      <c r="AV59">
+        <v>12</v>
+      </c>
+      <c r="AW59">
+        <v>9.4</v>
+      </c>
+      <c r="AX59">
+        <v>11</v>
+      </c>
+      <c r="AY59">
+        <v>10</v>
+      </c>
+      <c r="AZ59">
+        <v>5.2</v>
+      </c>
+      <c r="BA59">
+        <v>17</v>
+      </c>
+      <c r="BB59">
         <v>8.4</v>
-      </c>
-      <c r="AU59">
-        <v>6.2</v>
-      </c>
-      <c r="AV59">
-        <v>1.73</v>
-      </c>
-      <c r="AW59">
-        <v>14.5</v>
-      </c>
-      <c r="AX59">
-        <v>10</v>
-      </c>
-      <c r="AY59">
-        <v>1.65</v>
-      </c>
-      <c r="AZ59">
-        <v>5.3</v>
-      </c>
-      <c r="BA59">
-        <v>17.5</v>
-      </c>
-      <c r="BB59">
-        <v>10</v>
       </c>
       <c r="BC59">
         <v>8.6</v>
       </c>
       <c r="BD59">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BE59">
-        <v>1.86</v>
+        <v>17.5</v>
       </c>
       <c r="BF59">
-        <v>1.86</v>
+        <v>21</v>
       </c>
       <c r="BG59">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="BH59">
         <v>970</v>
       </c>
       <c r="BI59">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BJ59">
         <v>1000</v>
@@ -15576,64 +15576,64 @@
         <v>293</v>
       </c>
       <c r="F60">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="G60">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="H60">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="I60">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="J60">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K60">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="L60">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="M60">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N60">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="O60">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P60">
         <v>2.16</v>
       </c>
       <c r="Q60">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R60">
+        <v>1.4</v>
+      </c>
+      <c r="S60">
+        <v>2.96</v>
+      </c>
+      <c r="T60">
+        <v>1.63</v>
+      </c>
+      <c r="U60">
+        <v>2.14</v>
+      </c>
+      <c r="V60">
+        <v>1.76</v>
+      </c>
+      <c r="W60">
         <v>1.39</v>
       </c>
-      <c r="S60">
-        <v>2.92</v>
-      </c>
-      <c r="T60">
-        <v>1.01</v>
-      </c>
-      <c r="U60">
-        <v>1.01</v>
-      </c>
-      <c r="V60">
-        <v>1.72</v>
-      </c>
-      <c r="W60">
-        <v>1.37</v>
-      </c>
       <c r="X60">
         <v>1000</v>
       </c>
       <c r="Y60">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z60">
         <v>1000</v>
@@ -15645,10 +15645,10 @@
         <v>1000</v>
       </c>
       <c r="AC60">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD60">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE60">
         <v>1000</v>
@@ -15681,7 +15681,7 @@
         <v>1000</v>
       </c>
       <c r="AO60">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP60">
         <v>1.01</v>
@@ -15738,16 +15738,16 @@
         <v>1.01</v>
       </c>
       <c r="BH60">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BI60">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BJ60">
         <v>1000</v>
       </c>
       <c r="BK60">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BL60">
         <v>1000</v>
@@ -15759,7 +15759,7 @@
         <v>1000</v>
       </c>
       <c r="BO60">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BP60">
         <v>1000</v>
@@ -15774,10 +15774,10 @@
         <v>1.01</v>
       </c>
       <c r="BT60">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BU60">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BV60">
         <v>1000</v>
@@ -15830,10 +15830,10 @@
         <v>3.25</v>
       </c>
       <c r="J61">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K61">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L61">
         <v>1.38</v>
@@ -15860,10 +15860,10 @@
         <v>3.15</v>
       </c>
       <c r="T61">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U61">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V61">
         <v>1.44</v>
@@ -15887,7 +15887,7 @@
         <v>12</v>
       </c>
       <c r="AC61">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD61">
         <v>13</v>
@@ -15941,7 +15941,7 @@
         <v>11</v>
       </c>
       <c r="AU61">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV61">
         <v>12</v>
@@ -16007,7 +16007,7 @@
         <v>17.5</v>
       </c>
       <c r="BQ61">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BR61">
         <v>29</v>
@@ -16066,10 +16066,10 @@
         <v>2</v>
       </c>
       <c r="H62">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I62">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J62">
         <v>4.1</v>
@@ -16084,10 +16084,10 @@
         <v>1.04</v>
       </c>
       <c r="N62">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O62">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P62">
         <v>2.56</v>
@@ -16096,7 +16096,7 @@
         <v>1.61</v>
       </c>
       <c r="R62">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S62">
         <v>2.52</v>
@@ -16105,10 +16105,10 @@
         <v>1.59</v>
       </c>
       <c r="U62">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V62">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W62">
         <v>2</v>
@@ -16153,13 +16153,13 @@
         <v>23</v>
       </c>
       <c r="AK62">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL62">
         <v>27</v>
       </c>
       <c r="AM62">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN62">
         <v>9.6</v>
@@ -16222,61 +16222,61 @@
         <v>25</v>
       </c>
       <c r="BH62">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BI62">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="BJ62">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK62">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BL62">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM62">
         <v>1.01</v>
       </c>
       <c r="BN62">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BO62">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BP62">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BQ62">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BR62">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BS62">
         <v>1.01</v>
       </c>
       <c r="BT62">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BU62">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV62">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BW62">
         <v>1.01</v>
       </c>
       <c r="BX62">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="BY62">
         <v>1.01</v>
       </c>
       <c r="BZ62">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="CA62">
         <v>1.01</v>
@@ -16302,22 +16302,22 @@
         <v>296</v>
       </c>
       <c r="F63">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="G63">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="H63">
         <v>8.4</v>
       </c>
       <c r="I63">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c r="J63">
         <v>6.8</v>
       </c>
       <c r="K63">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="L63">
         <v>1.01</v>
@@ -16341,10 +16341,10 @@
         <v>2.26</v>
       </c>
       <c r="S63">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="T63">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="U63">
         <v>2.2</v>
@@ -16353,7 +16353,7 @@
         <v>1.04</v>
       </c>
       <c r="W63">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="X63">
         <v>1000</v>
@@ -16547,19 +16547,19 @@
         <v>2.52</v>
       </c>
       <c r="G64">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H64">
         <v>3.15</v>
       </c>
       <c r="I64">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="J64">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K64">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L64">
         <v>1.46</v>
@@ -16568,7 +16568,7 @@
         <v>1.1</v>
       </c>
       <c r="N64">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O64">
         <v>1.45</v>
@@ -16592,10 +16592,10 @@
         <v>1.94</v>
       </c>
       <c r="V64">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W64">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X64">
         <v>10.5</v>
@@ -16628,16 +16628,16 @@
         <v>12.5</v>
       </c>
       <c r="AH64">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI64">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ64">
         <v>46</v>
       </c>
       <c r="AK64">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AL64">
         <v>65</v>
@@ -16646,7 +16646,7 @@
         <v>160</v>
       </c>
       <c r="AN64">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO64">
         <v>55</v>
@@ -16661,7 +16661,7 @@
         <v>18.5</v>
       </c>
       <c r="AS64">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT64">
         <v>7.8</v>
@@ -16673,7 +16673,7 @@
         <v>12.5</v>
       </c>
       <c r="AW64">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AX64">
         <v>14</v>
@@ -16685,25 +16685,25 @@
         <v>17</v>
       </c>
       <c r="BA64">
+        <v>10</v>
+      </c>
+      <c r="BB64">
         <v>9.199999999999999</v>
       </c>
-      <c r="BB64">
-        <v>8.4</v>
-      </c>
       <c r="BC64">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD64">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BE64">
+        <v>11</v>
+      </c>
+      <c r="BF64">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG64">
         <v>10</v>
-      </c>
-      <c r="BF64">
-        <v>8</v>
-      </c>
-      <c r="BG64">
-        <v>8.800000000000001</v>
       </c>
       <c r="BH64">
         <v>970</v>
@@ -16786,16 +16786,16 @@
         <v>298</v>
       </c>
       <c r="F65">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="G65">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="H65">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I65">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J65">
         <v>4.7</v>
@@ -16816,7 +16816,7 @@
         <v>1.26</v>
       </c>
       <c r="P65">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q65">
         <v>1.78</v>
@@ -16825,7 +16825,7 @@
         <v>1.46</v>
       </c>
       <c r="S65">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T65">
         <v>1.97</v>
@@ -16837,13 +16837,13 @@
         <v>1.13</v>
       </c>
       <c r="W65">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="X65">
         <v>22</v>
       </c>
       <c r="Y65">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z65">
         <v>90</v>
@@ -16918,7 +16918,7 @@
         <v>9.4</v>
       </c>
       <c r="AX65">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY65">
         <v>9</v>
@@ -16987,7 +16987,7 @@
         <v>15.5</v>
       </c>
       <c r="BU65">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BV65">
         <v>95</v>
@@ -16996,7 +16996,7 @@
         <v>3.55</v>
       </c>
       <c r="BX65">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BY65">
         <v>3.55</v>
@@ -17028,121 +17028,121 @@
         <v>299</v>
       </c>
       <c r="F66">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="G66">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="H66">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="I66">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="J66">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K66">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="L66">
         <v>1.01</v>
       </c>
       <c r="M66">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N66">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O66">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P66">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="Q66">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="R66">
         <v>1.18</v>
       </c>
       <c r="S66">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T66">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="U66">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="V66">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="W66">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="X66">
         <v>9.800000000000001</v>
       </c>
       <c r="Y66">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z66">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AA66">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AB66">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AC66">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD66">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE66">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AF66">
+        <v>16.5</v>
+      </c>
+      <c r="AG66">
         <v>14.5</v>
       </c>
-      <c r="AG66">
-        <v>13.5</v>
-      </c>
       <c r="AH66">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI66">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AJ66">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AK66">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AL66">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM66">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AN66">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AO66">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="AP66">
         <v>6.6</v>
       </c>
       <c r="AQ66">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AR66">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AS66">
         <v>1.01</v>
@@ -17151,22 +17151,22 @@
         <v>6</v>
       </c>
       <c r="AU66">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AV66">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW66">
         <v>1.01</v>
       </c>
       <c r="AX66">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AY66">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ66">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA66">
         <v>1.01</v>
@@ -17273,16 +17273,16 @@
         <v>1.13</v>
       </c>
       <c r="G67">
-        <v>880</v>
+        <v>190</v>
       </c>
       <c r="H67">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="I67">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="J67">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="K67">
         <v>890</v>
@@ -17294,13 +17294,13 @@
         <v>1.01</v>
       </c>
       <c r="N67">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="O67">
         <v>1.01</v>
       </c>
       <c r="P67">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q67">
         <v>1.26</v>
@@ -17318,10 +17318,10 @@
         <v>1.01</v>
       </c>
       <c r="V67">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W67">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X67">
         <v>1000</v>
@@ -17524,10 +17524,10 @@
         <v>3.8</v>
       </c>
       <c r="J68">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="K68">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="L68">
         <v>1.64</v>
@@ -17539,7 +17539,7 @@
         <v>2.38</v>
       </c>
       <c r="O68">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="P68">
         <v>1.43</v>
@@ -17557,7 +17557,7 @@
         <v>2.4</v>
       </c>
       <c r="U68">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="V68">
         <v>1.36</v>
@@ -17596,7 +17596,7 @@
         <v>14</v>
       </c>
       <c r="AH68">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI68">
         <v>1000</v>
@@ -17632,7 +17632,7 @@
         <v>34</v>
       </c>
       <c r="AT68">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU68">
         <v>6.4</v>
@@ -17683,7 +17683,7 @@
         <v>1000</v>
       </c>
       <c r="BK68">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BL68">
         <v>1000</v>
@@ -17692,10 +17692,10 @@
         <v>1.01</v>
       </c>
       <c r="BN68">
-        <v>6.2</v>
+        <v>970</v>
       </c>
       <c r="BO68">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP68">
         <v>1000</v>
@@ -17710,10 +17710,10 @@
         <v>1.01</v>
       </c>
       <c r="BT68">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="BU68">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV68">
         <v>1000</v>
@@ -17781,25 +17781,25 @@
         <v>2.22</v>
       </c>
       <c r="O69">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="P69">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Q69">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R69">
         <v>1.13</v>
       </c>
       <c r="S69">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="T69">
         <v>2.56</v>
       </c>
       <c r="U69">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="V69">
         <v>1.53</v>
@@ -17814,7 +17814,7 @@
         <v>7</v>
       </c>
       <c r="Z69">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA69">
         <v>60</v>
@@ -17829,7 +17829,7 @@
         <v>17</v>
       </c>
       <c r="AE69">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AF69">
         <v>24</v>
@@ -17841,25 +17841,25 @@
         <v>36</v>
       </c>
       <c r="AI69">
-        <v>910</v>
+        <v>870</v>
       </c>
       <c r="AJ69">
-        <v>790</v>
+        <v>750</v>
       </c>
       <c r="AK69">
-        <v>790</v>
+        <v>750</v>
       </c>
       <c r="AL69">
-        <v>910</v>
+        <v>870</v>
       </c>
       <c r="AM69">
-        <v>760</v>
+        <v>630</v>
       </c>
       <c r="AN69">
-        <v>910</v>
+        <v>870</v>
       </c>
       <c r="AO69">
-        <v>780</v>
+        <v>740</v>
       </c>
       <c r="AP69">
         <v>5.8</v>
@@ -17916,7 +17916,7 @@
         <v>32</v>
       </c>
       <c r="BH69">
-        <v>2.42</v>
+        <v>970</v>
       </c>
       <c r="BI69">
         <v>1.36</v>
@@ -17925,16 +17925,16 @@
         <v>1000</v>
       </c>
       <c r="BK69">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="BL69">
         <v>1000</v>
       </c>
       <c r="BM69">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BN69">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="BO69">
         <v>1.17</v>
@@ -17943,16 +17943,16 @@
         <v>1000</v>
       </c>
       <c r="BQ69">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BR69">
         <v>1000</v>
       </c>
       <c r="BS69">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BT69">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="BU69">
         <v>2.18</v>
@@ -17961,19 +17961,19 @@
         <v>1000</v>
       </c>
       <c r="BW69">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BX69">
         <v>1000</v>
       </c>
       <c r="BY69">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BZ69">
         <v>1000</v>
       </c>
       <c r="CA69">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="CB69" t="s">
         <v>310</v>
@@ -18005,7 +18005,7 @@
         <v>2.18</v>
       </c>
       <c r="I70">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="J70">
         <v>3.45</v>
@@ -18020,88 +18020,88 @@
         <v>1.08</v>
       </c>
       <c r="N70">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="O70">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P70">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
       </c>
       <c r="R70">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S70">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="T70">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U70">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V70">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="W70">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X70">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y70">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z70">
         <v>14.5</v>
       </c>
       <c r="AA70">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB70">
         <v>13.5</v>
       </c>
       <c r="AC70">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD70">
         <v>12.5</v>
       </c>
       <c r="AE70">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF70">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AG70">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AH70">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AI70">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ70">
-        <v>940</v>
+        <v>900</v>
       </c>
       <c r="AK70">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AL70">
-        <v>510</v>
+        <v>470</v>
       </c>
       <c r="AM70">
-        <v>940</v>
+        <v>900</v>
       </c>
       <c r="AN70">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="AO70">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AP70">
         <v>11.5</v>
@@ -18110,16 +18110,16 @@
         <v>8.4</v>
       </c>
       <c r="AR70">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS70">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT70">
         <v>10</v>
       </c>
       <c r="AU70">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV70">
         <v>10.5</v>
@@ -18128,25 +18128,25 @@
         <v>17</v>
       </c>
       <c r="AX70">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY70">
         <v>13</v>
       </c>
       <c r="AZ70">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA70">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB70">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC70">
         <v>25</v>
       </c>
       <c r="BD70">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BE70">
         <v>40</v>
@@ -18238,22 +18238,22 @@
         <v>304</v>
       </c>
       <c r="F71">
+        <v>2.32</v>
+      </c>
+      <c r="G71">
+        <v>2.6</v>
+      </c>
+      <c r="H71">
+        <v>3.15</v>
+      </c>
+      <c r="I71">
+        <v>3.75</v>
+      </c>
+      <c r="J71">
         <v>1.1</v>
       </c>
-      <c r="G71">
-        <v>2.62</v>
-      </c>
-      <c r="H71">
-        <v>3</v>
-      </c>
-      <c r="I71">
-        <v>110</v>
-      </c>
-      <c r="J71">
-        <v>1.01</v>
-      </c>
       <c r="K71">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L71">
         <v>1.01</v>
@@ -18262,16 +18262,16 @@
         <v>1.08</v>
       </c>
       <c r="N71">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="O71">
         <v>1.35</v>
       </c>
       <c r="P71">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q71">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R71">
         <v>1.28</v>
@@ -18289,7 +18289,7 @@
         <v>1.4</v>
       </c>
       <c r="W71">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X71">
         <v>1000</v>
@@ -18480,58 +18480,58 @@
         <v>305</v>
       </c>
       <c r="F72">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="G72">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="H72">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="I72">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="J72">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="K72">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="L72">
         <v>1.55</v>
       </c>
       <c r="M72">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="N72">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="O72">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="P72">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="Q72">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="R72">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S72">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="T72">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U72">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="V72">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W72">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X72">
         <v>8.4</v>
@@ -18552,7 +18552,7 @@
         <v>7.2</v>
       </c>
       <c r="AD72">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AE72">
         <v>75</v>
@@ -18564,16 +18564,16 @@
         <v>12.5</v>
       </c>
       <c r="AH72">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI72">
         <v>100</v>
       </c>
       <c r="AJ72">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK72">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AL72">
         <v>75</v>
@@ -18582,7 +18582,7 @@
         <v>220</v>
       </c>
       <c r="AN72">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO72">
         <v>110</v>
@@ -18597,10 +18597,10 @@
         <v>21</v>
       </c>
       <c r="AS72">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AT72">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU72">
         <v>6.4</v>
@@ -18609,7 +18609,7 @@
         <v>14.5</v>
       </c>
       <c r="AW72">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AX72">
         <v>12.5</v>
@@ -18621,25 +18621,25 @@
         <v>20</v>
       </c>
       <c r="BA72">
+        <v>11</v>
+      </c>
+      <c r="BB72">
         <v>9.4</v>
       </c>
-      <c r="BB72">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BC72">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BD72">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BE72">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BF72">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG72">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BH72">
         <v>970</v>
@@ -18725,7 +18725,7 @@
         <v>1.73</v>
       </c>
       <c r="G73">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="H73">
         <v>4.7</v>
@@ -18770,10 +18770,10 @@
         <v>1.01</v>
       </c>
       <c r="V73">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W73">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="X73">
         <v>1000</v>
@@ -18967,19 +18967,19 @@
         <v>1.45</v>
       </c>
       <c r="G74">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="H74">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="I74">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="J74">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="K74">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="L74">
         <v>1.33</v>
@@ -18988,34 +18988,34 @@
         <v>1.04</v>
       </c>
       <c r="N74">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O74">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P74">
         <v>2.3</v>
       </c>
       <c r="Q74">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="R74">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="S74">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="T74">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="U74">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="V74">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W74">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="X74">
         <v>21</v>
@@ -19120,7 +19120,7 @@
         <v>12.5</v>
       </c>
       <c r="BF74">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BG74">
         <v>12</v>
@@ -19215,10 +19215,10 @@
         <v>1.13</v>
       </c>
       <c r="I75">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="J75">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="K75">
         <v>900</v>
@@ -19230,13 +19230,13 @@
         <v>1.01</v>
       </c>
       <c r="N75">
+        <v>1.46</v>
+      </c>
+      <c r="O75">
+        <v>1.01</v>
+      </c>
+      <c r="P75">
         <v>1.45</v>
-      </c>
-      <c r="O75">
-        <v>1.01</v>
-      </c>
-      <c r="P75">
-        <v>1.25</v>
       </c>
       <c r="Q75">
         <v>1.29</v>
@@ -19254,10 +19254,10 @@
         <v>1.01</v>
       </c>
       <c r="V75">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W75">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X75">
         <v>1000</v>
@@ -19451,10 +19451,10 @@
         <v>2.5</v>
       </c>
       <c r="G76">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H76">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="I76">
         <v>3.05</v>
@@ -19499,7 +19499,7 @@
         <v>1.48</v>
       </c>
       <c r="W76">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X76">
         <v>16.5</v>
@@ -19622,7 +19622,7 @@
         <v>1.01</v>
       </c>
       <c r="BL76">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM76">
         <v>1.01</v>
@@ -19637,13 +19637,13 @@
         <v>1000</v>
       </c>
       <c r="BQ76">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BR76">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS76">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BT76">
         <v>1000</v>
@@ -19664,10 +19664,10 @@
         <v>1.01</v>
       </c>
       <c r="BZ76">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA76">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="CB76" t="s">
         <v>310</v>
